--- a/DesignData/Excel_Masters/EnemyAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/EnemyAssets_Master.xlsx
@@ -1239,235 +1239,376 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>19</v>
       </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>20</v>
       </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>21</v>
       </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="J47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>54</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/EnemyAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/EnemyAssets_Master.xlsx
@@ -9,247 +9,526 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21555" windowHeight="8040"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15420" windowHeight="10965"/>
   </bookViews>
   <sheets>
-    <sheet name="EnemyStats_Master" sheetId="1" r:id="rId1"/>
-    <sheet name="Tags" sheetId="2" r:id="rId2"/>
+    <sheet name="EnemyAssets" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
-  <si>
-    <t>Unit.Attack.Melee</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Attack.Range</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Role.Tanker</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Role.Dealer</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Role.Support</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Rank.Normal</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Rank.Elite</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unit.Rank.Boss</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="170">
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>SkillEffectTags</t>
+  </si>
+  <si>
+    <t>FaceIcon</t>
+  </si>
+  <si>
+    <t>Scale</t>
+  </si>
+  <si>
+    <t>AIController</t>
+  </si>
+  <si>
+    <t>BehaviorTree</t>
+  </si>
+  <si>
+    <t>Blackboard</t>
+  </si>
+  <si>
+    <t>BasicAttackEffect</t>
+  </si>
+  <si>
+    <t>BasicAbility</t>
+  </si>
+  <si>
+    <t>SkillAbilities</t>
+  </si>
+  <si>
+    <t>ProjectileClass</t>
+  </si>
+  <si>
+    <t>BasicAttackEffectTag</t>
+  </si>
+  <si>
+    <t>SkeletalMesh</t>
+  </si>
+  <si>
+    <t>AnimBlueprint</t>
+  </si>
+  <si>
+    <t>AttackMontage</t>
+  </si>
+  <si>
+    <t>HitMontage</t>
+  </si>
+  <si>
+    <t>DeathMontage</t>
+  </si>
+  <si>
+    <t>UnitFXData</t>
+  </si>
+  <si>
+    <t>HitReactionTag</t>
   </si>
   <si>
     <t>Balrog</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Balrog_A.Icon_Balrog_A</t>
+  </si>
+  <si>
+    <t>/Script/Engine.BlueprintGeneratedClass'/Game/Test/KMJ/AI/BP_MyAIController.BP_MyAIController_C'</t>
+  </si>
+  <si>
+    <t>/Game/Test/KMJ/AI/BT_Monster.BT_Monster</t>
+  </si>
+  <si>
+    <t>/Game/Test/KMJ/AI/BB_Monster.BB_Monster</t>
+  </si>
+  <si>
+    <t>/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_MeleeBasicAttack.GA_MeleeBasicAttack_C'</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>(TagName="")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Balrog/SKM_Balrog.SKM_Balrog</t>
+  </si>
+  <si>
     <t>Bearking</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_BearKing.Icon_BearKing</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Bearking/SKM_BearKing_A.SKM_BearKing_A</t>
+  </si>
+  <si>
     <t>BombSpider</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_BombSpider.Icon_BombSpider</t>
+  </si>
+  <si>
     <t>BronzeGear</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_BronzeGear.Icon_BronzeGear</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/BronzeGear/SKM_BronzeGear.SKM_BronzeGear</t>
+  </si>
+  <si>
     <t>Cell</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Cell.Icon_Cell</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Cell/SKM_Cell.SKM_Cell</t>
+  </si>
+  <si>
     <t>Cursedmass</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Cursedmass.Icon_Cursedmass</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Cursedmass/SKM_Cursedmass.SKM_Cursedmass</t>
+  </si>
+  <si>
     <t>DanceMakane</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_DanceMakane.Icon_DanceMakane</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/DanceMakane/SKM_DanceMakane.SKM_DanceMakane</t>
+  </si>
+  <si>
     <t>Deatheye</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_DeathEye.Icon_DeathEye</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Deatheye/SKM_Deatheye.SKM_Deatheye</t>
+  </si>
+  <si>
     <t>DieS</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_DieS.Icon_DieS</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/DieS/SKM_DieS.SKM_DieS</t>
+  </si>
+  <si>
     <t>DoctorMacaron</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_DoctorMacaron.Icon_DoctorMacaron</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/DoctorMacaron/SKM_DoctorMacaron.SKM_DoctorMacaron</t>
+  </si>
+  <si>
     <t>Famine</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Famine.Icon_Famine</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Famine/SKM_Famine.SKM_Famine</t>
+  </si>
+  <si>
     <t>FelicisMachine</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_FelicisMachine.Icon_FelicisMachine</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/FelicisMachine/SKM_FelicisMachine.SKM_FelicisMachine</t>
+  </si>
+  <si>
     <t>FelicisShinobi</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_FelicisShinobi.Icon_FelicisShinobi</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/FelicisShinobi/SKM_FelicisShinobi.SKM_FelicisShinobi</t>
+  </si>
+  <si>
     <t>Fiti</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Fiti.Icon_Fiti</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Fiti/SKM_Fiti.SKM_Fiti</t>
+  </si>
+  <si>
     <t>Gemini_Scythe</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Gemini_Scythe.Icon_Gemini_Scythe</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Gemini_Scythe/SKM_Gemini_Scythe.SKM_Gemini_Scythe</t>
+  </si>
+  <si>
     <t>GhostMacaron</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_GhostMacaron.Icon_GhostMacaron</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/GhostMacaron/SKM_Ghostmacaron.SKM_Ghostmacaron</t>
+  </si>
+  <si>
     <t>Graf</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Graf.Icon_Graf</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Graf/SKM_Graf.SKM_Graf</t>
+  </si>
+  <si>
     <t>GuardianTreant</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_GuardianTreant.Icon_GuardianTreant</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/GuardianTreant/SKM_GuardianTreant.SKM_GuardianTreant</t>
+  </si>
+  <si>
     <t>HackingTool</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_HackingTool.Icon_HackingTool</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/HackingTool/SKM_HackingTool.SKM_HackingTool</t>
+  </si>
+  <si>
     <t>Hanged_Macaron</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Hanged_Macaron.Icon_Hanged_Macaron</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Hanged_Macaron/SKM_Hanged_Macaron.SKM_Hanged_Macaron</t>
+  </si>
+  <si>
     <t>HoneyMos</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_HoneyMos.Icon_HoneyMos</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/HoneyMos/SKM_HoneyMos.SKM_HoneyMos</t>
+  </si>
+  <si>
     <t>Jellyfish</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Jellyfish.Icon_Jellyfish</t>
+  </si>
+  <si>
+    <t>/Script/Engine.BlueprintGeneratedClass'/Game/Test/KMJ/AI/BP_MyAIController_Range.BP_MyAIController_Range_C'</t>
+  </si>
+  <si>
+    <t>/Game/Test/KMJ/AI/BT_Monster_Ranged.BT_Monster_Ranged</t>
+  </si>
+  <si>
+    <t>/Game/Test/KMJ/AI/BB_Monster_Ranged.BB_Monster_Ranged</t>
+  </si>
+  <si>
+    <t>/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_RangeBasicAttack.GA_RangeBasicAttack_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.BlueprintGeneratedClass'/Game/Test/YSM/BP_FireBall.BP_FireBall_C'</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Jellyfish/SKM_JellyFish.SKM_JellyFish</t>
+  </si>
+  <si>
     <t>Karakasa</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Karakasa.Icon_Karakasa</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Karakasa/SKM_Karakasa.SKM_Karakasa</t>
+  </si>
+  <si>
     <t>Kraken</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Kraken.Icon_Kraken</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Kraken/SKM_Kraken.SKM_Kraken</t>
+  </si>
+  <si>
     <t>KrakenTentacle</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_KrakenTentacle.Icon_KrakenTentacle</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/KrakenTentacle/SKM_KrakenTentacle.SKM_KrakenTentacle</t>
+  </si>
+  <si>
     <t>Leechking</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_LeechKing.Icon_LeechKing</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Leechking/SKM_LeechKing.SKM_LeechKing</t>
+  </si>
+  <si>
     <t>LikeStatue</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_LikeStatue.Icon_LikeStatue</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/LikeStatue/SKM_LikeStatue1.SKM_LikeStatue1</t>
+  </si>
+  <si>
     <t>LordFelice</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_LordFelice.Icon_LordFelice</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/LordFelice/SKM_LordFelice.SKM_LordFelice</t>
+  </si>
+  <si>
     <t>Makane</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Makane.Icon_Makane</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Makane/SKM_Makane_A.SKM_Makane_A</t>
+  </si>
+  <si>
     <t>Mandragora</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Mandragora.Icon_Mandragora</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Mandragora/SKM_Mandragora.SKM_Mandragora</t>
+  </si>
+  <si>
     <t>MaskScarecrow</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_MaskScarecrow.Icon_MaskScarecrow</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Mask/SKM_Mask.SKM_Mask</t>
+  </si>
+  <si>
     <t>Mechanicus</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Mechanicus.Icon_Mechanicus</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Mechanicus/SKM_Mechanicus.SKM_Mechanicus</t>
+  </si>
+  <si>
     <t>Megaron</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Megaron.Icon_Megaron</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Megaron/SKM_Megaron_A.SKM_Megaron_A</t>
+  </si>
+  <si>
     <t>Mimic</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Mimic.Icon_Mimic</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Mimic/SKM_Mimic.SKM_Mimic</t>
+  </si>
+  <si>
     <t>Octopus</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Octopus.Icon_Octopus</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Octopus/SKM_octopus.SKM_octopus</t>
+  </si>
+  <si>
     <t>PistolShrimp</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_PistolShrimp.Icon_PistolShrimp</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/PistolShrimp/SKM_PistolShrimp.SKM_PistolShrimp</t>
+  </si>
+  <si>
     <t>Pufferfish</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Pufferfish.Icon_Pufferfish</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Pufferfish/SKM_PufferFish_A.SKM_PufferFish_A</t>
+  </si>
+  <si>
     <t>Seasoner</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Seasoner.Icon_Seasoner</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Seasoner/SKM_Seasoner.SKM_Seasoner</t>
+  </si>
+  <si>
     <t>SharkRider</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_SharkRider.Icon_SharkRider</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/SharkRider/SKM_SharkRider.SKM_SharkRider</t>
+  </si>
+  <si>
     <t>SoundPro</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_SoundPro.Icon_SoundPro</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/SoundPro/SKM_SoundPro.SKM_SoundPro</t>
+  </si>
+  <si>
     <t>Starspawn</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Starspawn.Icon_Starspawn</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Starspawn/SKM_Starspawn.SKM_Starspawn</t>
+  </si>
+  <si>
     <t>TinWoodman</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_TinWoodman.Icon_TinWoodman</t>
+  </si>
+  <si>
     <t>Ushabti</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Ushabti.Icon_Ushabti</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Ushabti/SKM_Ushabti.SKM_Ushabti</t>
+  </si>
+  <si>
     <t>Wagon</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Wagon.Icon_Wagon</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Wagon/SKM_wagon_A.SKM_wagon_A</t>
+  </si>
+  <si>
     <t>Watcher</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Watcher.Icon_Watcher</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Watcher/SKM_Watcher_A.SKM_Watcher_A</t>
+  </si>
+  <si>
     <t>Weaponmaster</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Weaponmaster.Icon_Weaponmaster</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Weaponmaster/SKM_weaponmaster_B.SKM_weaponmaster_B</t>
+  </si>
+  <si>
     <t>Wolfron</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>SkeletalMesh</t>
-  </si>
-  <si>
-    <t>AnimBlueprint</t>
-  </si>
-  <si>
-    <t>AttackMontage</t>
-  </si>
-  <si>
-    <t>HitMontage</t>
-  </si>
-  <si>
-    <t>DeathMontage</t>
-  </si>
-  <si>
-    <t>VoiceDataAsset</t>
-  </si>
-  <si>
-    <t>HitReactionTag</t>
-  </si>
-  <si>
-    <t>FaceIcon</t>
-  </si>
-  <si>
-    <t>Scale</t>
-  </si>
-  <si>
-    <t>AIController</t>
-  </si>
-  <si>
-    <t>BehaviorTree</t>
-  </si>
-  <si>
-    <t>Blackboard</t>
-  </si>
-  <si>
-    <t>BasicAttackEffect</t>
-  </si>
-  <si>
-    <t>BasicAbility</t>
-  </si>
-  <si>
-    <t>SkillAbilities</t>
-  </si>
-  <si>
-    <t>ProjectileClass</t>
-  </si>
-  <si>
-    <t>BasicAttackEffectTag</t>
-  </si>
-  <si>
-    <t>SkillEffectTags</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Wolfron.Icon_Wolfron</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Wolfron/SKM_wolfron_C.SKM_wolfron_C</t>
   </si>
 </sst>
 </file>
@@ -1169,544 +1448,2555 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S48"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="15.625" customWidth="1"/>
-    <col min="3" max="3" width="14.125" customWidth="1"/>
-    <col min="4" max="4" width="13.5" customWidth="1"/>
-    <col min="6" max="6" width="9.125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="S1" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K3" t="s">
+        <v>94</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R3" t="s">
+        <v>26</v>
+      </c>
+      <c r="S3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>26</v>
+      </c>
+      <c r="R4" t="s">
+        <v>26</v>
+      </c>
+      <c r="S4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" t="s">
+        <v>91</v>
+      </c>
+      <c r="G5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K5" t="s">
+        <v>94</v>
+      </c>
+      <c r="L5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" t="s">
+        <v>26</v>
+      </c>
+      <c r="O5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>26</v>
+      </c>
+      <c r="R5" t="s">
+        <v>26</v>
+      </c>
+      <c r="S5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F6" t="s">
+        <v>91</v>
+      </c>
+      <c r="G6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" t="s">
+        <v>93</v>
+      </c>
+      <c r="K6" t="s">
+        <v>94</v>
+      </c>
+      <c r="L6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O6" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>26</v>
+      </c>
+      <c r="R6" t="s">
+        <v>26</v>
+      </c>
+      <c r="S6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N7" t="s">
+        <v>26</v>
+      </c>
+      <c r="O7" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>26</v>
+      </c>
+      <c r="R7" t="s">
+        <v>26</v>
+      </c>
+      <c r="S7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" t="s">
+        <v>45</v>
+      </c>
+      <c r="N8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>26</v>
+      </c>
+      <c r="R8" t="s">
+        <v>26</v>
+      </c>
+      <c r="S8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F9" t="s">
+        <v>91</v>
+      </c>
+      <c r="G9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" t="s">
+        <v>93</v>
+      </c>
+      <c r="K9" t="s">
+        <v>94</v>
+      </c>
+      <c r="L9" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" t="s">
+        <v>48</v>
+      </c>
+      <c r="N9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O9" t="s">
+        <v>26</v>
+      </c>
+      <c r="P9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>26</v>
+      </c>
+      <c r="R9" t="s">
+        <v>26</v>
+      </c>
+      <c r="S9" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
+        <v>49</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O10" t="s">
+        <v>26</v>
+      </c>
+      <c r="P10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>26</v>
+      </c>
+      <c r="R10" t="s">
+        <v>26</v>
+      </c>
+      <c r="S10" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" t="s">
+        <v>93</v>
+      </c>
+      <c r="K11" t="s">
+        <v>94</v>
+      </c>
+      <c r="L11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N11" t="s">
+        <v>26</v>
+      </c>
+      <c r="O11" t="s">
+        <v>26</v>
+      </c>
+      <c r="P11" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>26</v>
+      </c>
+      <c r="R11" t="s">
+        <v>26</v>
+      </c>
+      <c r="S11" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
+        <v>55</v>
+      </c>
+      <c r="C12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" t="s">
+        <v>26</v>
+      </c>
+      <c r="O12" t="s">
+        <v>26</v>
+      </c>
+      <c r="P12" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>26</v>
+      </c>
+      <c r="R12" t="s">
+        <v>26</v>
+      </c>
+      <c r="S12" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
+        <v>58</v>
+      </c>
+      <c r="C13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" t="s">
+        <v>27</v>
+      </c>
+      <c r="M13" t="s">
+        <v>60</v>
+      </c>
+      <c r="N13" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13" t="s">
+        <v>26</v>
+      </c>
+      <c r="P13" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>26</v>
+      </c>
+      <c r="R13" t="s">
+        <v>26</v>
+      </c>
+      <c r="S13" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
+        <v>61</v>
+      </c>
+      <c r="C14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" t="s">
+        <v>93</v>
+      </c>
+      <c r="K14" t="s">
+        <v>94</v>
+      </c>
+      <c r="L14" t="s">
+        <v>27</v>
+      </c>
+      <c r="M14" t="s">
+        <v>63</v>
+      </c>
+      <c r="N14" t="s">
+        <v>26</v>
+      </c>
+      <c r="O14" t="s">
+        <v>26</v>
+      </c>
+      <c r="P14" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>26</v>
+      </c>
+      <c r="R14" t="s">
+        <v>26</v>
+      </c>
+      <c r="S14" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
         <v>21</v>
       </c>
-      <c r="J15">
-        <v>1</v>
+      <c r="F15" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" t="s">
+        <v>25</v>
+      </c>
+      <c r="K15" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15" t="s">
+        <v>66</v>
+      </c>
+      <c r="N15" t="s">
+        <v>26</v>
+      </c>
+      <c r="O15" t="s">
+        <v>26</v>
+      </c>
+      <c r="P15" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>26</v>
+      </c>
+      <c r="R15" t="s">
+        <v>26</v>
+      </c>
+      <c r="S15" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
         <v>22</v>
       </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" t="s">
+        <v>27</v>
+      </c>
+      <c r="M16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N16" t="s">
+        <v>26</v>
+      </c>
+      <c r="O16" t="s">
+        <v>26</v>
+      </c>
+      <c r="P16" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>26</v>
+      </c>
+      <c r="R16" t="s">
+        <v>26</v>
+      </c>
+      <c r="S16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" t="s">
         <v>23</v>
       </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17" t="s">
+        <v>72</v>
+      </c>
+      <c r="N17" t="s">
+        <v>26</v>
+      </c>
+      <c r="O17" t="s">
+        <v>26</v>
+      </c>
+      <c r="P17" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>26</v>
+      </c>
+      <c r="R17" t="s">
+        <v>26</v>
+      </c>
+      <c r="S17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+      <c r="C18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18" t="s">
+        <v>75</v>
+      </c>
+      <c r="N18" t="s">
+        <v>26</v>
+      </c>
+      <c r="O18" t="s">
+        <v>26</v>
+      </c>
+      <c r="P18" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>26</v>
+      </c>
+      <c r="R18" t="s">
+        <v>26</v>
+      </c>
+      <c r="S18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" t="s">
         <v>25</v>
       </c>
-      <c r="J19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K19" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19" t="s">
+        <v>78</v>
+      </c>
+      <c r="N19" t="s">
+        <v>26</v>
+      </c>
+      <c r="O19" t="s">
+        <v>26</v>
+      </c>
+      <c r="P19" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>26</v>
+      </c>
+      <c r="R19" t="s">
+        <v>26</v>
+      </c>
+      <c r="S19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+      <c r="C20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" t="s">
+        <v>91</v>
+      </c>
+      <c r="G20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" t="s">
+        <v>93</v>
+      </c>
+      <c r="K20" t="s">
+        <v>94</v>
+      </c>
+      <c r="L20" t="s">
+        <v>27</v>
+      </c>
+      <c r="M20" t="s">
+        <v>81</v>
+      </c>
+      <c r="N20" t="s">
+        <v>26</v>
+      </c>
+      <c r="O20" t="s">
+        <v>26</v>
+      </c>
+      <c r="P20" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>26</v>
+      </c>
+      <c r="R20" t="s">
+        <v>26</v>
+      </c>
+      <c r="S20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>27</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+      <c r="C21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" t="s">
+        <v>93</v>
+      </c>
+      <c r="K21" t="s">
+        <v>94</v>
+      </c>
+      <c r="L21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21" t="s">
+        <v>84</v>
+      </c>
+      <c r="N21" t="s">
+        <v>26</v>
+      </c>
+      <c r="O21" t="s">
+        <v>26</v>
+      </c>
+      <c r="P21" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>26</v>
+      </c>
+      <c r="R21" t="s">
+        <v>26</v>
+      </c>
+      <c r="S21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>28</v>
-      </c>
-      <c r="J22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+      <c r="C22" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" t="s">
+        <v>25</v>
+      </c>
+      <c r="K22" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" t="s">
+        <v>27</v>
+      </c>
+      <c r="M22" t="s">
+        <v>87</v>
+      </c>
+      <c r="N22" t="s">
+        <v>26</v>
+      </c>
+      <c r="O22" t="s">
+        <v>26</v>
+      </c>
+      <c r="P22" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>26</v>
+      </c>
+      <c r="R22" t="s">
+        <v>26</v>
+      </c>
+      <c r="S22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>29</v>
-      </c>
-      <c r="J23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+      <c r="C23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K23" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" t="s">
+        <v>95</v>
+      </c>
+      <c r="N23" t="s">
+        <v>26</v>
+      </c>
+      <c r="O23" t="s">
+        <v>26</v>
+      </c>
+      <c r="P23" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>26</v>
+      </c>
+      <c r="R23" t="s">
+        <v>26</v>
+      </c>
+      <c r="S23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>30</v>
-      </c>
-      <c r="J24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+      <c r="C24" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" t="s">
+        <v>91</v>
+      </c>
+      <c r="G24" t="s">
+        <v>92</v>
+      </c>
+      <c r="H24" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" t="s">
+        <v>93</v>
+      </c>
+      <c r="K24" t="s">
+        <v>94</v>
+      </c>
+      <c r="L24" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" t="s">
+        <v>98</v>
+      </c>
+      <c r="N24" t="s">
+        <v>26</v>
+      </c>
+      <c r="O24" t="s">
+        <v>26</v>
+      </c>
+      <c r="P24" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>26</v>
+      </c>
+      <c r="R24" t="s">
+        <v>26</v>
+      </c>
+      <c r="S24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>31</v>
-      </c>
-      <c r="J25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+      <c r="C25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25" t="s">
+        <v>25</v>
+      </c>
+      <c r="K25" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" t="s">
+        <v>27</v>
+      </c>
+      <c r="M25" t="s">
+        <v>101</v>
+      </c>
+      <c r="N25" t="s">
+        <v>26</v>
+      </c>
+      <c r="O25" t="s">
+        <v>26</v>
+      </c>
+      <c r="P25" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>26</v>
+      </c>
+      <c r="R25" t="s">
+        <v>26</v>
+      </c>
+      <c r="S25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>32</v>
-      </c>
-      <c r="J26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+      <c r="C26" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>90</v>
+      </c>
+      <c r="F26" t="s">
+        <v>91</v>
+      </c>
+      <c r="G26" t="s">
+        <v>92</v>
+      </c>
+      <c r="H26" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" t="s">
+        <v>93</v>
+      </c>
+      <c r="K26" t="s">
+        <v>94</v>
+      </c>
+      <c r="L26" t="s">
+        <v>27</v>
+      </c>
+      <c r="M26" t="s">
+        <v>104</v>
+      </c>
+      <c r="N26" t="s">
+        <v>26</v>
+      </c>
+      <c r="O26" t="s">
+        <v>26</v>
+      </c>
+      <c r="P26" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>26</v>
+      </c>
+      <c r="R26" t="s">
+        <v>26</v>
+      </c>
+      <c r="S26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>33</v>
-      </c>
-      <c r="J27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+      <c r="C27" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" t="s">
+        <v>25</v>
+      </c>
+      <c r="K27" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" t="s">
+        <v>27</v>
+      </c>
+      <c r="M27" t="s">
+        <v>107</v>
+      </c>
+      <c r="N27" t="s">
+        <v>26</v>
+      </c>
+      <c r="O27" t="s">
+        <v>26</v>
+      </c>
+      <c r="P27" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>26</v>
+      </c>
+      <c r="R27" t="s">
+        <v>26</v>
+      </c>
+      <c r="S27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>34</v>
-      </c>
-      <c r="J28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+      <c r="C28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
+        <v>90</v>
+      </c>
+      <c r="F28" t="s">
+        <v>91</v>
+      </c>
+      <c r="G28" t="s">
+        <v>92</v>
+      </c>
+      <c r="H28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" t="s">
+        <v>93</v>
+      </c>
+      <c r="K28" t="s">
+        <v>94</v>
+      </c>
+      <c r="L28" t="s">
+        <v>27</v>
+      </c>
+      <c r="M28" t="s">
+        <v>110</v>
+      </c>
+      <c r="N28" t="s">
+        <v>26</v>
+      </c>
+      <c r="O28" t="s">
+        <v>26</v>
+      </c>
+      <c r="P28" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>26</v>
+      </c>
+      <c r="R28" t="s">
+        <v>26</v>
+      </c>
+      <c r="S28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>35</v>
-      </c>
-      <c r="J29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="C29" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>90</v>
+      </c>
+      <c r="F29" t="s">
+        <v>91</v>
+      </c>
+      <c r="G29" t="s">
+        <v>92</v>
+      </c>
+      <c r="H29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" t="s">
+        <v>93</v>
+      </c>
+      <c r="K29" t="s">
+        <v>94</v>
+      </c>
+      <c r="L29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M29" t="s">
+        <v>113</v>
+      </c>
+      <c r="N29" t="s">
+        <v>26</v>
+      </c>
+      <c r="O29" t="s">
+        <v>26</v>
+      </c>
+      <c r="P29" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>26</v>
+      </c>
+      <c r="R29" t="s">
+        <v>26</v>
+      </c>
+      <c r="S29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>36</v>
-      </c>
-      <c r="J30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+      <c r="C30" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" t="s">
+        <v>25</v>
+      </c>
+      <c r="K30" t="s">
+        <v>26</v>
+      </c>
+      <c r="L30" t="s">
+        <v>27</v>
+      </c>
+      <c r="M30" t="s">
+        <v>116</v>
+      </c>
+      <c r="N30" t="s">
+        <v>26</v>
+      </c>
+      <c r="O30" t="s">
+        <v>26</v>
+      </c>
+      <c r="P30" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>26</v>
+      </c>
+      <c r="R30" t="s">
+        <v>26</v>
+      </c>
+      <c r="S30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>37</v>
-      </c>
-      <c r="J31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+      <c r="C31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
+        <v>90</v>
+      </c>
+      <c r="F31" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" t="s">
+        <v>92</v>
+      </c>
+      <c r="H31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" t="s">
+        <v>93</v>
+      </c>
+      <c r="K31" t="s">
+        <v>94</v>
+      </c>
+      <c r="L31" t="s">
+        <v>27</v>
+      </c>
+      <c r="M31" t="s">
+        <v>119</v>
+      </c>
+      <c r="N31" t="s">
+        <v>26</v>
+      </c>
+      <c r="O31" t="s">
+        <v>26</v>
+      </c>
+      <c r="P31" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>26</v>
+      </c>
+      <c r="R31" t="s">
+        <v>26</v>
+      </c>
+      <c r="S31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>38</v>
-      </c>
-      <c r="J32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+      <c r="C32" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>90</v>
+      </c>
+      <c r="F32" t="s">
+        <v>91</v>
+      </c>
+      <c r="G32" t="s">
+        <v>92</v>
+      </c>
+      <c r="H32" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" t="s">
+        <v>93</v>
+      </c>
+      <c r="K32" t="s">
+        <v>94</v>
+      </c>
+      <c r="L32" t="s">
+        <v>27</v>
+      </c>
+      <c r="M32" t="s">
+        <v>122</v>
+      </c>
+      <c r="N32" t="s">
+        <v>26</v>
+      </c>
+      <c r="O32" t="s">
+        <v>26</v>
+      </c>
+      <c r="P32" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>26</v>
+      </c>
+      <c r="R32" t="s">
+        <v>26</v>
+      </c>
+      <c r="S32" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>39</v>
-      </c>
-      <c r="J33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="C33" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33" t="s">
+        <v>90</v>
+      </c>
+      <c r="F33" t="s">
+        <v>91</v>
+      </c>
+      <c r="G33" t="s">
+        <v>92</v>
+      </c>
+      <c r="H33" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" t="s">
+        <v>93</v>
+      </c>
+      <c r="K33" t="s">
+        <v>94</v>
+      </c>
+      <c r="L33" t="s">
+        <v>27</v>
+      </c>
+      <c r="M33" t="s">
+        <v>125</v>
+      </c>
+      <c r="N33" t="s">
+        <v>26</v>
+      </c>
+      <c r="O33" t="s">
+        <v>26</v>
+      </c>
+      <c r="P33" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>26</v>
+      </c>
+      <c r="R33" t="s">
+        <v>26</v>
+      </c>
+      <c r="S33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>40</v>
-      </c>
-      <c r="J34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+      <c r="C34" t="s">
+        <v>127</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34" t="s">
+        <v>90</v>
+      </c>
+      <c r="F34" t="s">
+        <v>91</v>
+      </c>
+      <c r="G34" t="s">
+        <v>92</v>
+      </c>
+      <c r="H34" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" t="s">
+        <v>93</v>
+      </c>
+      <c r="K34" t="s">
+        <v>94</v>
+      </c>
+      <c r="L34" t="s">
+        <v>27</v>
+      </c>
+      <c r="M34" t="s">
+        <v>128</v>
+      </c>
+      <c r="N34" t="s">
+        <v>26</v>
+      </c>
+      <c r="O34" t="s">
+        <v>26</v>
+      </c>
+      <c r="P34" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>26</v>
+      </c>
+      <c r="R34" t="s">
+        <v>26</v>
+      </c>
+      <c r="S34" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>41</v>
-      </c>
-      <c r="J35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+      <c r="C35" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
+        <v>21</v>
+      </c>
+      <c r="F35" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" t="s">
+        <v>25</v>
+      </c>
+      <c r="K35" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" t="s">
+        <v>27</v>
+      </c>
+      <c r="M35" t="s">
+        <v>131</v>
+      </c>
+      <c r="N35" t="s">
+        <v>26</v>
+      </c>
+      <c r="O35" t="s">
+        <v>26</v>
+      </c>
+      <c r="P35" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>26</v>
+      </c>
+      <c r="R35" t="s">
+        <v>26</v>
+      </c>
+      <c r="S35" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>42</v>
-      </c>
-      <c r="J36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+      <c r="C36" t="s">
+        <v>133</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>90</v>
+      </c>
+      <c r="F36" t="s">
+        <v>91</v>
+      </c>
+      <c r="G36" t="s">
+        <v>92</v>
+      </c>
+      <c r="H36" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" t="s">
+        <v>93</v>
+      </c>
+      <c r="K36" t="s">
+        <v>94</v>
+      </c>
+      <c r="L36" t="s">
+        <v>27</v>
+      </c>
+      <c r="M36" t="s">
+        <v>134</v>
+      </c>
+      <c r="N36" t="s">
+        <v>26</v>
+      </c>
+      <c r="O36" t="s">
+        <v>26</v>
+      </c>
+      <c r="P36" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>26</v>
+      </c>
+      <c r="R36" t="s">
+        <v>26</v>
+      </c>
+      <c r="S36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>43</v>
-      </c>
-      <c r="J37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+      <c r="C37" t="s">
+        <v>136</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F37" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37" t="s">
+        <v>25</v>
+      </c>
+      <c r="K37" t="s">
+        <v>26</v>
+      </c>
+      <c r="L37" t="s">
+        <v>27</v>
+      </c>
+      <c r="M37" t="s">
+        <v>137</v>
+      </c>
+      <c r="N37" t="s">
+        <v>26</v>
+      </c>
+      <c r="O37" t="s">
+        <v>26</v>
+      </c>
+      <c r="P37" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>26</v>
+      </c>
+      <c r="R37" t="s">
+        <v>26</v>
+      </c>
+      <c r="S37" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>44</v>
-      </c>
-      <c r="J38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+      <c r="C38" t="s">
+        <v>139</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38" t="s">
+        <v>90</v>
+      </c>
+      <c r="F38" t="s">
+        <v>91</v>
+      </c>
+      <c r="G38" t="s">
+        <v>92</v>
+      </c>
+      <c r="H38" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38" t="s">
+        <v>93</v>
+      </c>
+      <c r="K38" t="s">
+        <v>94</v>
+      </c>
+      <c r="L38" t="s">
+        <v>27</v>
+      </c>
+      <c r="M38" t="s">
+        <v>140</v>
+      </c>
+      <c r="N38" t="s">
+        <v>26</v>
+      </c>
+      <c r="O38" t="s">
+        <v>26</v>
+      </c>
+      <c r="P38" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>26</v>
+      </c>
+      <c r="R38" t="s">
+        <v>26</v>
+      </c>
+      <c r="S38" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>45</v>
-      </c>
-      <c r="J39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+      <c r="C39" t="s">
+        <v>142</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>90</v>
+      </c>
+      <c r="F39" t="s">
+        <v>91</v>
+      </c>
+      <c r="G39" t="s">
+        <v>92</v>
+      </c>
+      <c r="H39" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39" t="s">
+        <v>93</v>
+      </c>
+      <c r="K39" t="s">
+        <v>94</v>
+      </c>
+      <c r="L39" t="s">
+        <v>27</v>
+      </c>
+      <c r="M39" t="s">
+        <v>143</v>
+      </c>
+      <c r="N39" t="s">
+        <v>26</v>
+      </c>
+      <c r="O39" t="s">
+        <v>26</v>
+      </c>
+      <c r="P39" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>26</v>
+      </c>
+      <c r="R39" t="s">
+        <v>26</v>
+      </c>
+      <c r="S39" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>46</v>
-      </c>
-      <c r="J40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+      <c r="C40" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F40" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" t="s">
+        <v>23</v>
+      </c>
+      <c r="H40" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40" t="s">
+        <v>25</v>
+      </c>
+      <c r="K40" t="s">
+        <v>26</v>
+      </c>
+      <c r="L40" t="s">
+        <v>27</v>
+      </c>
+      <c r="M40" t="s">
+        <v>146</v>
+      </c>
+      <c r="N40" t="s">
+        <v>26</v>
+      </c>
+      <c r="O40" t="s">
+        <v>26</v>
+      </c>
+      <c r="P40" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>26</v>
+      </c>
+      <c r="R40" t="s">
+        <v>26</v>
+      </c>
+      <c r="S40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>47</v>
-      </c>
-      <c r="J41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+      <c r="C41" t="s">
+        <v>148</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41" t="s">
+        <v>21</v>
+      </c>
+      <c r="F41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41" t="s">
+        <v>25</v>
+      </c>
+      <c r="K41" t="s">
+        <v>26</v>
+      </c>
+      <c r="L41" t="s">
+        <v>27</v>
+      </c>
+      <c r="M41" t="s">
+        <v>149</v>
+      </c>
+      <c r="N41" t="s">
+        <v>26</v>
+      </c>
+      <c r="O41" t="s">
+        <v>26</v>
+      </c>
+      <c r="P41" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>26</v>
+      </c>
+      <c r="R41" t="s">
+        <v>26</v>
+      </c>
+      <c r="S41" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>48</v>
-      </c>
-      <c r="J42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+      <c r="C42" t="s">
+        <v>151</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42" t="s">
+        <v>21</v>
+      </c>
+      <c r="F42" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H42" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K42" t="s">
+        <v>26</v>
+      </c>
+      <c r="L42" t="s">
+        <v>27</v>
+      </c>
+      <c r="M42" t="s">
+        <v>152</v>
+      </c>
+      <c r="N42" t="s">
+        <v>26</v>
+      </c>
+      <c r="O42" t="s">
+        <v>26</v>
+      </c>
+      <c r="P42" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>26</v>
+      </c>
+      <c r="R42" t="s">
+        <v>26</v>
+      </c>
+      <c r="S42" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>49</v>
-      </c>
-      <c r="J43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+      <c r="C43" t="s">
+        <v>154</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
+        <v>90</v>
+      </c>
+      <c r="F43" t="s">
+        <v>91</v>
+      </c>
+      <c r="G43" t="s">
+        <v>92</v>
+      </c>
+      <c r="H43" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43" t="s">
+        <v>93</v>
+      </c>
+      <c r="K43" t="s">
+        <v>94</v>
+      </c>
+      <c r="L43" t="s">
+        <v>27</v>
+      </c>
+      <c r="M43" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" t="s">
+        <v>26</v>
+      </c>
+      <c r="O43" t="s">
+        <v>26</v>
+      </c>
+      <c r="P43" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>26</v>
+      </c>
+      <c r="R43" t="s">
+        <v>26</v>
+      </c>
+      <c r="S43" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>50</v>
-      </c>
-      <c r="J44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+      <c r="C44" t="s">
+        <v>156</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44" t="s">
+        <v>90</v>
+      </c>
+      <c r="F44" t="s">
+        <v>91</v>
+      </c>
+      <c r="G44" t="s">
+        <v>92</v>
+      </c>
+      <c r="H44" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44" t="s">
+        <v>93</v>
+      </c>
+      <c r="K44" t="s">
+        <v>94</v>
+      </c>
+      <c r="L44" t="s">
+        <v>27</v>
+      </c>
+      <c r="M44" t="s">
+        <v>157</v>
+      </c>
+      <c r="N44" t="s">
+        <v>26</v>
+      </c>
+      <c r="O44" t="s">
+        <v>26</v>
+      </c>
+      <c r="P44" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>26</v>
+      </c>
+      <c r="R44" t="s">
+        <v>26</v>
+      </c>
+      <c r="S44" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>51</v>
-      </c>
-      <c r="J45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+      <c r="C45" t="s">
+        <v>159</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45" t="s">
+        <v>21</v>
+      </c>
+      <c r="F45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" t="s">
+        <v>23</v>
+      </c>
+      <c r="H45" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45" t="s">
+        <v>25</v>
+      </c>
+      <c r="K45" t="s">
+        <v>26</v>
+      </c>
+      <c r="L45" t="s">
+        <v>27</v>
+      </c>
+      <c r="M45" t="s">
+        <v>160</v>
+      </c>
+      <c r="N45" t="s">
+        <v>26</v>
+      </c>
+      <c r="O45" t="s">
+        <v>26</v>
+      </c>
+      <c r="P45" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>26</v>
+      </c>
+      <c r="R45" t="s">
+        <v>26</v>
+      </c>
+      <c r="S45" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>52</v>
-      </c>
-      <c r="J46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+      <c r="C46" t="s">
+        <v>162</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F46" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" t="s">
+        <v>24</v>
+      </c>
+      <c r="I46" t="s">
+        <v>25</v>
+      </c>
+      <c r="K46" t="s">
+        <v>26</v>
+      </c>
+      <c r="L46" t="s">
+        <v>27</v>
+      </c>
+      <c r="M46" t="s">
+        <v>163</v>
+      </c>
+      <c r="N46" t="s">
+        <v>26</v>
+      </c>
+      <c r="O46" t="s">
+        <v>26</v>
+      </c>
+      <c r="P46" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>26</v>
+      </c>
+      <c r="R46" t="s">
+        <v>26</v>
+      </c>
+      <c r="S46" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>53</v>
-      </c>
-      <c r="J47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+      <c r="C47" t="s">
+        <v>165</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47" t="s">
+        <v>21</v>
+      </c>
+      <c r="F47" t="s">
+        <v>22</v>
+      </c>
+      <c r="G47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K47" t="s">
+        <v>26</v>
+      </c>
+      <c r="L47" t="s">
+        <v>27</v>
+      </c>
+      <c r="M47" t="s">
+        <v>166</v>
+      </c>
+      <c r="N47" t="s">
+        <v>26</v>
+      </c>
+      <c r="O47" t="s">
+        <v>26</v>
+      </c>
+      <c r="P47" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>26</v>
+      </c>
+      <c r="R47" t="s">
+        <v>26</v>
+      </c>
+      <c r="S47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>54</v>
-      </c>
-      <c r="J48">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <dataValidations count="8">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="중복된 ID (RowName Error)" error="이미 존재하는 ID입니다!_x000a__x000a_RowName(행 이름)은 고유해야 합니다._x000a_(같은 이름을 두 번 쓸 수 없습니다.)" sqref="A1:A1048576">
-      <formula1>COUNTIF($A:$A, A1) &lt;= 1</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류" error="음수(-)와 0은 입력할 수 없습니다. 0 보다 큰 숫자를 입력해주세요." sqref="E2:E1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류(Range)" error="공격 사거리는 0보다 작을 수 없습니다._x000a_(예: 100 = 1미터)" sqref="F1:F1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류 (Speed)" error="속도는 0보다 작을 수 없습니다._x000a_언리얼 단위(cm/s)입니다._x000a_(예: 100 = 1미터, 600 = 달리기 속도)" sqref="L1:L1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="최소 체력 오류" error="최대 체력(MaxHP)은 최소 1 이상이어야 합니다._x000a_0을 입력하면 유닛이 생성되자마자 죽습니다!" sqref="H1:H1048576">
-      <formula1>1</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="스탯 입력 오류" error="기본 스탯은 음수(-)일 수 없습니다._x000a_0 이상의 값을 입력해주세요." sqref="I1:K1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="확률 범위 오류 (0~1)" error="확률은 0.0 ~ 1.0 사이의 값만 가능합니다._x000a__x000a_[올바른 예시]_x000a_- 10% -&gt; 0.1 입력_x000a_- 50% -&gt; 0.5 입력_x000a_- 100% -&gt; 1.0 입력" sqref="M1:M1048576">
-      <formula1>0</formula1>
-      <formula2>1</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="단위 확인 (Cooldown)" error="쿨타임은 0보다 작을 수 없습니다._x000a__x000a_※ 단위: 초 (Seconds)_x000a_- 1분 = '60' 입력_x000a_- 0.5초 = '0.5' 입력_x000a_- 쿨타임 없음 = '0' 입력_x000a__x000a_밀리초(ms) 단위가 아닙니다! 다시 확인해주세요." sqref="G2:G1048576">
-      <formula1>0</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>Tags!$A$1:$A$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>Tags!$B$1:$B$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>C2:C1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>Tags!$C$1:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>D2:D1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.25" customWidth="1"/>
-    <col min="2" max="2" width="17.5" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
+        <v>167</v>
+      </c>
+      <c r="C48" t="s">
+        <v>168</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48" t="s">
+        <v>21</v>
+      </c>
+      <c r="F48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G48" t="s">
+        <v>23</v>
+      </c>
+      <c r="H48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I48" t="s">
+        <v>25</v>
+      </c>
+      <c r="K48" t="s">
+        <v>26</v>
+      </c>
+      <c r="L48" t="s">
+        <v>27</v>
+      </c>
+      <c r="M48" t="s">
+        <v>169</v>
+      </c>
+      <c r="N48" t="s">
+        <v>26</v>
+      </c>
+      <c r="O48" t="s">
+        <v>26</v>
+      </c>
+      <c r="P48" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>26</v>
+      </c>
+      <c r="R48" t="s">
+        <v>26</v>
+      </c>
+      <c r="S48" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/EnemyAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/EnemyAssets_Master.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="165">
   <si>
     <t>---</t>
   </si>
@@ -289,21 +289,6 @@
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Jellyfish.Icon_Jellyfish</t>
-  </si>
-  <si>
-    <t>/Script/Engine.BlueprintGeneratedClass'/Game/Test/KMJ/AI/BP_MyAIController_Range.BP_MyAIController_Range_C'</t>
-  </si>
-  <si>
-    <t>/Game/Test/KMJ/AI/BT_Monster_Ranged.BT_Monster_Ranged</t>
-  </si>
-  <si>
-    <t>/Game/Test/KMJ/AI/BB_Monster_Ranged.BB_Monster_Ranged</t>
-  </si>
-  <si>
-    <t>/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_RangeBasicAttack.GA_RangeBasicAttack_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.BlueprintGeneratedClass'/Game/Test/YSM/BP_FireBall.BP_FireBall_C'</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Jellyfish/SKM_JellyFish.SKM_JellyFish</t>
@@ -1572,22 +1557,22 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
         <v>27</v>
@@ -1678,22 +1663,22 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H5" t="s">
         <v>24</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K5" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L5" t="s">
         <v>27</v>
@@ -1731,22 +1716,22 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H6" t="s">
         <v>24</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K6" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L6" t="s">
         <v>27</v>
@@ -1784,22 +1769,22 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H7" t="s">
         <v>24</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L7" t="s">
         <v>27</v>
@@ -1890,22 +1875,22 @@
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
         <v>24</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K9" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L9" t="s">
         <v>27</v>
@@ -1996,22 +1981,22 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G11" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H11" t="s">
         <v>24</v>
       </c>
       <c r="I11" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K11" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L11" t="s">
         <v>27</v>
@@ -2155,22 +2140,22 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F14" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G14" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H14" t="s">
         <v>24</v>
       </c>
       <c r="I14" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K14" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L14" t="s">
         <v>27</v>
@@ -2473,22 +2458,22 @@
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F20" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G20" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H20" t="s">
         <v>24</v>
       </c>
       <c r="I20" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K20" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L20" t="s">
         <v>27</v>
@@ -2526,22 +2511,22 @@
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F21" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G21" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H21" t="s">
         <v>24</v>
       </c>
       <c r="I21" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K21" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L21" t="s">
         <v>27</v>
@@ -2653,7 +2638,7 @@
         <v>27</v>
       </c>
       <c r="M23" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N23" t="s">
         <v>26</v>
@@ -2676,37 +2661,37 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D24">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F24" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G24" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H24" t="s">
         <v>24</v>
       </c>
       <c r="I24" t="s">
+        <v>25</v>
+      </c>
+      <c r="K24" t="s">
+        <v>26</v>
+      </c>
+      <c r="L24" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" t="s">
         <v>93</v>
-      </c>
-      <c r="K24" t="s">
-        <v>94</v>
-      </c>
-      <c r="L24" t="s">
-        <v>27</v>
-      </c>
-      <c r="M24" t="s">
-        <v>98</v>
       </c>
       <c r="N24" t="s">
         <v>26</v>
@@ -2729,10 +2714,10 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -2759,7 +2744,7 @@
         <v>27</v>
       </c>
       <c r="M25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="N25" t="s">
         <v>26</v>
@@ -2782,37 +2767,37 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F26" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G26" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H26" t="s">
         <v>24</v>
       </c>
       <c r="I26" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K26" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L26" t="s">
         <v>27</v>
       </c>
       <c r="M26" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="N26" t="s">
         <v>26</v>
@@ -2835,10 +2820,10 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -2865,7 +2850,7 @@
         <v>27</v>
       </c>
       <c r="M27" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="N27" t="s">
         <v>26</v>
@@ -2888,37 +2873,37 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F28" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G28" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H28" t="s">
         <v>24</v>
       </c>
       <c r="I28" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K28" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L28" t="s">
         <v>27</v>
       </c>
       <c r="M28" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="N28" t="s">
         <v>26</v>
@@ -2941,37 +2926,37 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F29" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G29" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H29" t="s">
         <v>24</v>
       </c>
       <c r="I29" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K29" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L29" t="s">
         <v>27</v>
       </c>
       <c r="M29" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N29" t="s">
         <v>26</v>
@@ -2994,10 +2979,10 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -3024,7 +3009,7 @@
         <v>27</v>
       </c>
       <c r="M30" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="N30" t="s">
         <v>26</v>
@@ -3047,37 +3032,37 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F31" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G31" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H31" t="s">
         <v>24</v>
       </c>
       <c r="I31" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K31" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L31" t="s">
         <v>27</v>
       </c>
       <c r="M31" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="N31" t="s">
         <v>26</v>
@@ -3100,37 +3085,37 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F32" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G32" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H32" t="s">
         <v>24</v>
       </c>
       <c r="I32" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K32" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L32" t="s">
         <v>27</v>
       </c>
       <c r="M32" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="N32" t="s">
         <v>26</v>
@@ -3153,37 +3138,37 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H33" t="s">
         <v>24</v>
       </c>
       <c r="I33" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K33" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L33" t="s">
         <v>27</v>
       </c>
       <c r="M33" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="N33" t="s">
         <v>26</v>
@@ -3206,37 +3191,37 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C34" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F34" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G34" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H34" t="s">
         <v>24</v>
       </c>
       <c r="I34" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K34" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L34" t="s">
         <v>27</v>
       </c>
       <c r="M34" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="N34" t="s">
         <v>26</v>
@@ -3259,10 +3244,10 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -3289,7 +3274,7 @@
         <v>27</v>
       </c>
       <c r="M35" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="N35" t="s">
         <v>26</v>
@@ -3312,37 +3297,37 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D36">
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F36" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G36" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H36" t="s">
         <v>24</v>
       </c>
       <c r="I36" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K36" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L36" t="s">
         <v>27</v>
       </c>
       <c r="M36" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="N36" t="s">
         <v>26</v>
@@ -3365,10 +3350,10 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C37" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -3395,7 +3380,7 @@
         <v>27</v>
       </c>
       <c r="M37" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="N37" t="s">
         <v>26</v>
@@ -3418,37 +3403,37 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C38" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F38" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G38" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H38" t="s">
         <v>24</v>
       </c>
       <c r="I38" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K38" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L38" t="s">
         <v>27</v>
       </c>
       <c r="M38" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="N38" t="s">
         <v>26</v>
@@ -3471,37 +3456,37 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C39" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F39" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G39" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H39" t="s">
         <v>24</v>
       </c>
       <c r="I39" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K39" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L39" t="s">
         <v>27</v>
       </c>
       <c r="M39" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="N39" t="s">
         <v>26</v>
@@ -3524,10 +3509,10 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C40" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -3554,7 +3539,7 @@
         <v>27</v>
       </c>
       <c r="M40" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="N40" t="s">
         <v>26</v>
@@ -3577,10 +3562,10 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C41" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -3607,7 +3592,7 @@
         <v>27</v>
       </c>
       <c r="M41" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="N41" t="s">
         <v>26</v>
@@ -3630,10 +3615,10 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C42" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -3660,7 +3645,7 @@
         <v>27</v>
       </c>
       <c r="M42" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="N42" t="s">
         <v>26</v>
@@ -3683,31 +3668,31 @@
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C43" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D43">
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F43" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G43" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H43" t="s">
         <v>24</v>
       </c>
       <c r="I43" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K43" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L43" t="s">
         <v>27</v>
@@ -3736,37 +3721,37 @@
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C44" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D44">
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="F44" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="G44" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="H44" t="s">
         <v>24</v>
       </c>
       <c r="I44" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K44" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="L44" t="s">
         <v>27</v>
       </c>
       <c r="M44" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="N44" t="s">
         <v>26</v>
@@ -3789,10 +3774,10 @@
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C45" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -3819,7 +3804,7 @@
         <v>27</v>
       </c>
       <c r="M45" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="N45" t="s">
         <v>26</v>
@@ -3842,10 +3827,10 @@
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C46" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -3872,7 +3857,7 @@
         <v>27</v>
       </c>
       <c r="M46" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="N46" t="s">
         <v>26</v>
@@ -3895,10 +3880,10 @@
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C47" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -3925,7 +3910,7 @@
         <v>27</v>
       </c>
       <c r="M47" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="N47" t="s">
         <v>26</v>
@@ -3948,10 +3933,10 @@
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C48" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -3978,7 +3963,7 @@
         <v>27</v>
       </c>
       <c r="M48" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N48" t="s">
         <v>26</v>

--- a/DesignData/Excel_Masters/EnemyAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/EnemyAssets_Master.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\Unreal Projects\ProjectParadise\DesignData\Excel_Masters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealCpp\Paradise\DesignData\Excel_Masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15420" windowHeight="10965"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23745" windowHeight="7590"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyAssets" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="195">
   <si>
     <t>---</t>
   </si>
@@ -33,6 +33,12 @@
     <t>Scale</t>
   </si>
   <si>
+    <t>AttackMontage</t>
+  </si>
+  <si>
+    <t>SkillMontages</t>
+  </si>
+  <si>
     <t>AIController</t>
   </si>
   <si>
@@ -42,19 +48,16 @@
     <t>Blackboard</t>
   </si>
   <si>
-    <t>BasicAttackEffect</t>
-  </si>
-  <si>
-    <t>BasicAbility</t>
-  </si>
-  <si>
-    <t>SkillAbilities</t>
-  </si>
-  <si>
-    <t>ProjectileClass</t>
-  </si>
-  <si>
-    <t>BasicAttackEffectTag</t>
+    <t>BasicAttackSetup</t>
+  </si>
+  <si>
+    <t>SkillSetups</t>
+  </si>
+  <si>
+    <t>ActionFX</t>
+  </si>
+  <si>
+    <t>FactionTag</t>
   </si>
   <si>
     <t>SkeletalMesh</t>
@@ -63,19 +66,13 @@
     <t>AnimBlueprint</t>
   </si>
   <si>
-    <t>AttackMontage</t>
-  </si>
-  <si>
     <t>HitMontage</t>
   </si>
   <si>
     <t>DeathMontage</t>
   </si>
   <si>
-    <t>UnitFXData</t>
-  </si>
-  <si>
-    <t>HitReactionTag</t>
+    <t>ReactionFX</t>
   </si>
   <si>
     <t>Balrog</t>
@@ -84,6 +81,12 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Balrog_A.Icon_Balrog_A</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Enemy/Balrog/AM_Balrog_Attack.AM_Balrog_Attack</t>
+  </si>
+  <si>
+    <t>("/Game/Blueprints/Characters/Enemy/Balrog/AM_Balrog_Attack.AM_Balrog_Attack","/Game/Blueprints/Characters/Enemy/Balrog/AM_Balrog_Attack.AM_Balrog_Attack")</t>
+  </si>
+  <si>
     <t>/Script/Engine.BlueprintGeneratedClass'/Game/Test/KMJ/AI/BP_MyAIController.BP_MyAIController_C'</t>
   </si>
   <si>
@@ -93,81 +96,165 @@
     <t>/Game/Test/KMJ/AI/BB_Monster.BB_Monster</t>
   </si>
   <si>
-    <t>/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_MeleeBasicAttack.GA_MeleeBasicAttack_C'</t>
+    <t>(ActionFXData=None,BasicAttackTag=(TagName=""),SkillTag=(TagName=""))</t>
+  </si>
+  <si>
+    <t>(TagName="Unit.Faction.Enemy")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Balrog/SKM_Balrog.SKM_Balrog</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Balrog/ABP_Balrog.ABP_Balrog_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Balrog/AM_Balrog_Damage.AM_Balrog_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Balrog/AM_Balrog_Death.AM_Balrog_Death</t>
+  </si>
+  <si>
+    <t>(ReactionFXData=None,HitTag=(TagName=""),DeathTag=(TagName=""))</t>
+  </si>
+  <si>
+    <t>Bearking</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_BearKing.Icon_BearKing</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Bearking/AM_Bearking_Attack.AM_Bearking_Attack</t>
+  </si>
+  <si>
+    <t>("/Game/Blueprints/Characters/Enemy/Bearking/AM_Bearking_Attack.AM_Bearking_Attack","/Game/Blueprints/Characters/Enemy/Bearking/AM_Bearking_Attack.AM_Bearking_Attack")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Bearking/SKM_BearKing_A.SKM_BearKing_A</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Bearking/ABP_Bearking.ABP_Bearking_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Bearking/AM_Bearking_Damage.AM_Bearking_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Bearking/AM_Bearking_Dead.AM_Bearking_Dead</t>
+  </si>
+  <si>
+    <t>BombSpider</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_BombSpider.Icon_BombSpider</t>
   </si>
   <si>
     <t>None</t>
   </si>
   <si>
-    <t>(TagName="")</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Monster/Balrog/SKM_Balrog.SKM_Balrog</t>
-  </si>
-  <si>
-    <t>Bearking</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_BearKing.Icon_BearKing</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Monster/Bearking/SKM_BearKing_A.SKM_BearKing_A</t>
-  </si>
-  <si>
-    <t>BombSpider</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_BombSpider.Icon_BombSpider</t>
-  </si>
-  <si>
     <t>BronzeGear</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_BronzeGear.Icon_BronzeGear</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Enemy/BronzeGear/AM_BronzeGear_Attack.AM_BronzeGear_Attack</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Monster/BronzeGear/SKM_BronzeGear.SKM_BronzeGear</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/BronzeGear/ABP_BronzeGear.ABP_BronzeGear_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/BronzeGear/AM_BronzeGear_Damage.AM_BronzeGear_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/BronzeGear/AM_BronzeGear_Dead.AM_BronzeGear_Dead</t>
+  </si>
+  <si>
     <t>Cell</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Cell.Icon_Cell</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Boss_Cell.Icon_Boss_Cell</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Cell/AM_Cell_Attack.AM_Cell_Attack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Cell/SKM_Cell.SKM_Cell</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Cell/ABP_Cell.ABP_Cell_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Cell/AM_Cell_Damage.AM_Cell_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Cell/AM_Cell_Dead.AM_Cell_Dead</t>
+  </si>
+  <si>
     <t>Cursedmass</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Cursedmass.Icon_Cursedmass</t>
+    <t>/Game/External_Assets/Monster/Cursedmass/Material/T_Cursedmas_A_Ball.T_Cursedmas_A_Ball</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Cursedmass/AM_Cursedmass_Attack.AM_Cursedmass_Attack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Cursedmass/SKM_Cursedmass.SKM_Cursedmass</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Cursedmass/ABP_Cursedmass.ABP_Cursedmass_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Cursedmass/AM_Cursedmass_Damage.AM_Cursedmass_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Cursedmass/AM_Cursedmass_Dead.AM_Cursedmass_Dead</t>
+  </si>
+  <si>
     <t>DanceMakane</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_DanceMakane.Icon_DanceMakane</t>
+    <t>/Game/External_Assets/Monster/DanceMakane/Material/T_DanceMakane_Type_A.T_DanceMakane_Type_A</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/DanceMakane/AM_DanceMakane_Attack.AM_DanceMakane_Attack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/DanceMakane/SKM_DanceMakane.SKM_DanceMakane</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/DanceMakane/ABP_DanceMakane.ABP_DanceMakane_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/DanceMakane/AM_DanceMakane_Damage.AM_DanceMakane_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/DanceMakane/AM_DanceMakane_Death.AM_DanceMakane_Death</t>
+  </si>
+  <si>
     <t>Deatheye</t>
   </si>
   <si>
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_DeathEye.Icon_DeathEye</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Enemy/Deatheye/AM_Deatheye_Attack.AM_Deatheye_Attack</t>
+  </si>
+  <si>
     <t>/Game/External_Assets/Monster/Deatheye/SKM_Deatheye.SKM_Deatheye</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Deatheye/ABP_Deatheye.ABP_Deatheye_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Deatheye/AM_Deatheye_Damage.AM_Deatheye_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Deatheye/AM_Deatheye_Dead.AM_Deatheye_Dead</t>
+  </si>
+  <si>
     <t>DieS</t>
   </si>
   <si>
@@ -514,6 +601,10 @@
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Wolfron/SKM_wolfron_C.SKM_wolfron_C</t>
+  </si>
+  <si>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaBasicAttack.GA_AreaBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'",ProjectileClass=None)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1431,10 +1522,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S48"/>
+  <dimension ref="A1:R48"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1489,2499 +1580,2220 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>21</v>
       </c>
-      <c r="F2" t="s">
-        <v>22</v>
-      </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>194</v>
       </c>
       <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
         <v>27</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>28</v>
       </c>
-      <c r="N2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" t="s">
-        <v>26</v>
-      </c>
       <c r="P2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="R2" t="s">
-        <v>26</v>
-      </c>
-      <c r="S2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>194</v>
       </c>
       <c r="L3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="N3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="P3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="Q3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="R3" t="s">
-        <v>26</v>
-      </c>
-      <c r="S3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>194</v>
       </c>
       <c r="L4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M4" t="s">
         <v>26</v>
       </c>
       <c r="N4" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P4" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q4" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R4" t="s">
-        <v>26</v>
-      </c>
-      <c r="S4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J5" t="s">
+        <v>194</v>
       </c>
       <c r="L5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M5" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="N5" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="P5" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="Q5" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="R5" t="s">
-        <v>26</v>
-      </c>
-      <c r="S5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J6" t="s">
+        <v>194</v>
       </c>
       <c r="L6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M6" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="N6" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="O6" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="P6" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="Q6" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="R6" t="s">
-        <v>26</v>
-      </c>
-      <c r="S6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J7" t="s">
+        <v>194</v>
       </c>
       <c r="L7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="N7" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="O7" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="P7" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="Q7" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="R7" t="s">
-        <v>26</v>
-      </c>
-      <c r="S7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I8" t="s">
-        <v>25</v>
-      </c>
-      <c r="K8" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J8" t="s">
+        <v>194</v>
       </c>
       <c r="L8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M8" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N8" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="O8" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="P8" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="Q8" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="R8" t="s">
-        <v>26</v>
-      </c>
-      <c r="S8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I9" t="s">
-        <v>25</v>
-      </c>
-      <c r="K9" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J9" t="s">
+        <v>194</v>
       </c>
       <c r="L9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M9" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="N9" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="O9" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="P9" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="Q9" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="R9" t="s">
-        <v>26</v>
-      </c>
-      <c r="S9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I10" t="s">
-        <v>25</v>
-      </c>
-      <c r="K10" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J10" t="s">
+        <v>194</v>
       </c>
       <c r="L10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M10" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N10" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="O10" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P10" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q10" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R10" t="s">
-        <v>26</v>
-      </c>
-      <c r="S10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I11" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J11" t="s">
+        <v>194</v>
       </c>
       <c r="L11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M11" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N11" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="O11" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P11" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q11" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R11" t="s">
-        <v>26</v>
-      </c>
-      <c r="S11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I12" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J12" t="s">
+        <v>194</v>
       </c>
       <c r="L12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M12" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="N12" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="O12" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P12" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q12" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R12" t="s">
-        <v>26</v>
-      </c>
-      <c r="S12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I13" t="s">
-        <v>25</v>
-      </c>
-      <c r="K13" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J13" t="s">
+        <v>194</v>
       </c>
       <c r="L13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M13" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="N13" t="s">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="O13" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P13" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q13" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R13" t="s">
-        <v>26</v>
-      </c>
-      <c r="S13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I14" t="s">
-        <v>25</v>
-      </c>
-      <c r="K14" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J14" t="s">
+        <v>194</v>
       </c>
       <c r="L14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M14" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="N14" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="O14" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P14" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q14" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R14" t="s">
-        <v>26</v>
-      </c>
-      <c r="S14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I15" t="s">
-        <v>25</v>
-      </c>
-      <c r="K15" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J15" t="s">
+        <v>194</v>
       </c>
       <c r="L15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M15" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="N15" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="O15" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P15" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q15" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R15" t="s">
-        <v>26</v>
-      </c>
-      <c r="S15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I16" t="s">
-        <v>25</v>
-      </c>
-      <c r="K16" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J16" t="s">
+        <v>194</v>
       </c>
       <c r="L16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M16" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="N16" t="s">
-        <v>26</v>
+        <v>98</v>
       </c>
       <c r="O16" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P16" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q16" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R16" t="s">
-        <v>26</v>
-      </c>
-      <c r="S16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I17" t="s">
-        <v>25</v>
-      </c>
-      <c r="K17" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J17" t="s">
+        <v>194</v>
       </c>
       <c r="L17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M17" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="N17" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="O17" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P17" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q17" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R17" t="s">
-        <v>26</v>
-      </c>
-      <c r="S17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I18" t="s">
-        <v>25</v>
-      </c>
-      <c r="K18" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J18" t="s">
+        <v>194</v>
       </c>
       <c r="L18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M18" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="N18" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="O18" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P18" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q18" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R18" t="s">
-        <v>26</v>
-      </c>
-      <c r="S18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I19" t="s">
-        <v>25</v>
-      </c>
-      <c r="K19" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J19" t="s">
+        <v>194</v>
       </c>
       <c r="L19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M19" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="N19" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="O19" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P19" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q19" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R19" t="s">
-        <v>26</v>
-      </c>
-      <c r="S19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I20" t="s">
-        <v>25</v>
-      </c>
-      <c r="K20" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J20" t="s">
+        <v>194</v>
       </c>
       <c r="L20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M20" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="N20" t="s">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="O20" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P20" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q20" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R20" t="s">
-        <v>26</v>
-      </c>
-      <c r="S20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I21" t="s">
-        <v>25</v>
-      </c>
-      <c r="K21" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J21" t="s">
+        <v>194</v>
       </c>
       <c r="L21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M21" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="N21" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
       <c r="O21" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P21" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q21" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R21" t="s">
-        <v>26</v>
-      </c>
-      <c r="S21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I22" t="s">
-        <v>25</v>
-      </c>
-      <c r="K22" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J22" t="s">
+        <v>194</v>
       </c>
       <c r="L22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M22" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="N22" t="s">
-        <v>26</v>
+        <v>116</v>
       </c>
       <c r="O22" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P22" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q22" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R22" t="s">
-        <v>26</v>
-      </c>
-      <c r="S22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I23" t="s">
-        <v>25</v>
-      </c>
-      <c r="K23" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J23" t="s">
+        <v>194</v>
       </c>
       <c r="L23" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M23" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="N23" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="O23" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P23" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q23" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R23" t="s">
-        <v>26</v>
-      </c>
-      <c r="S23" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="D24">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I24" t="s">
-        <v>25</v>
-      </c>
-      <c r="K24" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J24" t="s">
+        <v>194</v>
       </c>
       <c r="L24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M24" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="N24" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="O24" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P24" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q24" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R24" t="s">
-        <v>26</v>
-      </c>
-      <c r="S24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I25" t="s">
-        <v>25</v>
-      </c>
-      <c r="K25" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J25" t="s">
+        <v>194</v>
       </c>
       <c r="L25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M25" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="N25" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="O25" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P25" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q25" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R25" t="s">
-        <v>26</v>
-      </c>
-      <c r="S25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I26" t="s">
-        <v>25</v>
-      </c>
-      <c r="K26" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J26" t="s">
+        <v>194</v>
       </c>
       <c r="L26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M26" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="N26" t="s">
-        <v>26</v>
+        <v>128</v>
       </c>
       <c r="O26" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P26" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q26" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R26" t="s">
-        <v>26</v>
-      </c>
-      <c r="S26" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I27" t="s">
-        <v>25</v>
-      </c>
-      <c r="K27" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J27" t="s">
+        <v>194</v>
       </c>
       <c r="L27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M27" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="N27" t="s">
-        <v>26</v>
+        <v>131</v>
       </c>
       <c r="O27" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P27" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q27" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R27" t="s">
-        <v>26</v>
-      </c>
-      <c r="S27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I28" t="s">
-        <v>25</v>
-      </c>
-      <c r="K28" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J28" t="s">
+        <v>194</v>
       </c>
       <c r="L28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M28" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="N28" t="s">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="O28" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P28" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q28" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R28" t="s">
-        <v>26</v>
-      </c>
-      <c r="S28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I29" t="s">
-        <v>25</v>
-      </c>
-      <c r="K29" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J29" t="s">
+        <v>194</v>
       </c>
       <c r="L29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M29" t="s">
-        <v>108</v>
+        <v>26</v>
       </c>
       <c r="N29" t="s">
-        <v>26</v>
+        <v>137</v>
       </c>
       <c r="O29" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P29" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q29" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R29" t="s">
-        <v>26</v>
-      </c>
-      <c r="S29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I30" t="s">
-        <v>25</v>
-      </c>
-      <c r="K30" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J30" t="s">
+        <v>194</v>
       </c>
       <c r="L30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M30" t="s">
-        <v>111</v>
+        <v>26</v>
       </c>
       <c r="N30" t="s">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="O30" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P30" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q30" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R30" t="s">
-        <v>26</v>
-      </c>
-      <c r="S30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="C31" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I31" t="s">
-        <v>25</v>
-      </c>
-      <c r="K31" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J31" t="s">
+        <v>194</v>
       </c>
       <c r="L31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M31" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="N31" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="O31" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P31" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q31" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R31" t="s">
-        <v>26</v>
-      </c>
-      <c r="S31" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="C32" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>21</v>
-      </c>
-      <c r="F32" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I32" t="s">
-        <v>25</v>
-      </c>
-      <c r="K32" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J32" t="s">
+        <v>194</v>
       </c>
       <c r="L32" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M32" t="s">
-        <v>117</v>
+        <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>26</v>
+        <v>146</v>
       </c>
       <c r="O32" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P32" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q32" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R32" t="s">
-        <v>26</v>
-      </c>
-      <c r="S32" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I33" t="s">
-        <v>25</v>
-      </c>
-      <c r="K33" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J33" t="s">
+        <v>194</v>
       </c>
       <c r="L33" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M33" t="s">
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>26</v>
+        <v>149</v>
       </c>
       <c r="O33" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P33" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q33" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R33" t="s">
-        <v>26</v>
-      </c>
-      <c r="S33" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="C34" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>21</v>
-      </c>
-      <c r="F34" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I34" t="s">
-        <v>25</v>
-      </c>
-      <c r="K34" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J34" t="s">
+        <v>194</v>
       </c>
       <c r="L34" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M34" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="N34" t="s">
-        <v>26</v>
+        <v>152</v>
       </c>
       <c r="O34" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P34" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q34" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R34" t="s">
-        <v>26</v>
-      </c>
-      <c r="S34" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
-      </c>
-      <c r="F35" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I35" t="s">
-        <v>25</v>
-      </c>
-      <c r="K35" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J35" t="s">
+        <v>194</v>
       </c>
       <c r="L35" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M35" t="s">
-        <v>126</v>
+        <v>26</v>
       </c>
       <c r="N35" t="s">
-        <v>26</v>
+        <v>155</v>
       </c>
       <c r="O35" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P35" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q35" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R35" t="s">
-        <v>26</v>
-      </c>
-      <c r="S35" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="C36" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="D36">
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>21</v>
-      </c>
-      <c r="F36" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I36" t="s">
-        <v>25</v>
-      </c>
-      <c r="K36" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J36" t="s">
+        <v>194</v>
       </c>
       <c r="L36" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M36" t="s">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="N36" t="s">
-        <v>26</v>
+        <v>158</v>
       </c>
       <c r="O36" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P36" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q36" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R36" t="s">
-        <v>26</v>
-      </c>
-      <c r="S36" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="C37" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>21</v>
-      </c>
-      <c r="F37" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I37" t="s">
-        <v>25</v>
-      </c>
-      <c r="K37" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J37" t="s">
+        <v>194</v>
       </c>
       <c r="L37" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M37" t="s">
-        <v>132</v>
+        <v>26</v>
       </c>
       <c r="N37" t="s">
-        <v>26</v>
+        <v>161</v>
       </c>
       <c r="O37" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P37" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q37" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R37" t="s">
-        <v>26</v>
-      </c>
-      <c r="S37" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>21</v>
-      </c>
-      <c r="F38" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I38" t="s">
-        <v>25</v>
-      </c>
-      <c r="K38" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J38" t="s">
+        <v>194</v>
       </c>
       <c r="L38" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M38" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="N38" t="s">
-        <v>26</v>
+        <v>164</v>
       </c>
       <c r="O38" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P38" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q38" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R38" t="s">
-        <v>26</v>
-      </c>
-      <c r="S38" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="C39" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>21</v>
-      </c>
-      <c r="F39" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I39" t="s">
-        <v>25</v>
-      </c>
-      <c r="K39" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J39" t="s">
+        <v>194</v>
       </c>
       <c r="L39" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M39" t="s">
-        <v>138</v>
+        <v>26</v>
       </c>
       <c r="N39" t="s">
-        <v>26</v>
+        <v>167</v>
       </c>
       <c r="O39" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P39" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q39" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R39" t="s">
-        <v>26</v>
-      </c>
-      <c r="S39" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="C40" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D40">
         <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>21</v>
-      </c>
-      <c r="F40" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I40" t="s">
-        <v>25</v>
-      </c>
-      <c r="K40" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J40" t="s">
+        <v>194</v>
       </c>
       <c r="L40" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M40" t="s">
-        <v>141</v>
+        <v>26</v>
       </c>
       <c r="N40" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="O40" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P40" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q40" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R40" t="s">
-        <v>26</v>
-      </c>
-      <c r="S40" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="C41" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="D41">
         <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>21</v>
-      </c>
-      <c r="F41" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I41" t="s">
-        <v>25</v>
-      </c>
-      <c r="K41" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J41" t="s">
+        <v>194</v>
       </c>
       <c r="L41" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M41" t="s">
-        <v>144</v>
+        <v>26</v>
       </c>
       <c r="N41" t="s">
-        <v>26</v>
+        <v>173</v>
       </c>
       <c r="O41" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P41" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q41" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R41" t="s">
-        <v>26</v>
-      </c>
-      <c r="S41" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="C42" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="E42" t="s">
-        <v>21</v>
-      </c>
-      <c r="F42" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I42" t="s">
-        <v>25</v>
-      </c>
-      <c r="K42" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J42" t="s">
+        <v>194</v>
       </c>
       <c r="L42" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M42" t="s">
-        <v>147</v>
+        <v>26</v>
       </c>
       <c r="N42" t="s">
-        <v>26</v>
+        <v>176</v>
       </c>
       <c r="O42" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P42" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q42" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R42" t="s">
-        <v>26</v>
-      </c>
-      <c r="S42" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="C43" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="D43">
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>21</v>
-      </c>
-      <c r="F43" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H43" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I43" t="s">
-        <v>25</v>
-      </c>
-      <c r="K43" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J43" t="s">
+        <v>194</v>
       </c>
       <c r="L43" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M43" t="s">
         <v>26</v>
       </c>
       <c r="N43" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="O43" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P43" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q43" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R43" t="s">
-        <v>26</v>
-      </c>
-      <c r="S43" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="C44" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="D44">
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>21</v>
-      </c>
-      <c r="F44" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I44" t="s">
-        <v>25</v>
-      </c>
-      <c r="K44" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J44" t="s">
+        <v>194</v>
       </c>
       <c r="L44" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M44" t="s">
-        <v>152</v>
+        <v>26</v>
       </c>
       <c r="N44" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="O44" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P44" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q44" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R44" t="s">
-        <v>26</v>
-      </c>
-      <c r="S44" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="C45" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="E45" t="s">
-        <v>21</v>
-      </c>
-      <c r="F45" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I45" t="s">
-        <v>25</v>
-      </c>
-      <c r="K45" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J45" t="s">
+        <v>194</v>
       </c>
       <c r="L45" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M45" t="s">
-        <v>155</v>
+        <v>26</v>
       </c>
       <c r="N45" t="s">
-        <v>26</v>
+        <v>184</v>
       </c>
       <c r="O45" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P45" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q45" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R45" t="s">
-        <v>26</v>
-      </c>
-      <c r="S45" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="C46" t="s">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="D46">
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>21</v>
-      </c>
-      <c r="F46" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I46" t="s">
-        <v>25</v>
-      </c>
-      <c r="K46" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J46" t="s">
+        <v>194</v>
       </c>
       <c r="L46" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M46" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="N46" t="s">
-        <v>26</v>
+        <v>187</v>
       </c>
       <c r="O46" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P46" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q46" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R46" t="s">
-        <v>26</v>
-      </c>
-      <c r="S46" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="C47" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="D47">
         <v>1</v>
       </c>
       <c r="E47" t="s">
-        <v>21</v>
-      </c>
-      <c r="F47" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I47" t="s">
-        <v>25</v>
-      </c>
-      <c r="K47" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J47" t="s">
+        <v>194</v>
       </c>
       <c r="L47" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M47" t="s">
-        <v>161</v>
+        <v>26</v>
       </c>
       <c r="N47" t="s">
-        <v>26</v>
+        <v>190</v>
       </c>
       <c r="O47" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P47" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q47" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R47" t="s">
-        <v>26</v>
-      </c>
-      <c r="S47" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="C48" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D48">
         <v>1</v>
       </c>
       <c r="E48" t="s">
-        <v>21</v>
-      </c>
-      <c r="F48" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I48" t="s">
-        <v>25</v>
-      </c>
-      <c r="K48" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="J48" t="s">
+        <v>194</v>
       </c>
       <c r="L48" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M48" t="s">
-        <v>164</v>
+        <v>26</v>
       </c>
       <c r="N48" t="s">
-        <v>26</v>
+        <v>193</v>
       </c>
       <c r="O48" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P48" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q48" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="R48" t="s">
-        <v>26</v>
-      </c>
-      <c r="S48" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/EnemyAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/EnemyAssets_Master.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="335">
   <si>
     <t>---</t>
   </si>
@@ -27,6 +27,9 @@
     <t>SkillEffectTags</t>
   </si>
   <si>
+    <t>SkillHitEffectTags</t>
+  </si>
+  <si>
     <t>Scale</t>
   </si>
   <si>
@@ -75,7 +78,10 @@
     <t>Balrog</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Boss/DA_EnemyFX_Boss_Balrog.DA_EnemyFX_Boss_Balrog",BasicAttackTag=(TagName="FX.Enemy.Boss.Balrog"),HitTag=(TagName="FX.Enemy.Boss.Balrog.Hit"),DeathTag=(TagName="FX.Enemy.Boss.Balrog.Death"))</t>
+    <t>((TagName="FX.Enemy.Boss.Balrog.Pattern1Hit"),(TagName="FX.Enemy.Boss.Balrog.Pattern2Hit"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Boss/DA_EnemyFX_Boss_Balrog.DA_EnemyFX_Boss_Balrog",BasicAttackTag=(TagName="FX.Enemy.Boss.Balrog"),BasicAttackHitTag=(TagName="FX.Enemy.Boss.Balrog.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Boss.Balrog.Hit"),DeathTag=(TagName="FX.Enemy.Boss.Balrog.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Balrog/AM_Balrog_BasicAttack.AM_Balrog_BasicAttack</t>
@@ -93,10 +99,10 @@
     <t>/Game/AI/BB/BB_Boss.BB_Boss</t>
   </si>
   <si>
-    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaBasicAttack.GA_AreaBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'",ProjectileClass=None)</t>
-  </si>
-  <si>
-    <t>((AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_BossProjectilePattern1.GA_BossProjectilePattern1_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'",ProjectileClass="/Script/Engine.BlueprintGeneratedClass'/Game/Blueprints/Object/Projectile/BP_Bullet.BP_Bullet_C'"),(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_BossProjectilePattern2.GA_BossProjectilePattern2_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'",ProjectileClass="/Script/Engine.BlueprintGeneratedClass'/Game/Blueprints/Object/Projectile/BP_Bullet.BP_Bullet_C'"))</t>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_AreaBasicAttack.GA_AreaBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass=None)</t>
+  </si>
+  <si>
+    <t>((AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_BossProjectilePattern1.GA_BossProjectilePattern1_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Skill.GE_Damage_Skill_C'",ProjectileClass="/Script/Engine.BlueprintGeneratedClass'/Game/Blueprints/Object/Projectile/BP_Bullet.BP_Bullet_C'"),(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_BossProjectilePattern2.GA_BossProjectilePattern2_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Skill.GE_Damage_Skill_C'",ProjectileClass="/Script/Engine.BlueprintGeneratedClass'/Game/Blueprints/Object/Projectile/BP_Bullet.BP_Bullet_C'"))</t>
   </si>
   <si>
     <t>(TagName="Unit.Faction.Enemy")</t>
@@ -120,7 +126,7 @@
     <t>Bearking</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Boss/DA_EnemyFX_Boss_Bearking.DA_EnemyFX_Boss_Bearking",BasicAttackTag=(TagName="FX.Enemy.Boss.Bearking"),HitTag=(TagName="FX.Enemy.Boss.Bearking.Hit"),DeathTag=(TagName="FX.Enemy.Boss.Bearking.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Boss/DA_EnemyFX_Boss_Bearking.DA_EnemyFX_Boss_Bearking",BasicAttackTag=(TagName="FX.Enemy.Boss.Bearking"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Boss.Bearking.Hit"),DeathTag=(TagName="FX.Enemy.Boss.Bearking.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Bearking/AM_Bearking_BasicAttack.AM_Bearking_BasicAttack</t>
@@ -129,7 +135,7 @@
     <t>("/Game/Blueprints/Characters/Enemy/Bearking/AM_Bearking_Pattern1.AM_Bearking_Pattern1","/Game/Blueprints/Characters/Enemy/Bearking/AM_Bearking_Pattern2.AM_Bearking_Pattern2")</t>
   </si>
   <si>
-    <t>((AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_BossAreaPattern1.GA_BossAreaPattern1_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'",ProjectileClass=None),(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_BossAreaPattern2.GA_BossAreaPattern2_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'",ProjectileClass=None))</t>
+    <t>((AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_BossAreaPattern1.GA_BossAreaPattern1_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Skill.GE_Damage_Skill_C'",ProjectileClass=None),(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_BossAreaPattern2.GA_BossAreaPattern2_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Skill.GE_Damage_Skill_C'",ProjectileClass=None))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Bearking/SKM_BearKing_A.SKM_BearKing_A</t>
@@ -150,7 +156,7 @@
     <t>BronzeGear</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_BronzeGear.DA_EnemyFX_Common_BronzeGear",BasicAttackTag=(TagName="FX.Enemy.Common.BronzeGear"),HitTag=(TagName="FX.Enemy.Common.BronzeGear.Hit"),DeathTag=(TagName="FX.Enemy.Common.BronzeGear.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_BronzeGear.DA_EnemyFX_Common_BronzeGear",BasicAttackTag=(TagName="FX.Enemy.Common.BronzeGear"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.BronzeGear.Hit"),DeathTag=(TagName="FX.Enemy.Common.BronzeGear.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/BronzeGear/AM_BronzeGear_BasicAttack.AM_BronzeGear_BasicAttack</t>
@@ -183,7 +189,7 @@
     <t>Cell</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Cell.DA_EnemyFX_Common_Cell",BasicAttackTag=(TagName="FX.Enemy.Common.Cell"),HitTag=(TagName="FX.Enemy.Common.Cell.Hit"),DeathTag=(TagName="FX.Enemy.Common.Cell.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Cell.DA_EnemyFX_Common_Cell",BasicAttackTag=(TagName="FX.Enemy.Common.Cell"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Cell.Hit"),DeathTag=(TagName="FX.Enemy.Common.Cell.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Cell/AM_Cell_BasicAttack.AM_Cell_BasicAttack</t>
@@ -207,7 +213,7 @@
     <t>Cursedmass</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Cursedmass.DA_EnemyFX_Common_Cursedmass",BasicAttackTag=(TagName="FX.Enemy.Common.Cursedmass"),HitTag=(TagName="FX.Enemy.Common.Cursedmass.Hit"),DeathTag=(TagName="FX.Enemy.Common.Cursedmass.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Cursedmass.DA_EnemyFX_Common_Cursedmass",BasicAttackTag=(TagName="FX.Enemy.Common.Cursedmass"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Cursedmass.Hit"),DeathTag=(TagName="FX.Enemy.Common.Cursedmass.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Cursedmass/AM_Cursedmass_BasicAttack.AM_Cursedmass_BasicAttack</t>
@@ -231,7 +237,7 @@
     <t>DanceMakane</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_DanceMakane.DA_EnemyFX_Common_DanceMakane",BasicAttackTag=(TagName="FX.Enemy.Common.DanceMakane"),HitTag=(TagName="FX.Enemy.Common.DanceMakane.Hit"),DeathTag=(TagName="FX.Enemy.Common.DanceMakane.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_DanceMakane.DA_EnemyFX_Common_DanceMakane",BasicAttackTag=(TagName="FX.Enemy.Common.DanceMakane"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.DanceMakane.Hit"),DeathTag=(TagName="FX.Enemy.Common.DanceMakane.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/DanceMakane/AM_DanceMakane_BasicAttack.AM_DanceMakane_BasicAttack</t>
@@ -255,13 +261,13 @@
     <t>Deatheye</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Deatheye.DA_EnemyFX_Common_Deatheye",BasicAttackTag=(TagName="FX.Enemy.Common.Deatheye"),HitTag=(TagName="FX.Enemy.Common.Deatheye.Hit"),DeathTag=(TagName="FX.Enemy.Common.Deatheye.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Deatheye.DA_EnemyFX_Common_Deatheye",BasicAttackTag=(TagName="FX.Enemy.Common.Deatheye"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Deatheye.Hit"),DeathTag=(TagName="FX.Enemy.Common.Deatheye.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Deatheye/AM_Deatheye_BasicAttack.AM_Deatheye_BasicAttack</t>
   </si>
   <si>
-    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileBasicAttack.GA_ProjectileBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'",ProjectileClass=None)</t>
+    <t>(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_ProjectileBasicAttack.GA_ProjectileBasicAttack_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass=None)</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Deatheye/SKM_Deatheye.SKM_Deatheye</t>
@@ -282,7 +288,7 @@
     <t>DieS</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_DieS.DA_EnemyFX_Common_DieS",BasicAttackTag=(TagName="FX.Enemy.Common.DieS"),HitTag=(TagName="FX.Enemy.Common.DieS.Hit"),DeathTag=(TagName="FX.Enemy.Common.DieS.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_DieS.DA_EnemyFX_Common_DieS",BasicAttackTag=(TagName="FX.Enemy.Common.DieS"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.DieS.Hit"),DeathTag=(TagName="FX.Enemy.Common.DieS.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Dies/AM_DieS_BasicAttack.AM_DieS_BasicAttack</t>
@@ -294,30 +300,30 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_DieS.Icon_DieS</t>
   </si>
   <si>
+    <t>/Game/Blueprints/Characters/Enemy/Dies/AM_DieS_Damaged.AM_DieS_Damaged</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Dies/AM_DieS_Dead.AM_DieS_Dead</t>
+  </si>
+  <si>
+    <t>DoctorMacaron</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_DoctorMacaron.DA_EnemyFX_Common_DoctorMacaron",BasicAttackTag=(TagName="FX.Enemy.Common.DoctorMacaron"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.DoctorMacaron.Hit"),DeathTag=(TagName="FX.Enemy.Common.DoctorMacaron.Death"))</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/DoctorMacaron/AM_DoctorMacaron_BasicAttack.AM_DoctorMacaron_BasicAttack</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/DoctorMacaron/SKM_DoctorMacaron.SKM_DoctorMacaron</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_DoctorMacaron.Icon_DoctorMacaron</t>
+  </si>
+  <si>
     <t>None</t>
   </si>
   <si>
-    <t>/Game/Blueprints/Characters/Enemy/Dies/AM_DieS_Damaged.AM_DieS_Damaged</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Enemy/Dies/AM_DieS_Dead.AM_DieS_Dead</t>
-  </si>
-  <si>
-    <t>DoctorMacaron</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_DoctorMacaron.DA_EnemyFX_Common_DoctorMacaron",BasicAttackTag=(TagName="FX.Enemy.Common.DoctorMacaron"),HitTag=(TagName="FX.Enemy.Common.DoctorMacaron.Hit"),DeathTag=(TagName="FX.Enemy.Common.DoctorMacaron.Death"))</t>
-  </si>
-  <si>
-    <t>/Game/Blueprints/Characters/Enemy/DoctorMacaron/AM_DoctorMacaron_BasicAttack.AM_DoctorMacaron_BasicAttack</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/Monster/DoctorMacaron/SKM_DoctorMacaron.SKM_DoctorMacaron</t>
-  </si>
-  <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_DoctorMacaron.Icon_DoctorMacaron</t>
-  </si>
-  <si>
     <t>/Game/Blueprints/Characters/Enemy/DoctorMacaron/AM_DoctorMacaron_Damaged.AM_DoctorMacaron_Damaged</t>
   </si>
   <si>
@@ -327,7 +333,7 @@
     <t>Famine</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Famine.DA_EnemyFX_Common_Famine",BasicAttackTag=(TagName="FX.Enemy.Common.Famine"),HitTag=(TagName="FX.Enemy.Common.Famine.Hit"),DeathTag=(TagName="FX.Enemy.Common.Famine.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Famine.DA_EnemyFX_Common_Famine",BasicAttackTag=(TagName="FX.Enemy.Common.Famine"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Famine.Hit"),DeathTag=(TagName="FX.Enemy.Common.Famine.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Famine/AM_Famine_BasicAttack.AM_Famine_BasicAttack</t>
@@ -348,7 +354,7 @@
     <t>FelicisMachine</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_FelicisMachine.DA_EnemyFX_Common_FelicisMachine",BasicAttackTag=(TagName="FX.Enemy.Common.FelicisMachine"),HitTag=(TagName="FX.Enemy.Common.FelicisMachine.Hit"),DeathTag=(TagName="FX.Enemy.Common.FelicisMachine.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_FelicisMachine.DA_EnemyFX_Common_FelicisMachine",BasicAttackTag=(TagName="FX.Enemy.Common.FelicisMachine"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.FelicisMachine.Hit"),DeathTag=(TagName="FX.Enemy.Common.FelicisMachine.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/FelicisMachine/AM_FelicisMachine_BasicAttack.AM_FelicisMachine_BasicAttack</t>
@@ -369,7 +375,7 @@
     <t>FelicisShinobi</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_FelicisShinobi.DA_EnemyFX_Common_FelicisShinobi",BasicAttackTag=(TagName="FX.Enemy.Common.FelicisShinobi"),HitTag=(TagName="FX.Enemy.Common.FelicisShinobi.Hit"),DeathTag=(TagName="FX.Enemy.Common.FelicisShinobi.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_FelicisShinobi.DA_EnemyFX_Common_FelicisShinobi",BasicAttackTag=(TagName="FX.Enemy.Common.FelicisShinobi"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.FelicisShinobi.Hit"),DeathTag=(TagName="FX.Enemy.Common.FelicisShinobi.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/FelicisShinobi/AM_FelicisShinobi_BasicAttack.AM_FelicisShinobi_BasicAttack</t>
@@ -390,7 +396,7 @@
     <t>Fiti</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Fiti.DA_EnemyFX_Common_Fiti",BasicAttackTag=(TagName="FX.Enemy.Common.Fiti"),HitTag=(TagName="FX.Enemy.Common.Fiti.Hit"),DeathTag=(TagName="FX.Enemy.Common.Fiti.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Fiti.DA_EnemyFX_Common_Fiti",BasicAttackTag=(TagName="FX.Enemy.Common.Fiti"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Fiti.Hit"),DeathTag=(TagName="FX.Enemy.Common.Fiti.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Fiti/AM_Fiti_BasicAttack.AM_Fiti_BasicAttack</t>
@@ -411,7 +417,7 @@
     <t>Gemini_Scythe</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_GeminiScythe.DA_EnemyFX_Common_GeminiScythe",BasicAttackTag=(TagName="FX.Enemy.Common.GeminiScythe"),HitTag=(TagName="FX.Enemy.Common.GeminiScythe.Hit"),DeathTag=(TagName="FX.Enemy.Common.GeminiScythe.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Gemini_Scythe.DA_EnemyFX_Common_Gemini_Scythe",BasicAttackTag=(TagName="FX.Enemy.Common.GeminiScythe"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.GeminiScythe.Hit"),DeathTag=(TagName="FX.Enemy.Common.GeminiScythe.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Gemini_Scythe/AM_Gemini_Scythe_BasicAttack.AM_Gemini_Scythe_BasicAttack</t>
@@ -432,7 +438,7 @@
     <t>GhostMacaron</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_GhostMacaron.DA_EnemyFX_Common_GhostMacaron",BasicAttackTag=(TagName="FX.Enemy.Common.GhostMacaron"),HitTag=(TagName="FX.Enemy.Common.GhostMacaron.Hit"),DeathTag=(TagName="FX.Enemy.Common.GhostMacaron.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_GhostMacaron.DA_EnemyFX_Common_GhostMacaron",BasicAttackTag=(TagName="FX.Enemy.Common.GhostMacaron"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.GhostMacaron.Hit"),DeathTag=(TagName="FX.Enemy.Common.GhostMacaron.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/GhostMacaron/AM_GhostMacaron_BasicAttack.AM_GhostMacaron_BasicAttack</t>
@@ -453,7 +459,7 @@
     <t>Graf</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Graf.DA_EnemyFX_Common_Graf",BasicAttackTag=(TagName="FX.Enemy.Common.Graf"),HitTag=(TagName="FX.Enemy.Common.Graf.Hit"),DeathTag=(TagName="FX.Enemy.Common.Graf.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Graf.DA_EnemyFX_Common_Graf",BasicAttackTag=(TagName="FX.Enemy.Common.Graf"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Graf.Hit"),DeathTag=(TagName="FX.Enemy.Common.Graf.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Graf/AM_Graf_BasicAttack.AM_Graf_BasicAttack</t>
@@ -474,7 +480,7 @@
     <t>GuardianTreant</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Boss/DA_EnemyFX_Boss_GuardianTreant.DA_EnemyFX_Boss_GuardianTreant",BasicAttackTag=(TagName="FX.Enemy.Boss.GuardianTreant"),HitTag=(TagName="FX.Enemy.Boss.GuardianTreant.Hit"),DeathTag=(TagName="FX.Enemy.Boss.GuardianTreant.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Boss/DA_EnemyFX_Boss_GuardianTreant.DA_EnemyFX_Boss_GuardianTreant",BasicAttackTag=(TagName="FX.Enemy.Boss.GuardianTreant"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Boss.GuardianTreant.Hit"),DeathTag=(TagName="FX.Enemy.Boss.GuardianTreant.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/GuardianTreant/AM_GuardianTreant_BasicAttack.AM_GuardianTreant_BasicAttack</t>
@@ -483,7 +489,7 @@
     <t>("/Game/Blueprints/Characters/Enemy/GuardianTreant/AM_GuardianTreant_Pattern1.AM_GuardianTreant_Pattern1","/Game/Blueprints/Characters/Enemy/GuardianTreant/AM_GuardianTreant_Pattern2.AM_GuardianTreant_Pattern2")</t>
   </si>
   <si>
-    <t>((AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_BossAreaPattern1.GA_BossAreaPattern1_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'",ProjectileClass=None),(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_BossAreaPattern2.GA_BossAreaPattern2_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Heal_Base.GE_Heal_Base_C'",ProjectileClass=None))</t>
+    <t>((AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_BossAreaPattern1.GA_BossAreaPattern1_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass=None),(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_BossAreaPattern2.GA_BossAreaPattern2_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Heal_Skill.GE_Heal_Skill_C'",ProjectileClass=None))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/GuardianTreant/SKM_GuardianTreant.SKM_GuardianTreant</t>
@@ -501,7 +507,7 @@
     <t>HackingTool</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_HackingTool.DA_EnemyFX_Common_HackingTool",BasicAttackTag=(TagName="FX.Enemy.Common.HackingTool"),HitTag=(TagName="FX.Enemy.Common.HackingTool.Hit"),DeathTag=(TagName="FX.Enemy.Common.HackingTool.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_HackingTool.DA_EnemyFX_Common_HackingTool",BasicAttackTag=(TagName="FX.Enemy.Common.HackingTool"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.HackingTool.Hit"),DeathTag=(TagName="FX.Enemy.Common.HackingTool.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/HackingTool/AM_HackingTool_BasicAttack.AM_HackingTool_BasicAttack</t>
@@ -522,7 +528,7 @@
     <t>HoneyMos</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_HoneyMos.DA_EnemyFX_Common_HoneyMos",BasicAttackTag=(TagName="FX.Enemy.Common.HoneyMos"),HitTag=(TagName="FX.Enemy.Common.HoneyMos.Hit"),DeathTag=(TagName="FX.Enemy.Common.HoneyMos.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_HoneyMos.DA_EnemyFX_Common_HoneyMos",BasicAttackTag=(TagName="FX.Enemy.Common.HoneyMos"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.HoneyMos.Hit"),DeathTag=(TagName="FX.Enemy.Common.HoneyMos.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/HoneyMos/AM_HoneyMos_BasicAttack.AM_HoneyMos_BasicAttack</t>
@@ -543,7 +549,7 @@
     <t>Jellyfish</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Jellyfish.DA_EnemyFX_Common_Jellyfish",BasicAttackTag=(TagName="FX.Enemy.Common.Jellyfish"),HitTag=(TagName="FX.Enemy.Common.Jellyfish.Hit"),DeathTag=(TagName="FX.Enemy.Common.Jellyfish.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Jellyfish.DA_EnemyFX_Common_Jellyfish",BasicAttackTag=(TagName="FX.Enemy.Common.Jellyfish"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Jellyfish.Hit"),DeathTag=(TagName="FX.Enemy.Common.Jellyfish.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Jellyfish/AM_JellyFish_BasicAttack.AM_JellyFish_BasicAttack</t>
@@ -564,7 +570,7 @@
     <t>Karakasa</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Karakasa.DA_EnemyFX_Common_Karakasa",BasicAttackTag=(TagName="FX.Enemy.Common.Karakasa"),HitTag=(TagName="FX.Enemy.Common.Karakasa.Hit"),DeathTag=(TagName="FX.Enemy.Common.Karakasa.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Karakasa.DA_EnemyFX_Common_Karakasa",BasicAttackTag=(TagName="FX.Enemy.Common.Karakasa"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Karakasa.Hit"),DeathTag=(TagName="FX.Enemy.Common.Karakasa.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Karakasa/AM_Karakasa_BasicAttack.AM_Karakasa_BasicAttack</t>
@@ -585,7 +591,7 @@
     <t>Kraken</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Kraken.DA_EnemyFX_Common_Kraken",BasicAttackTag=(TagName="FX.Enemy.Common.Kraken"),HitTag=(TagName="FX.Enemy.Common.Kraken.Hit"),DeathTag=(TagName="FX.Enemy.Common.Kraken.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Kraken.DA_EnemyFX_Common_Kraken",BasicAttackTag=(TagName="FX.Enemy.Common.Kraken"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Kraken.Hit"),DeathTag=(TagName="FX.Enemy.Common.Kraken.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Kraken/AM_Kraken_BasicAttack.AM_Kraken_BasicAttack</t>
@@ -606,7 +612,7 @@
     <t>LikeStatue</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_LikeStatue.DA_EnemyFX_Common_LikeStatue",BasicAttackTag=(TagName="FX.Enemy.Common.LikeStatue"),HitTag=(TagName="FX.Enemy.Common.LikeStatue.Hit"),DeathTag=(TagName="FX.Enemy.Common.LikeStatue.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_LikeStatue.DA_EnemyFX_Common_LikeStatue",BasicAttackTag=(TagName="FX.Enemy.Common.LikeStatue"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.LikeStatue.Hit"),DeathTag=(TagName="FX.Enemy.Common.LikeStatue.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/LikeStatue/AM_LikeStatue2_BasicAttack.AM_LikeStatue2_BasicAttack</t>
@@ -627,7 +633,7 @@
     <t>LordFelice</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_LordFelice.DA_EnemyFX_Common_LordFelice",BasicAttackTag=(TagName="FX.Enemy.Common.LordFelice"),HitTag=(TagName="FX.Enemy.Common.LordFelice.Hit"),DeathTag=(TagName="FX.Enemy.Common.LordFelice.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_LordFelice.DA_EnemyFX_Common_LordFelice",BasicAttackTag=(TagName="FX.Enemy.Common.LordFelice"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.LordFelice.Hit"),DeathTag=(TagName="FX.Enemy.Common.LordFelice.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/LordFelice/AM_LordFelice_BasicAttack.AM_LordFelice_BasicAttack</t>
@@ -648,7 +654,7 @@
     <t>Mandragora</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Mandragora.DA_EnemyFX_Common_Mandragora",BasicAttackTag=(TagName="FX.Enemy.Common.Mandragora"),HitTag=(TagName="FX.Enemy.Common.Mandragora.Hit"),DeathTag=(TagName="FX.Enemy.Common.Mandragora.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Mandragora.DA_EnemyFX_Common_Mandragora",BasicAttackTag=(TagName="FX.Enemy.Common.Mandragora"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Mandragora.Hit"),DeathTag=(TagName="FX.Enemy.Common.Mandragora.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Mandragora/AM_Mandragora_BasicAttack.AM_Mandragora_BasicAttack</t>
@@ -669,7 +675,7 @@
     <t>Mask</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Mask.DA_EnemyFX_Common_Mask",BasicAttackTag=(TagName="FX.Enemy.Common.Mask"),HitTag=(TagName="FX.Enemy.Common.Mask.Hit"),DeathTag=(TagName="FX.Enemy.Common.Mask.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Mask.DA_EnemyFX_Common_Mask",BasicAttackTag=(TagName="FX.Enemy.Common.Mask"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Mask.Hit"),DeathTag=(TagName="FX.Enemy.Common.Mask.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Mask/AM_Mask_BasicAttack.AM_Mask_BasicAttack</t>
@@ -690,7 +696,7 @@
     <t>Mechanicus</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Mechanicus.DA_EnemyFX_Common_Mechanicus",BasicAttackTag=(TagName="FX.Enemy.Common.Mechanicus"),HitTag=(TagName="FX.Enemy.Common.Mechanicus.Hit"),DeathTag=(TagName="FX.Enemy.Common.Mechanicus.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Mechanicus.DA_EnemyFX_Common_Mechanicus",BasicAttackTag=(TagName="FX.Enemy.Common.Mechanicus"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Mechanicus.Hit"),DeathTag=(TagName="FX.Enemy.Common.Mechanicus.Death"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Mechanicus/SKM_Mechanicus.SKM_Mechanicus</t>
@@ -702,7 +708,7 @@
     <t>Megaron</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Boss/DA_EnemyFX_Boss_Megaron.DA_EnemyFX_Boss_Megaron",BasicAttackTag=(TagName="FX.Enemy.Boss.Megaron"),HitTag=(TagName="FX.Enemy.Boss.Megaron.Hit"),DeathTag=(TagName="FX.Enemy.Boss.Megaron.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Boss/DA_EnemyFX_Boss_Megaron.DA_EnemyFX_Boss_Megaron",BasicAttackTag=(TagName="FX.Enemy.Boss.Megaron"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Boss.Megaron.Hit"),DeathTag=(TagName="FX.Enemy.Boss.Megaron.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Megaron/AM_Megaron_BasicAttack.AM_Megaron_BasicAttack</t>
@@ -711,7 +717,7 @@
     <t>("/Game/Blueprints/Characters/Enemy/Megaron/AM_Megaron_Pattern1.AM_Megaron_Pattern1","/Game/Blueprints/Characters/Enemy/Megaron/AM_Megaron_Pattern2.AM_Megaron_Pattern2")</t>
   </si>
   <si>
-    <t>((AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_BossAreaPattern1.GA_BossAreaPattern1_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'",ProjectileClass=None),(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_BossProjectilePattern2.GA_BossProjectilePattern2_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Standard.GE_Damage_Standard_C'",ProjectileClass=None))</t>
+    <t>((AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_BossAreaPattern1.GA_BossAreaPattern1_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass=None),(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_BossProjectilePattern2.GA_BossProjectilePattern2_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_BasicAttack.GE_Damage_BasicAttack_C'",ProjectileClass=None))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Megaron/SKM_Megaron_A.SKM_Megaron_A</t>
@@ -729,7 +735,7 @@
     <t>Mimic</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Mimic.DA_EnemyFX_Common_Mimic",BasicAttackTag=(TagName="FX.Enemy.Common.Mimic"),HitTag=(TagName="FX.Enemy.Common.Mimic.Hit"),DeathTag=(TagName="FX.Enemy.Common.Mimic.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Mimic.DA_EnemyFX_Common_Mimic",BasicAttackTag=(TagName="FX.Enemy.Common.Mimic"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Mimic.Hit"),DeathTag=(TagName="FX.Enemy.Common.Mimic.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Mimic/AM_Mimic_BasicAttack.AM_Mimic_BasicAttack</t>
@@ -750,7 +756,7 @@
     <t>Octopus</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Octopus.DA_EnemyFX_Common_Octopus",BasicAttackTag=(TagName="FX.Enemy.Common.Octopus"),HitTag=(TagName="FX.Enemy.Common.Octopus.Hit"),DeathTag=(TagName="FX.Enemy.Common.Octopus.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Octopus.DA_EnemyFX_Common_Octopus",BasicAttackTag=(TagName="FX.Enemy.Common.Octopus"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Octopus.Hit"),DeathTag=(TagName="FX.Enemy.Common.Octopus.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Octopus/AM_Octopus_BasicAttack.AM_Octopus_BasicAttack</t>
@@ -771,7 +777,7 @@
     <t>PistolShrimp</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_PistolShrimp.DA_EnemyFX_Common_PistolShrimp",BasicAttackTag=(TagName="FX.Enemy.Common.PistolShrimp"),HitTag=(TagName="FX.Enemy.Common.PistolShrimp.Hit"),DeathTag=(TagName="FX.Enemy.Common.PistolShrimp.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_PistolShrimp.DA_EnemyFX_Common_PistolShrimp",BasicAttackTag=(TagName="FX.Enemy.Common.PistolShrimp"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.PistolShrimp.Hit"),DeathTag=(TagName="FX.Enemy.Common.PistolShrimp.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/PistolShrimp/AM_PistolShrimp_BasicAttack.AM_PistolShrimp_BasicAttack</t>
@@ -792,7 +798,7 @@
     <t>Pufferfish</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Pufferfish.DA_EnemyFX_Common_Pufferfish",BasicAttackTag=(TagName="FX.Enemy.Common.Pufferfish"),HitTag=(TagName="FX.Enemy.Common.Pufferfish.Hit"),DeathTag=(TagName="FX.Enemy.Common.Pufferfish.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Pufferfish.DA_EnemyFX_Common_Pufferfish",BasicAttackTag=(TagName="FX.Enemy.Common.Pufferfish"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Pufferfish.Hit"),DeathTag=(TagName="FX.Enemy.Common.Pufferfish.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Pufferfish/AM_Pufferfish_BasicAttack.AM_Pufferfish_BasicAttack</t>
@@ -813,7 +819,7 @@
     <t>Seasoner</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Seasoner.DA_EnemyFX_Common_Seasoner",BasicAttackTag=(TagName="FX.Enemy.Common.Seasoner"),HitTag=(TagName="FX.Enemy.Common.Seasoner.Hit"),DeathTag=(TagName="FX.Enemy.Common.Seasoner.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Seasoner.DA_EnemyFX_Common_Seasoner",BasicAttackTag=(TagName="FX.Enemy.Common.Seasoner"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Seasoner.Hit"),DeathTag=(TagName="FX.Enemy.Common.Seasoner.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Seasoner/AM_Seasoner_BasicAttack.AM_Seasoner_BasicAttack</t>
@@ -834,7 +840,7 @@
     <t>SharkRider</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_SharkRider.DA_EnemyFX_Common_SharkRider",BasicAttackTag=(TagName="FX.Enemy.Common.SharkRider"),HitTag=(TagName="FX.Enemy.Common.SharkRider.Hit"),DeathTag=(TagName="FX.Enemy.Common.SharkRider.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_SharkRider.DA_EnemyFX_Common_SharkRider",BasicAttackTag=(TagName="FX.Enemy.Common.SharkRider"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.SharkRider.Hit"),DeathTag=(TagName="FX.Enemy.Common.SharkRider.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/SharkRider/AM_SharkRider_BasicAttack.AM_SharkRider_BasicAttack</t>
@@ -855,7 +861,7 @@
     <t>Starspawn</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Starspawn.DA_EnemyFX_Common_Starspawn",BasicAttackTag=(TagName="FX.Enemy.Common.Starspawn"),HitTag=(TagName="FX.Enemy.Common.Starspawn.Hit"),DeathTag=(TagName="FX.Enemy.Common.Starspawn.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Starspawn.DA_EnemyFX_Common_Starspawn",BasicAttackTag=(TagName="FX.Enemy.Common.Starspawn"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Starspawn.Hit"),DeathTag=(TagName="FX.Enemy.Common.Starspawn.Death"))</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Starspawn/SKM_Starspawn.SKM_Starspawn</t>
@@ -867,7 +873,7 @@
     <t>Ushabti</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Ushabti.DA_EnemyFX_Common_Ushabti",BasicAttackTag=(TagName="FX.Enemy.Common.Ushabti"),HitTag=(TagName="FX.Enemy.Common.Ushabti.Hit"),DeathTag=(TagName="FX.Enemy.Common.Ushabti.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Ushabti.DA_EnemyFX_Common_Ushabti",BasicAttackTag=(TagName="FX.Enemy.Common.Ushabti"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Ushabti.Hit"),DeathTag=(TagName="FX.Enemy.Common.Ushabti.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Ushabti/AM_Ushabti_BasicAttack.AM_Ushabti_BasicAttack</t>
@@ -888,7 +894,7 @@
     <t>Wagon</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Wagon.DA_EnemyFX_Common_Wagon",BasicAttackTag=(TagName="FX.Enemy.Common.Wagon"),HitTag=(TagName="FX.Enemy.Common.Wagon.Hit"),DeathTag=(TagName="FX.Enemy.Common.Wagon.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Wagon.DA_EnemyFX_Common_Wagon",BasicAttackTag=(TagName="FX.Enemy.Common.Wagon"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Wagon.Hit"),DeathTag=(TagName="FX.Enemy.Common.Wagon.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Wagon/AM_Wagon_BasicAttack.AM_Wagon_BasicAttack</t>
@@ -909,7 +915,7 @@
     <t>Watcher</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Watcher.DA_EnemyFX_Common_Watcher",BasicAttackTag=(TagName="FX.Enemy.Common.Watcher"),HitTag=(TagName="FX.Enemy.Common.Watcher.Hit"),DeathTag=(TagName="FX.Enemy.Common.Watcher.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Watcher.DA_EnemyFX_Common_Watcher",BasicAttackTag=(TagName="FX.Enemy.Common.Watcher"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Watcher.Hit"),DeathTag=(TagName="FX.Enemy.Common.Watcher.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Watcher/AM_Watcher_BasicAttack.AM_Watcher_BasicAttack</t>
@@ -925,6 +931,100 @@
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Watcher/AM_Watcher_Dead.AM_Watcher_Dead</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Dies/ABP_Dies.ABP_Dies_C'</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/DoctorMacaron/ABP_DoctorMacaron.ABP_DoctorMacaron_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Famine/ABP_Famine.ABP_Famine_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/FelicisMachine/ABP_FelicisMachine.ABP_FelicisMachine_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/FelicisShinobi/ABP_FelicisShinobi.ABP_FelicisShinobi_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Fiti/ABP_Fiti.ABP_Fiti_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Gemini_Scythe/ABP_Gemini_Scythe.ABP_Gemini_Scythe_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/GhostMacaron/ABP_GhostMacaron.ABP_GhostMacaron_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Graf/ABP_Graf.ABP_Graf_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/GuardianTreant/ABP_GuardianTreant.ABP_GuardianTreant_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/HackingTool/ABP_HackingTool.ABP_HackingTool_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/HoneyMos/ABP_HoneyMos.ABP_HoneyMos_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Jellyfish/ABP_Jellyfish.ABP_Jellyfish_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Karakasa/ABP_Karakasa.ABP_Karakasa_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Kraken/ABP_Kraken.ABP_Kraken_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/LikeStatue/ABP_LikeStatue.ABP_LikeStatue_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/LordFelice/ABP_LordFelice.ABP_LordFelice_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Mandragora/ABP_Mandragora.ABP_Mandragora_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Mask/ABP_Mask.ABP_Mask_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Mechanicus/ABP_Mechanicus.ABP_Mechanicus_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Megaron/ABP_Megaron.ABP_Megaron_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Mimic/ABP_Mimic.ABP_Mimic_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Octopus/ABP_Octopus.ABP_Octopus_C'</t>
+  </si>
+  <si>
+    <t>/Script/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/PistolShrimp/ABP_PistolShrimp.ABP_PistolShrimp_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Pufferfish/ABP_Pufferfish.ABP_Pufferfish_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Seasoner/ABP_Seasoner.ABP_Seasoner_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/SharkRider/ABP_SharkRider.ABP_SharkRider_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Starspawn/ABP_Starspawn.ABP_Starspawn_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Ushabti/ABP_Ushabti.ABP_Ushabti_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Wagon/ABP_Wagon.ABP_Wagon_C'</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Watcher/ABP_Watcher.ABP_Watcher_C'</t>
   </si>
 </sst>
 </file>
@@ -1842,10 +1942,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1897,1701 +1997,1707 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2">
         <v>1.3</v>
       </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3">
+        <v>0.8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" t="s">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="I3" t="s">
         <v>24</v>
       </c>
-      <c r="K2" t="s">
+      <c r="J3" t="s">
         <v>25</v>
       </c>
-      <c r="L2" t="s">
+      <c r="K3" t="s">
         <v>26</v>
       </c>
-      <c r="M2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="L3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" t="s">
         <v>28</v>
       </c>
-      <c r="O2" t="s">
-        <v>29</v>
-      </c>
-      <c r="P2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3">
+      <c r="N3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>42</v>
+      </c>
+      <c r="R3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4">
         <v>0.8</v>
       </c>
-      <c r="D3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="E4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" t="s">
         <v>26</v>
       </c>
-      <c r="M3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4">
+      <c r="M4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" t="s">
+        <v>50</v>
+      </c>
+      <c r="O4" t="s">
+        <v>51</v>
+      </c>
+      <c r="P4" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>53</v>
+      </c>
+      <c r="R4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" t="s">
+        <v>58</v>
+      </c>
+      <c r="O5" t="s">
+        <v>59</v>
+      </c>
+      <c r="P5" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>61</v>
+      </c>
+      <c r="R5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6">
+        <v>1.5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6" t="s">
+        <v>66</v>
+      </c>
+      <c r="O6" t="s">
+        <v>67</v>
+      </c>
+      <c r="P6" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7">
+        <v>1.8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" t="s">
+        <v>28</v>
+      </c>
+      <c r="N7" t="s">
+        <v>74</v>
+      </c>
+      <c r="O7" t="s">
+        <v>75</v>
+      </c>
+      <c r="P7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>77</v>
+      </c>
+      <c r="R7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" t="s">
+        <v>82</v>
+      </c>
+      <c r="M8" t="s">
+        <v>28</v>
+      </c>
+      <c r="N8" t="s">
+        <v>83</v>
+      </c>
+      <c r="O8" t="s">
+        <v>84</v>
+      </c>
+      <c r="P8" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>86</v>
+      </c>
+      <c r="R8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9">
         <v>0.8</v>
       </c>
-      <c r="D4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="E9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H9" t="s">
         <v>47</v>
       </c>
-      <c r="J4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="I9" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" t="s">
         <v>26</v>
       </c>
-      <c r="M4" t="s">
-        <v>48</v>
-      </c>
-      <c r="N4" t="s">
-        <v>49</v>
-      </c>
-      <c r="O4" t="s">
-        <v>50</v>
-      </c>
-      <c r="P4" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" t="s">
-        <v>56</v>
-      </c>
-      <c r="N5" t="s">
-        <v>57</v>
-      </c>
-      <c r="O5" t="s">
-        <v>58</v>
-      </c>
-      <c r="P5" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6">
-        <v>1.5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H6" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" t="s">
-        <v>47</v>
-      </c>
-      <c r="J6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6" t="s">
-        <v>64</v>
-      </c>
-      <c r="N6" t="s">
-        <v>65</v>
-      </c>
-      <c r="O6" t="s">
-        <v>66</v>
-      </c>
-      <c r="P6" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7">
-        <v>1.8</v>
-      </c>
-      <c r="D7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" t="s">
-        <v>72</v>
-      </c>
-      <c r="N7" t="s">
-        <v>73</v>
-      </c>
-      <c r="O7" t="s">
-        <v>74</v>
-      </c>
-      <c r="P7" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" t="s">
-        <v>80</v>
-      </c>
-      <c r="L8" t="s">
-        <v>26</v>
-      </c>
-      <c r="M8" t="s">
-        <v>81</v>
-      </c>
-      <c r="N8" t="s">
-        <v>82</v>
-      </c>
-      <c r="O8" t="s">
-        <v>83</v>
-      </c>
-      <c r="P8" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9">
-        <v>0.8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J9" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" t="s">
-        <v>26</v>
-      </c>
       <c r="M9" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="N9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P9" t="s">
-        <v>92</v>
+        <v>304</v>
       </c>
       <c r="Q9" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10">
+        <v>95</v>
+      </c>
+      <c r="D10">
         <v>0.3</v>
-      </c>
-      <c r="D10" t="s">
-        <v>95</v>
       </c>
       <c r="E10" t="s">
         <v>96</v>
       </c>
-      <c r="G10" t="s">
-        <v>45</v>
+      <c r="F10" t="s">
+        <v>97</v>
       </c>
       <c r="H10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J10" t="s">
-        <v>80</v>
-      </c>
-      <c r="L10" t="s">
-        <v>26</v>
+        <v>49</v>
+      </c>
+      <c r="K10" t="s">
+        <v>82</v>
       </c>
       <c r="M10" t="s">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="N10" t="s">
         <v>98</v>
       </c>
       <c r="O10" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="P10" t="s">
-        <v>99</v>
+        <v>305</v>
       </c>
       <c r="Q10" t="s">
+        <v>101</v>
+      </c>
+      <c r="R10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11">
+        <v>1.2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" t="s">
+        <v>105</v>
+      </c>
+      <c r="H11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J11" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" t="s">
+        <v>28</v>
+      </c>
+      <c r="N11" t="s">
+        <v>106</v>
+      </c>
+      <c r="O11" t="s">
+        <v>107</v>
+      </c>
+      <c r="P11" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>108</v>
+      </c>
+      <c r="R11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>111</v>
+      </c>
+      <c r="F12" t="s">
+        <v>112</v>
+      </c>
+      <c r="H12" t="s">
+        <v>47</v>
+      </c>
+      <c r="I12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" t="s">
+        <v>82</v>
+      </c>
+      <c r="M12" t="s">
+        <v>28</v>
+      </c>
+      <c r="N12" t="s">
+        <v>113</v>
+      </c>
+      <c r="O12" t="s">
+        <v>114</v>
+      </c>
+      <c r="P12" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>115</v>
+      </c>
+      <c r="R12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13">
+        <v>0.5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>118</v>
+      </c>
+      <c r="F13" t="s">
+        <v>119</v>
+      </c>
+      <c r="H13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I13" t="s">
+        <v>48</v>
+      </c>
+      <c r="J13" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" t="s">
+        <v>28</v>
+      </c>
+      <c r="N13" t="s">
+        <v>120</v>
+      </c>
+      <c r="O13" t="s">
+        <v>121</v>
+      </c>
+      <c r="P13" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>122</v>
+      </c>
+      <c r="R13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14">
+        <v>0.4</v>
+      </c>
+      <c r="E14" t="s">
+        <v>125</v>
+      </c>
+      <c r="F14" t="s">
+        <v>126</v>
+      </c>
+      <c r="H14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I14" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" t="s">
+        <v>28</v>
+      </c>
+      <c r="N14" t="s">
+        <v>127</v>
+      </c>
+      <c r="O14" t="s">
+        <v>128</v>
+      </c>
+      <c r="P14" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>129</v>
+      </c>
+      <c r="R14" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15">
+        <v>1.3</v>
+      </c>
+      <c r="E15" t="s">
+        <v>132</v>
+      </c>
+      <c r="F15" t="s">
+        <v>133</v>
+      </c>
+      <c r="H15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" t="s">
+        <v>48</v>
+      </c>
+      <c r="J15" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" t="s">
+        <v>28</v>
+      </c>
+      <c r="N15" t="s">
+        <v>134</v>
+      </c>
+      <c r="O15" t="s">
+        <v>135</v>
+      </c>
+      <c r="P15" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>136</v>
+      </c>
+      <c r="R15" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16">
+        <v>1.2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>139</v>
+      </c>
+      <c r="F16" t="s">
+        <v>140</v>
+      </c>
+      <c r="H16" t="s">
+        <v>47</v>
+      </c>
+      <c r="I16" t="s">
+        <v>48</v>
+      </c>
+      <c r="J16" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" t="s">
+        <v>28</v>
+      </c>
+      <c r="N16" t="s">
+        <v>141</v>
+      </c>
+      <c r="O16" t="s">
+        <v>142</v>
+      </c>
+      <c r="P16" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>143</v>
+      </c>
+      <c r="R16" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>145</v>
+      </c>
+      <c r="D17">
+        <v>0.4</v>
+      </c>
+      <c r="E17" t="s">
+        <v>146</v>
+      </c>
+      <c r="F17" t="s">
+        <v>147</v>
+      </c>
+      <c r="H17" t="s">
+        <v>47</v>
+      </c>
+      <c r="I17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J17" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" t="s">
+        <v>28</v>
+      </c>
+      <c r="N17" t="s">
+        <v>148</v>
+      </c>
+      <c r="O17" t="s">
+        <v>149</v>
+      </c>
+      <c r="P17" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>150</v>
+      </c>
+      <c r="R17" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>152</v>
+      </c>
+      <c r="D18">
+        <v>0.8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>153</v>
+      </c>
+      <c r="F18" t="s">
+        <v>154</v>
+      </c>
+      <c r="G18" t="s">
+        <v>155</v>
+      </c>
+      <c r="H18" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" t="s">
+        <v>156</v>
+      </c>
+      <c r="M18" t="s">
+        <v>28</v>
+      </c>
+      <c r="N18" t="s">
+        <v>157</v>
+      </c>
+      <c r="O18" t="s">
+        <v>158</v>
+      </c>
+      <c r="P18" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>159</v>
+      </c>
+      <c r="R18" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>161</v>
+      </c>
+      <c r="D19">
+        <v>0.3</v>
+      </c>
+      <c r="E19" t="s">
+        <v>162</v>
+      </c>
+      <c r="F19" t="s">
+        <v>163</v>
+      </c>
+      <c r="H19" t="s">
+        <v>47</v>
+      </c>
+      <c r="I19" t="s">
+        <v>48</v>
+      </c>
+      <c r="J19" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" t="s">
+        <v>28</v>
+      </c>
+      <c r="N19" t="s">
+        <v>164</v>
+      </c>
+      <c r="O19" t="s">
+        <v>165</v>
+      </c>
+      <c r="P19" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>166</v>
+      </c>
+      <c r="R19" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>168</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H20" t="s">
+        <v>47</v>
+      </c>
+      <c r="I20" t="s">
+        <v>48</v>
+      </c>
+      <c r="J20" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" t="s">
+        <v>26</v>
+      </c>
+      <c r="M20" t="s">
+        <v>28</v>
+      </c>
+      <c r="N20" t="s">
+        <v>171</v>
+      </c>
+      <c r="O20" t="s">
+        <v>172</v>
+      </c>
+      <c r="P20" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>173</v>
+      </c>
+      <c r="R20" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>175</v>
+      </c>
+      <c r="D21">
+        <v>0.9</v>
+      </c>
+      <c r="E21" t="s">
+        <v>176</v>
+      </c>
+      <c r="F21" t="s">
+        <v>177</v>
+      </c>
+      <c r="H21" t="s">
+        <v>47</v>
+      </c>
+      <c r="I21" t="s">
+        <v>48</v>
+      </c>
+      <c r="J21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" t="s">
+        <v>28</v>
+      </c>
+      <c r="N21" t="s">
+        <v>178</v>
+      </c>
+      <c r="O21" t="s">
+        <v>179</v>
+      </c>
+      <c r="P21" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>180</v>
+      </c>
+      <c r="R21" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>182</v>
+      </c>
+      <c r="D22">
+        <v>0.6</v>
+      </c>
+      <c r="E22" t="s">
+        <v>183</v>
+      </c>
+      <c r="F22" t="s">
+        <v>184</v>
+      </c>
+      <c r="H22" t="s">
+        <v>47</v>
+      </c>
+      <c r="I22" t="s">
+        <v>48</v>
+      </c>
+      <c r="J22" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" t="s">
+        <v>26</v>
+      </c>
+      <c r="M22" t="s">
+        <v>28</v>
+      </c>
+      <c r="N22" t="s">
+        <v>185</v>
+      </c>
+      <c r="O22" t="s">
+        <v>186</v>
+      </c>
+      <c r="P22" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>187</v>
+      </c>
+      <c r="R22" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>189</v>
+      </c>
+      <c r="D23">
+        <v>0.3</v>
+      </c>
+      <c r="E23" t="s">
+        <v>190</v>
+      </c>
+      <c r="F23" t="s">
+        <v>191</v>
+      </c>
+      <c r="H23" t="s">
+        <v>47</v>
+      </c>
+      <c r="I23" t="s">
+        <v>48</v>
+      </c>
+      <c r="J23" t="s">
+        <v>49</v>
+      </c>
+      <c r="K23" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" t="s">
+        <v>28</v>
+      </c>
+      <c r="N23" t="s">
+        <v>192</v>
+      </c>
+      <c r="O23" t="s">
+        <v>193</v>
+      </c>
+      <c r="P23" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>194</v>
+      </c>
+      <c r="R23" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>196</v>
+      </c>
+      <c r="D24">
+        <v>0.7</v>
+      </c>
+      <c r="E24" t="s">
+        <v>197</v>
+      </c>
+      <c r="F24" t="s">
+        <v>198</v>
+      </c>
+      <c r="H24" t="s">
+        <v>47</v>
+      </c>
+      <c r="I24" t="s">
+        <v>48</v>
+      </c>
+      <c r="J24" t="s">
+        <v>49</v>
+      </c>
+      <c r="K24" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" t="s">
+        <v>28</v>
+      </c>
+      <c r="N24" t="s">
+        <v>199</v>
+      </c>
+      <c r="O24" t="s">
+        <v>200</v>
+      </c>
+      <c r="P24" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>201</v>
+      </c>
+      <c r="R24" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>203</v>
+      </c>
+      <c r="D25">
+        <v>0.3</v>
+      </c>
+      <c r="E25" t="s">
+        <v>204</v>
+      </c>
+      <c r="F25" t="s">
+        <v>205</v>
+      </c>
+      <c r="H25" t="s">
+        <v>47</v>
+      </c>
+      <c r="I25" t="s">
+        <v>48</v>
+      </c>
+      <c r="J25" t="s">
+        <v>49</v>
+      </c>
+      <c r="K25" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" t="s">
+        <v>28</v>
+      </c>
+      <c r="N25" t="s">
+        <v>206</v>
+      </c>
+      <c r="O25" t="s">
+        <v>207</v>
+      </c>
+      <c r="P25" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>208</v>
+      </c>
+      <c r="R25" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>210</v>
+      </c>
+      <c r="D26">
+        <v>1.5</v>
+      </c>
+      <c r="E26" t="s">
+        <v>211</v>
+      </c>
+      <c r="F26" t="s">
+        <v>212</v>
+      </c>
+      <c r="H26" t="s">
+        <v>47</v>
+      </c>
+      <c r="I26" t="s">
+        <v>48</v>
+      </c>
+      <c r="J26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K26" t="s">
+        <v>82</v>
+      </c>
+      <c r="M26" t="s">
+        <v>28</v>
+      </c>
+      <c r="N26" t="s">
+        <v>213</v>
+      </c>
+      <c r="O26" t="s">
+        <v>214</v>
+      </c>
+      <c r="P26" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>215</v>
+      </c>
+      <c r="R26" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>217</v>
+      </c>
+      <c r="D27">
+        <v>1.2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>218</v>
+      </c>
+      <c r="F27" t="s">
+        <v>219</v>
+      </c>
+      <c r="H27" t="s">
+        <v>47</v>
+      </c>
+      <c r="I27" t="s">
+        <v>48</v>
+      </c>
+      <c r="J27" t="s">
+        <v>49</v>
+      </c>
+      <c r="K27" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" t="s">
+        <v>28</v>
+      </c>
+      <c r="N27" t="s">
+        <v>220</v>
+      </c>
+      <c r="O27" t="s">
+        <v>221</v>
+      </c>
+      <c r="P27" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>222</v>
+      </c>
+      <c r="R27" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>224</v>
+      </c>
+      <c r="D28">
+        <v>1.5</v>
+      </c>
+      <c r="E28" t="s">
+        <v>225</v>
+      </c>
+      <c r="F28" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>101</v>
-      </c>
-      <c r="C11">
+      <c r="H28" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" t="s">
+        <v>48</v>
+      </c>
+      <c r="J28" t="s">
+        <v>49</v>
+      </c>
+      <c r="K28" t="s">
+        <v>82</v>
+      </c>
+      <c r="M28" t="s">
+        <v>28</v>
+      </c>
+      <c r="N28" t="s">
+        <v>226</v>
+      </c>
+      <c r="O28" t="s">
+        <v>227</v>
+      </c>
+      <c r="P28" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>100</v>
+      </c>
+      <c r="R28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>228</v>
+      </c>
+      <c r="D29">
+        <v>2.5</v>
+      </c>
+      <c r="E29" t="s">
+        <v>229</v>
+      </c>
+      <c r="F29" t="s">
+        <v>230</v>
+      </c>
+      <c r="G29" t="s">
+        <v>231</v>
+      </c>
+      <c r="H29" t="s">
+        <v>47</v>
+      </c>
+      <c r="I29" t="s">
+        <v>48</v>
+      </c>
+      <c r="J29" t="s">
+        <v>49</v>
+      </c>
+      <c r="K29" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" t="s">
+        <v>232</v>
+      </c>
+      <c r="M29" t="s">
+        <v>28</v>
+      </c>
+      <c r="N29" t="s">
+        <v>233</v>
+      </c>
+      <c r="O29" t="s">
+        <v>234</v>
+      </c>
+      <c r="P29" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>235</v>
+      </c>
+      <c r="R29" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>237</v>
+      </c>
+      <c r="D30">
+        <v>0.5</v>
+      </c>
+      <c r="E30" t="s">
+        <v>238</v>
+      </c>
+      <c r="F30" t="s">
+        <v>239</v>
+      </c>
+      <c r="H30" t="s">
+        <v>47</v>
+      </c>
+      <c r="I30" t="s">
+        <v>48</v>
+      </c>
+      <c r="J30" t="s">
+        <v>49</v>
+      </c>
+      <c r="K30" t="s">
+        <v>26</v>
+      </c>
+      <c r="M30" t="s">
+        <v>28</v>
+      </c>
+      <c r="N30" t="s">
+        <v>240</v>
+      </c>
+      <c r="O30" t="s">
+        <v>241</v>
+      </c>
+      <c r="P30" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>242</v>
+      </c>
+      <c r="R30" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>244</v>
+      </c>
+      <c r="D31">
         <v>1.2</v>
       </c>
-      <c r="D11" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" t="s">
-        <v>103</v>
-      </c>
-      <c r="G11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="E31" t="s">
+        <v>245</v>
+      </c>
+      <c r="F31" t="s">
+        <v>246</v>
+      </c>
+      <c r="H31" t="s">
         <v>47</v>
       </c>
-      <c r="J11" t="s">
-        <v>24</v>
-      </c>
-      <c r="L11" t="s">
+      <c r="I31" t="s">
+        <v>48</v>
+      </c>
+      <c r="J31" t="s">
+        <v>49</v>
+      </c>
+      <c r="K31" t="s">
         <v>26</v>
       </c>
-      <c r="M11" t="s">
-        <v>104</v>
-      </c>
-      <c r="N11" t="s">
-        <v>105</v>
-      </c>
-      <c r="O11" t="s">
-        <v>91</v>
-      </c>
-      <c r="P11" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C12">
+      <c r="M31" t="s">
+        <v>28</v>
+      </c>
+      <c r="N31" t="s">
+        <v>247</v>
+      </c>
+      <c r="O31" t="s">
+        <v>248</v>
+      </c>
+      <c r="P31" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>249</v>
+      </c>
+      <c r="R31" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>251</v>
+      </c>
+      <c r="D32">
+        <v>0.6</v>
+      </c>
+      <c r="E32" t="s">
+        <v>252</v>
+      </c>
+      <c r="F32" t="s">
+        <v>253</v>
+      </c>
+      <c r="H32" t="s">
+        <v>47</v>
+      </c>
+      <c r="I32" t="s">
+        <v>48</v>
+      </c>
+      <c r="J32" t="s">
+        <v>49</v>
+      </c>
+      <c r="K32" t="s">
+        <v>26</v>
+      </c>
+      <c r="M32" t="s">
+        <v>28</v>
+      </c>
+      <c r="N32" t="s">
+        <v>254</v>
+      </c>
+      <c r="O32" t="s">
+        <v>255</v>
+      </c>
+      <c r="P32" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>256</v>
+      </c>
+      <c r="R32" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>258</v>
+      </c>
+      <c r="D33">
+        <v>0.6</v>
+      </c>
+      <c r="E33" t="s">
+        <v>259</v>
+      </c>
+      <c r="F33" t="s">
+        <v>260</v>
+      </c>
+      <c r="H33" t="s">
+        <v>47</v>
+      </c>
+      <c r="I33" t="s">
+        <v>48</v>
+      </c>
+      <c r="J33" t="s">
+        <v>49</v>
+      </c>
+      <c r="K33" t="s">
+        <v>26</v>
+      </c>
+      <c r="M33" t="s">
+        <v>28</v>
+      </c>
+      <c r="N33" t="s">
+        <v>261</v>
+      </c>
+      <c r="O33" t="s">
+        <v>262</v>
+      </c>
+      <c r="P33" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>263</v>
+      </c>
+      <c r="R33" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>265</v>
+      </c>
+      <c r="D34">
+        <v>1.4</v>
+      </c>
+      <c r="E34" t="s">
+        <v>266</v>
+      </c>
+      <c r="F34" t="s">
+        <v>267</v>
+      </c>
+      <c r="H34" t="s">
+        <v>47</v>
+      </c>
+      <c r="I34" t="s">
+        <v>48</v>
+      </c>
+      <c r="J34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K34" t="s">
+        <v>26</v>
+      </c>
+      <c r="M34" t="s">
+        <v>28</v>
+      </c>
+      <c r="N34" t="s">
+        <v>268</v>
+      </c>
+      <c r="O34" t="s">
+        <v>269</v>
+      </c>
+      <c r="P34" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>270</v>
+      </c>
+      <c r="R34" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>272</v>
+      </c>
+      <c r="D35">
+        <v>0.4</v>
+      </c>
+      <c r="E35" t="s">
+        <v>273</v>
+      </c>
+      <c r="F35" t="s">
+        <v>274</v>
+      </c>
+      <c r="H35" t="s">
+        <v>47</v>
+      </c>
+      <c r="I35" t="s">
+        <v>48</v>
+      </c>
+      <c r="J35" t="s">
+        <v>49</v>
+      </c>
+      <c r="K35" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" t="s">
+        <v>28</v>
+      </c>
+      <c r="N35" t="s">
+        <v>275</v>
+      </c>
+      <c r="O35" t="s">
+        <v>276</v>
+      </c>
+      <c r="P35" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>277</v>
+      </c>
+      <c r="R35" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>279</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36" t="s">
+        <v>280</v>
+      </c>
+      <c r="F36" t="s">
+        <v>100</v>
+      </c>
+      <c r="H36" t="s">
+        <v>47</v>
+      </c>
+      <c r="I36" t="s">
+        <v>48</v>
+      </c>
+      <c r="J36" t="s">
+        <v>49</v>
+      </c>
+      <c r="K36" t="s">
+        <v>26</v>
+      </c>
+      <c r="M36" t="s">
+        <v>28</v>
+      </c>
+      <c r="N36" t="s">
+        <v>281</v>
+      </c>
+      <c r="O36" t="s">
+        <v>282</v>
+      </c>
+      <c r="P36" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>100</v>
+      </c>
+      <c r="R36" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>283</v>
+      </c>
+      <c r="D37">
         <v>1</v>
       </c>
-      <c r="D12" t="s">
-        <v>109</v>
-      </c>
-      <c r="E12" t="s">
-        <v>110</v>
-      </c>
-      <c r="G12" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" t="s">
-        <v>46</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="E37" t="s">
+        <v>284</v>
+      </c>
+      <c r="F37" t="s">
+        <v>285</v>
+      </c>
+      <c r="H37" t="s">
         <v>47</v>
       </c>
-      <c r="J12" t="s">
-        <v>80</v>
-      </c>
-      <c r="L12" t="s">
+      <c r="I37" t="s">
+        <v>48</v>
+      </c>
+      <c r="J37" t="s">
+        <v>49</v>
+      </c>
+      <c r="K37" t="s">
         <v>26</v>
       </c>
-      <c r="M12" t="s">
-        <v>111</v>
-      </c>
-      <c r="N12" t="s">
-        <v>112</v>
-      </c>
-      <c r="O12" t="s">
-        <v>91</v>
-      </c>
-      <c r="P12" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>115</v>
-      </c>
-      <c r="C13">
-        <v>0.5</v>
-      </c>
-      <c r="D13" t="s">
-        <v>116</v>
-      </c>
-      <c r="E13" t="s">
-        <v>117</v>
-      </c>
-      <c r="G13" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="M37" t="s">
+        <v>28</v>
+      </c>
+      <c r="N37" t="s">
+        <v>286</v>
+      </c>
+      <c r="O37" t="s">
+        <v>287</v>
+      </c>
+      <c r="P37" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>288</v>
+      </c>
+      <c r="R37" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>290</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38" t="s">
+        <v>291</v>
+      </c>
+      <c r="F38" t="s">
+        <v>292</v>
+      </c>
+      <c r="H38" t="s">
         <v>47</v>
       </c>
-      <c r="J13" t="s">
-        <v>24</v>
-      </c>
-      <c r="L13" t="s">
+      <c r="I38" t="s">
+        <v>48</v>
+      </c>
+      <c r="J38" t="s">
+        <v>49</v>
+      </c>
+      <c r="K38" t="s">
+        <v>82</v>
+      </c>
+      <c r="M38" t="s">
+        <v>28</v>
+      </c>
+      <c r="N38" t="s">
+        <v>293</v>
+      </c>
+      <c r="O38" t="s">
+        <v>294</v>
+      </c>
+      <c r="P38" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>295</v>
+      </c>
+      <c r="R38" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>297</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>298</v>
+      </c>
+      <c r="F39" t="s">
+        <v>299</v>
+      </c>
+      <c r="H39" t="s">
+        <v>47</v>
+      </c>
+      <c r="I39" t="s">
+        <v>48</v>
+      </c>
+      <c r="J39" t="s">
+        <v>49</v>
+      </c>
+      <c r="K39" t="s">
         <v>26</v>
       </c>
-      <c r="M13" t="s">
-        <v>118</v>
-      </c>
-      <c r="N13" t="s">
-        <v>119</v>
-      </c>
-      <c r="O13" t="s">
-        <v>91</v>
-      </c>
-      <c r="P13" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>122</v>
-      </c>
-      <c r="C14">
-        <v>0.4</v>
-      </c>
-      <c r="D14" t="s">
-        <v>123</v>
-      </c>
-      <c r="E14" t="s">
-        <v>124</v>
-      </c>
-      <c r="G14" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14" t="s">
-        <v>46</v>
-      </c>
-      <c r="I14" t="s">
-        <v>47</v>
-      </c>
-      <c r="J14" t="s">
-        <v>24</v>
-      </c>
-      <c r="L14" t="s">
-        <v>26</v>
-      </c>
-      <c r="M14" t="s">
-        <v>125</v>
-      </c>
-      <c r="N14" t="s">
-        <v>126</v>
-      </c>
-      <c r="O14" t="s">
-        <v>91</v>
-      </c>
-      <c r="P14" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>129</v>
-      </c>
-      <c r="C15">
-        <v>1.3</v>
-      </c>
-      <c r="D15" t="s">
-        <v>130</v>
-      </c>
-      <c r="E15" t="s">
-        <v>131</v>
-      </c>
-      <c r="G15" t="s">
-        <v>45</v>
-      </c>
-      <c r="H15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I15" t="s">
-        <v>47</v>
-      </c>
-      <c r="J15" t="s">
-        <v>24</v>
-      </c>
-      <c r="L15" t="s">
-        <v>26</v>
-      </c>
-      <c r="M15" t="s">
-        <v>132</v>
-      </c>
-      <c r="N15" t="s">
-        <v>133</v>
-      </c>
-      <c r="O15" t="s">
-        <v>91</v>
-      </c>
-      <c r="P15" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>136</v>
-      </c>
-      <c r="C16">
-        <v>1.2</v>
-      </c>
-      <c r="D16" t="s">
-        <v>137</v>
-      </c>
-      <c r="E16" t="s">
-        <v>138</v>
-      </c>
-      <c r="G16" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16" t="s">
-        <v>47</v>
-      </c>
-      <c r="J16" t="s">
-        <v>24</v>
-      </c>
-      <c r="L16" t="s">
-        <v>26</v>
-      </c>
-      <c r="M16" t="s">
-        <v>139</v>
-      </c>
-      <c r="N16" t="s">
-        <v>140</v>
-      </c>
-      <c r="O16" t="s">
-        <v>91</v>
-      </c>
-      <c r="P16" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>143</v>
-      </c>
-      <c r="C17">
-        <v>0.4</v>
-      </c>
-      <c r="D17" t="s">
-        <v>144</v>
-      </c>
-      <c r="E17" t="s">
-        <v>145</v>
-      </c>
-      <c r="G17" t="s">
-        <v>45</v>
-      </c>
-      <c r="H17" t="s">
-        <v>46</v>
-      </c>
-      <c r="I17" t="s">
-        <v>47</v>
-      </c>
-      <c r="J17" t="s">
-        <v>24</v>
-      </c>
-      <c r="L17" t="s">
-        <v>26</v>
-      </c>
-      <c r="M17" t="s">
-        <v>146</v>
-      </c>
-      <c r="N17" t="s">
-        <v>147</v>
-      </c>
-      <c r="O17" t="s">
-        <v>91</v>
-      </c>
-      <c r="P17" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>150</v>
-      </c>
-      <c r="C18">
-        <v>0.8</v>
-      </c>
-      <c r="D18" t="s">
-        <v>151</v>
-      </c>
-      <c r="E18" t="s">
-        <v>152</v>
-      </c>
-      <c r="F18" t="s">
-        <v>153</v>
-      </c>
-      <c r="G18" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" t="s">
-        <v>23</v>
-      </c>
-      <c r="J18" t="s">
-        <v>24</v>
-      </c>
-      <c r="K18" t="s">
-        <v>154</v>
-      </c>
-      <c r="L18" t="s">
-        <v>26</v>
-      </c>
-      <c r="M18" t="s">
-        <v>155</v>
-      </c>
-      <c r="N18" t="s">
-        <v>156</v>
-      </c>
-      <c r="O18" t="s">
-        <v>91</v>
-      </c>
-      <c r="P18" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>159</v>
-      </c>
-      <c r="C19">
-        <v>0.3</v>
-      </c>
-      <c r="D19" t="s">
-        <v>160</v>
-      </c>
-      <c r="E19" t="s">
-        <v>161</v>
-      </c>
-      <c r="G19" t="s">
-        <v>45</v>
-      </c>
-      <c r="H19" t="s">
-        <v>46</v>
-      </c>
-      <c r="I19" t="s">
-        <v>47</v>
-      </c>
-      <c r="J19" t="s">
-        <v>24</v>
-      </c>
-      <c r="L19" t="s">
-        <v>26</v>
-      </c>
-      <c r="M19" t="s">
-        <v>162</v>
-      </c>
-      <c r="N19" t="s">
-        <v>163</v>
-      </c>
-      <c r="O19" t="s">
-        <v>91</v>
-      </c>
-      <c r="P19" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>166</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20" t="s">
-        <v>167</v>
-      </c>
-      <c r="E20" t="s">
-        <v>168</v>
-      </c>
-      <c r="G20" t="s">
-        <v>45</v>
-      </c>
-      <c r="H20" t="s">
-        <v>46</v>
-      </c>
-      <c r="I20" t="s">
-        <v>47</v>
-      </c>
-      <c r="J20" t="s">
-        <v>24</v>
-      </c>
-      <c r="L20" t="s">
-        <v>26</v>
-      </c>
-      <c r="M20" t="s">
-        <v>169</v>
-      </c>
-      <c r="N20" t="s">
-        <v>170</v>
-      </c>
-      <c r="O20" t="s">
-        <v>91</v>
-      </c>
-      <c r="P20" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>173</v>
-      </c>
-      <c r="C21">
-        <v>0.9</v>
-      </c>
-      <c r="D21" t="s">
-        <v>174</v>
-      </c>
-      <c r="E21" t="s">
-        <v>175</v>
-      </c>
-      <c r="G21" t="s">
-        <v>45</v>
-      </c>
-      <c r="H21" t="s">
-        <v>46</v>
-      </c>
-      <c r="I21" t="s">
-        <v>47</v>
-      </c>
-      <c r="J21" t="s">
-        <v>24</v>
-      </c>
-      <c r="L21" t="s">
-        <v>26</v>
-      </c>
-      <c r="M21" t="s">
-        <v>176</v>
-      </c>
-      <c r="N21" t="s">
-        <v>177</v>
-      </c>
-      <c r="O21" t="s">
-        <v>91</v>
-      </c>
-      <c r="P21" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>180</v>
-      </c>
-      <c r="C22">
-        <v>0.6</v>
-      </c>
-      <c r="D22" t="s">
-        <v>181</v>
-      </c>
-      <c r="E22" t="s">
-        <v>182</v>
-      </c>
-      <c r="G22" t="s">
-        <v>45</v>
-      </c>
-      <c r="H22" t="s">
-        <v>46</v>
-      </c>
-      <c r="I22" t="s">
-        <v>47</v>
-      </c>
-      <c r="J22" t="s">
-        <v>24</v>
-      </c>
-      <c r="L22" t="s">
-        <v>26</v>
-      </c>
-      <c r="M22" t="s">
-        <v>183</v>
-      </c>
-      <c r="N22" t="s">
-        <v>184</v>
-      </c>
-      <c r="O22" t="s">
-        <v>91</v>
-      </c>
-      <c r="P22" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>187</v>
-      </c>
-      <c r="C23">
-        <v>0.3</v>
-      </c>
-      <c r="D23" t="s">
-        <v>188</v>
-      </c>
-      <c r="E23" t="s">
-        <v>189</v>
-      </c>
-      <c r="G23" t="s">
-        <v>45</v>
-      </c>
-      <c r="H23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I23" t="s">
-        <v>47</v>
-      </c>
-      <c r="J23" t="s">
-        <v>24</v>
-      </c>
-      <c r="L23" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" t="s">
-        <v>190</v>
-      </c>
-      <c r="N23" t="s">
-        <v>191</v>
-      </c>
-      <c r="O23" t="s">
-        <v>91</v>
-      </c>
-      <c r="P23" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>194</v>
-      </c>
-      <c r="C24">
-        <v>0.7</v>
-      </c>
-      <c r="D24" t="s">
-        <v>195</v>
-      </c>
-      <c r="E24" t="s">
-        <v>196</v>
-      </c>
-      <c r="G24" t="s">
-        <v>45</v>
-      </c>
-      <c r="H24" t="s">
-        <v>46</v>
-      </c>
-      <c r="I24" t="s">
-        <v>47</v>
-      </c>
-      <c r="J24" t="s">
-        <v>24</v>
-      </c>
-      <c r="L24" t="s">
-        <v>26</v>
-      </c>
-      <c r="M24" t="s">
-        <v>197</v>
-      </c>
-      <c r="N24" t="s">
-        <v>198</v>
-      </c>
-      <c r="O24" t="s">
-        <v>91</v>
-      </c>
-      <c r="P24" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>201</v>
-      </c>
-      <c r="C25">
-        <v>0.3</v>
-      </c>
-      <c r="D25" t="s">
-        <v>202</v>
-      </c>
-      <c r="E25" t="s">
-        <v>203</v>
-      </c>
-      <c r="G25" t="s">
-        <v>45</v>
-      </c>
-      <c r="H25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I25" t="s">
-        <v>47</v>
-      </c>
-      <c r="J25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L25" t="s">
-        <v>26</v>
-      </c>
-      <c r="M25" t="s">
-        <v>204</v>
-      </c>
-      <c r="N25" t="s">
-        <v>205</v>
-      </c>
-      <c r="O25" t="s">
-        <v>91</v>
-      </c>
-      <c r="P25" t="s">
-        <v>206</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>208</v>
-      </c>
-      <c r="C26">
-        <v>1.5</v>
-      </c>
-      <c r="D26" t="s">
-        <v>209</v>
-      </c>
-      <c r="E26" t="s">
-        <v>210</v>
-      </c>
-      <c r="G26" t="s">
-        <v>45</v>
-      </c>
-      <c r="H26" t="s">
-        <v>46</v>
-      </c>
-      <c r="I26" t="s">
-        <v>47</v>
-      </c>
-      <c r="J26" t="s">
-        <v>80</v>
-      </c>
-      <c r="L26" t="s">
-        <v>26</v>
-      </c>
-      <c r="M26" t="s">
-        <v>211</v>
-      </c>
-      <c r="N26" t="s">
-        <v>212</v>
-      </c>
-      <c r="O26" t="s">
-        <v>91</v>
-      </c>
-      <c r="P26" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>215</v>
-      </c>
-      <c r="C27">
-        <v>1.2</v>
-      </c>
-      <c r="D27" t="s">
-        <v>216</v>
-      </c>
-      <c r="E27" t="s">
-        <v>217</v>
-      </c>
-      <c r="G27" t="s">
-        <v>45</v>
-      </c>
-      <c r="H27" t="s">
-        <v>46</v>
-      </c>
-      <c r="I27" t="s">
-        <v>47</v>
-      </c>
-      <c r="J27" t="s">
-        <v>24</v>
-      </c>
-      <c r="L27" t="s">
-        <v>26</v>
-      </c>
-      <c r="M27" t="s">
-        <v>218</v>
-      </c>
-      <c r="N27" t="s">
-        <v>219</v>
-      </c>
-      <c r="O27" t="s">
-        <v>91</v>
-      </c>
-      <c r="P27" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>222</v>
-      </c>
-      <c r="C28">
-        <v>1.5</v>
-      </c>
-      <c r="D28" t="s">
-        <v>223</v>
-      </c>
-      <c r="E28" t="s">
-        <v>91</v>
-      </c>
-      <c r="G28" t="s">
-        <v>45</v>
-      </c>
-      <c r="H28" t="s">
-        <v>46</v>
-      </c>
-      <c r="I28" t="s">
-        <v>47</v>
-      </c>
-      <c r="J28" t="s">
-        <v>80</v>
-      </c>
-      <c r="L28" t="s">
-        <v>26</v>
-      </c>
-      <c r="M28" t="s">
-        <v>224</v>
-      </c>
-      <c r="N28" t="s">
-        <v>225</v>
-      </c>
-      <c r="O28" t="s">
-        <v>91</v>
-      </c>
-      <c r="P28" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>226</v>
-      </c>
-      <c r="C29">
-        <v>2.5</v>
-      </c>
-      <c r="D29" t="s">
-        <v>227</v>
-      </c>
-      <c r="E29" t="s">
-        <v>228</v>
-      </c>
-      <c r="F29" t="s">
-        <v>229</v>
-      </c>
-      <c r="G29" t="s">
-        <v>45</v>
-      </c>
-      <c r="H29" t="s">
-        <v>46</v>
-      </c>
-      <c r="I29" t="s">
-        <v>47</v>
-      </c>
-      <c r="J29" t="s">
-        <v>24</v>
-      </c>
-      <c r="K29" t="s">
-        <v>230</v>
-      </c>
-      <c r="L29" t="s">
-        <v>26</v>
-      </c>
-      <c r="M29" t="s">
-        <v>231</v>
-      </c>
-      <c r="N29" t="s">
-        <v>232</v>
-      </c>
-      <c r="O29" t="s">
-        <v>91</v>
-      </c>
-      <c r="P29" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>235</v>
-      </c>
-      <c r="C30">
-        <v>0.5</v>
-      </c>
-      <c r="D30" t="s">
-        <v>236</v>
-      </c>
-      <c r="E30" t="s">
-        <v>237</v>
-      </c>
-      <c r="G30" t="s">
-        <v>45</v>
-      </c>
-      <c r="H30" t="s">
-        <v>46</v>
-      </c>
-      <c r="I30" t="s">
-        <v>47</v>
-      </c>
-      <c r="J30" t="s">
-        <v>24</v>
-      </c>
-      <c r="L30" t="s">
-        <v>26</v>
-      </c>
-      <c r="M30" t="s">
-        <v>238</v>
-      </c>
-      <c r="N30" t="s">
-        <v>239</v>
-      </c>
-      <c r="O30" t="s">
-        <v>91</v>
-      </c>
-      <c r="P30" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>242</v>
-      </c>
-      <c r="C31">
-        <v>1.2</v>
-      </c>
-      <c r="D31" t="s">
-        <v>243</v>
-      </c>
-      <c r="E31" t="s">
-        <v>244</v>
-      </c>
-      <c r="G31" t="s">
-        <v>45</v>
-      </c>
-      <c r="H31" t="s">
-        <v>46</v>
-      </c>
-      <c r="I31" t="s">
-        <v>47</v>
-      </c>
-      <c r="J31" t="s">
-        <v>24</v>
-      </c>
-      <c r="L31" t="s">
-        <v>26</v>
-      </c>
-      <c r="M31" t="s">
-        <v>245</v>
-      </c>
-      <c r="N31" t="s">
-        <v>246</v>
-      </c>
-      <c r="O31" t="s">
-        <v>91</v>
-      </c>
-      <c r="P31" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>249</v>
-      </c>
-      <c r="C32">
-        <v>0.6</v>
-      </c>
-      <c r="D32" t="s">
-        <v>250</v>
-      </c>
-      <c r="E32" t="s">
-        <v>251</v>
-      </c>
-      <c r="G32" t="s">
-        <v>45</v>
-      </c>
-      <c r="H32" t="s">
-        <v>46</v>
-      </c>
-      <c r="I32" t="s">
-        <v>47</v>
-      </c>
-      <c r="J32" t="s">
-        <v>24</v>
-      </c>
-      <c r="L32" t="s">
-        <v>26</v>
-      </c>
-      <c r="M32" t="s">
-        <v>252</v>
-      </c>
-      <c r="N32" t="s">
-        <v>253</v>
-      </c>
-      <c r="O32" t="s">
-        <v>91</v>
-      </c>
-      <c r="P32" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>256</v>
-      </c>
-      <c r="C33">
-        <v>0.6</v>
-      </c>
-      <c r="D33" t="s">
-        <v>257</v>
-      </c>
-      <c r="E33" t="s">
-        <v>258</v>
-      </c>
-      <c r="G33" t="s">
-        <v>45</v>
-      </c>
-      <c r="H33" t="s">
-        <v>46</v>
-      </c>
-      <c r="I33" t="s">
-        <v>47</v>
-      </c>
-      <c r="J33" t="s">
-        <v>24</v>
-      </c>
-      <c r="L33" t="s">
-        <v>26</v>
-      </c>
-      <c r="M33" t="s">
-        <v>259</v>
-      </c>
-      <c r="N33" t="s">
-        <v>260</v>
-      </c>
-      <c r="O33" t="s">
-        <v>91</v>
-      </c>
-      <c r="P33" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>263</v>
-      </c>
-      <c r="C34">
-        <v>1.4</v>
-      </c>
-      <c r="D34" t="s">
-        <v>264</v>
-      </c>
-      <c r="E34" t="s">
-        <v>265</v>
-      </c>
-      <c r="G34" t="s">
-        <v>45</v>
-      </c>
-      <c r="H34" t="s">
-        <v>46</v>
-      </c>
-      <c r="I34" t="s">
-        <v>47</v>
-      </c>
-      <c r="J34" t="s">
-        <v>24</v>
-      </c>
-      <c r="L34" t="s">
-        <v>26</v>
-      </c>
-      <c r="M34" t="s">
-        <v>266</v>
-      </c>
-      <c r="N34" t="s">
-        <v>267</v>
-      </c>
-      <c r="O34" t="s">
-        <v>91</v>
-      </c>
-      <c r="P34" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>270</v>
-      </c>
-      <c r="C35">
-        <v>0.4</v>
-      </c>
-      <c r="D35" t="s">
-        <v>271</v>
-      </c>
-      <c r="E35" t="s">
-        <v>272</v>
-      </c>
-      <c r="G35" t="s">
-        <v>45</v>
-      </c>
-      <c r="H35" t="s">
-        <v>46</v>
-      </c>
-      <c r="I35" t="s">
-        <v>47</v>
-      </c>
-      <c r="J35" t="s">
-        <v>24</v>
-      </c>
-      <c r="L35" t="s">
-        <v>26</v>
-      </c>
-      <c r="M35" t="s">
-        <v>273</v>
-      </c>
-      <c r="N35" t="s">
-        <v>274</v>
-      </c>
-      <c r="O35" t="s">
-        <v>91</v>
-      </c>
-      <c r="P35" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>277</v>
-      </c>
-      <c r="C36">
-        <v>2</v>
-      </c>
-      <c r="D36" t="s">
-        <v>278</v>
-      </c>
-      <c r="E36" t="s">
-        <v>91</v>
-      </c>
-      <c r="G36" t="s">
-        <v>45</v>
-      </c>
-      <c r="H36" t="s">
-        <v>46</v>
-      </c>
-      <c r="I36" t="s">
-        <v>47</v>
-      </c>
-      <c r="J36" t="s">
-        <v>24</v>
-      </c>
-      <c r="L36" t="s">
-        <v>26</v>
-      </c>
-      <c r="M36" t="s">
-        <v>279</v>
-      </c>
-      <c r="N36" t="s">
-        <v>280</v>
-      </c>
-      <c r="O36" t="s">
-        <v>91</v>
-      </c>
-      <c r="P36" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>281</v>
-      </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37" t="s">
-        <v>282</v>
-      </c>
-      <c r="E37" t="s">
-        <v>283</v>
-      </c>
-      <c r="G37" t="s">
-        <v>45</v>
-      </c>
-      <c r="H37" t="s">
-        <v>46</v>
-      </c>
-      <c r="I37" t="s">
-        <v>47</v>
-      </c>
-      <c r="J37" t="s">
-        <v>24</v>
-      </c>
-      <c r="L37" t="s">
-        <v>26</v>
-      </c>
-      <c r="M37" t="s">
-        <v>284</v>
-      </c>
-      <c r="N37" t="s">
-        <v>285</v>
-      </c>
-      <c r="O37" t="s">
-        <v>91</v>
-      </c>
-      <c r="P37" t="s">
-        <v>286</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>288</v>
-      </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38" t="s">
-        <v>289</v>
-      </c>
-      <c r="E38" t="s">
-        <v>290</v>
-      </c>
-      <c r="G38" t="s">
-        <v>45</v>
-      </c>
-      <c r="H38" t="s">
-        <v>46</v>
-      </c>
-      <c r="I38" t="s">
-        <v>47</v>
-      </c>
-      <c r="J38" t="s">
-        <v>80</v>
-      </c>
-      <c r="L38" t="s">
-        <v>26</v>
-      </c>
-      <c r="M38" t="s">
-        <v>291</v>
-      </c>
-      <c r="N38" t="s">
-        <v>292</v>
-      </c>
-      <c r="O38" t="s">
-        <v>91</v>
-      </c>
-      <c r="P38" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>295</v>
-      </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39" t="s">
-        <v>296</v>
-      </c>
-      <c r="E39" t="s">
-        <v>297</v>
-      </c>
-      <c r="G39" t="s">
-        <v>45</v>
-      </c>
-      <c r="H39" t="s">
-        <v>46</v>
-      </c>
-      <c r="I39" t="s">
-        <v>47</v>
-      </c>
-      <c r="J39" t="s">
-        <v>24</v>
-      </c>
-      <c r="L39" t="s">
-        <v>26</v>
-      </c>
       <c r="M39" t="s">
-        <v>298</v>
+        <v>28</v>
       </c>
       <c r="N39" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O39" t="s">
-        <v>91</v>
+        <v>301</v>
       </c>
       <c r="P39" t="s">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="Q39" t="s">
-        <v>301</v>
+        <v>302</v>
+      </c>
+      <c r="R39" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/EnemyAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/EnemyAssets_Master.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealCpp\Paradise\DesignData\Excel_Masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="10050"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="10035"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyAssets" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="345">
   <si>
     <t>---</t>
   </si>
@@ -78,6 +78,9 @@
     <t>Balrog</t>
   </si>
   <si>
+    <t>((TagName="FX.Enemy.Boss.Balrog.Pattern1"),(TagName="FX.Enemy.Boss.Balrog.Pattern2"))</t>
+  </si>
+  <si>
     <t>((TagName="FX.Enemy.Boss.Balrog.Pattern1Hit"),(TagName="FX.Enemy.Boss.Balrog.Pattern2Hit"))</t>
   </si>
   <si>
@@ -126,7 +129,7 @@
     <t>Bearking</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Boss/DA_EnemyFX_Boss_Bearking.DA_EnemyFX_Boss_Bearking",BasicAttackTag=(TagName="FX.Enemy.Boss.Bearking"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Boss.Bearking.Hit"),DeathTag=(TagName="FX.Enemy.Boss.Bearking.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Boss/DA_EnemyFX_Boss_Bearking.DA_EnemyFX_Boss_Bearking",BasicAttackTag=(TagName="FX.Enemy.Boss.Bearking"),BasicAttackHitTag=(TagName="FX.Enemy.Boss.Bearking.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Boss.Bearking.Hit"),DeathTag=(TagName="FX.Enemy.Boss.Bearking.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Bearking/AM_Bearking_BasicAttack.AM_Bearking_BasicAttack</t>
@@ -156,7 +159,7 @@
     <t>BronzeGear</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_BronzeGear.DA_EnemyFX_Common_BronzeGear",BasicAttackTag=(TagName="FX.Enemy.Common.BronzeGear"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.BronzeGear.Hit"),DeathTag=(TagName="FX.Enemy.Common.BronzeGear.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_BronzeGear.DA_EnemyFX_Common_BronzeGear",BasicAttackTag=(TagName="FX.Enemy.Common.BronzeGear"),BasicAttackHitTag=(TagName="FX.Enemy.Common.BronzeGear.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.BronzeGear.Hit"),DeathTag=(TagName="FX.Enemy.Common.BronzeGear.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/BronzeGear/AM_BronzeGear_BasicAttack.AM_BronzeGear_BasicAttack</t>
@@ -189,7 +192,7 @@
     <t>Cell</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Cell.DA_EnemyFX_Common_Cell",BasicAttackTag=(TagName="FX.Enemy.Common.Cell"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Cell.Hit"),DeathTag=(TagName="FX.Enemy.Common.Cell.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Cell.DA_EnemyFX_Common_Cell",BasicAttackTag=(TagName="FX.Enemy.Common.Cell"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Cell.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Cell.Hit"),DeathTag=(TagName="FX.Enemy.Common.Cell.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Cell/AM_Cell_BasicAttack.AM_Cell_BasicAttack</t>
@@ -213,7 +216,7 @@
     <t>Cursedmass</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Cursedmass.DA_EnemyFX_Common_Cursedmass",BasicAttackTag=(TagName="FX.Enemy.Common.Cursedmass"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Cursedmass.Hit"),DeathTag=(TagName="FX.Enemy.Common.Cursedmass.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Cursedmass.DA_EnemyFX_Common_Cursedmass",BasicAttackTag=(TagName="FX.Enemy.Common.Cursedmass"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Cursedmass.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Cursedmass.Hit"),DeathTag=(TagName="FX.Enemy.Common.Cursedmass.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Cursedmass/AM_Cursedmass_BasicAttack.AM_Cursedmass_BasicAttack</t>
@@ -237,7 +240,7 @@
     <t>DanceMakane</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_DanceMakane.DA_EnemyFX_Common_DanceMakane",BasicAttackTag=(TagName="FX.Enemy.Common.DanceMakane"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.DanceMakane.Hit"),DeathTag=(TagName="FX.Enemy.Common.DanceMakane.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_DanceMakane.DA_EnemyFX_Common_DanceMakane",BasicAttackTag=(TagName="FX.Enemy.Common.DanceMakane"),BasicAttackHitTag=(TagName="FX.Enemy.Common.DanceMakane.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.DanceMakane.Hit"),DeathTag=(TagName="FX.Enemy.Common.DanceMakane.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/DanceMakane/AM_DanceMakane_BasicAttack.AM_DanceMakane_BasicAttack</t>
@@ -261,7 +264,7 @@
     <t>Deatheye</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Deatheye.DA_EnemyFX_Common_Deatheye",BasicAttackTag=(TagName="FX.Enemy.Common.Deatheye"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Deatheye.Hit"),DeathTag=(TagName="FX.Enemy.Common.Deatheye.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Deatheye.DA_EnemyFX_Common_Deatheye",BasicAttackTag=(TagName="FX.Enemy.Common.Deatheye"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Deatheye.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Deatheye.Hit"),DeathTag=(TagName="FX.Enemy.Common.Deatheye.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Deatheye/AM_Deatheye_BasicAttack.AM_Deatheye_BasicAttack</t>
@@ -288,7 +291,7 @@
     <t>DieS</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_DieS.DA_EnemyFX_Common_DieS",BasicAttackTag=(TagName="FX.Enemy.Common.DieS"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.DieS.Hit"),DeathTag=(TagName="FX.Enemy.Common.DieS.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_DieS.DA_EnemyFX_Common_DieS",BasicAttackTag=(TagName="FX.Enemy.Common.DieS"),BasicAttackHitTag=(TagName="FX.Enemy.Common.DieS.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.DieS.Hit"),DeathTag=(TagName="FX.Enemy.Common.DieS.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Dies/AM_DieS_BasicAttack.AM_DieS_BasicAttack</t>
@@ -300,6 +303,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_DieS.Icon_DieS</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Dies/ABP_Dies.ABP_Dies_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/Dies/AM_DieS_Damaged.AM_DieS_Damaged</t>
   </si>
   <si>
@@ -309,7 +315,7 @@
     <t>DoctorMacaron</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_DoctorMacaron.DA_EnemyFX_Common_DoctorMacaron",BasicAttackTag=(TagName="FX.Enemy.Common.DoctorMacaron"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.DoctorMacaron.Hit"),DeathTag=(TagName="FX.Enemy.Common.DoctorMacaron.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_DoctorMacaron.DA_EnemyFX_Common_DoctorMacaron",BasicAttackTag=(TagName="FX.Enemy.Common.DoctorMacaron"),BasicAttackHitTag=(TagName="FX.Enemy.Common.DoctorMacaron.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.DoctorMacaron.Hit"),DeathTag=(TagName="FX.Enemy.Common.DoctorMacaron.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/DoctorMacaron/AM_DoctorMacaron_BasicAttack.AM_DoctorMacaron_BasicAttack</t>
@@ -321,7 +327,7 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_DoctorMacaron.Icon_DoctorMacaron</t>
   </si>
   <si>
-    <t>None</t>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/DoctorMacaron/ABP_DoctorMacaron.ABP_DoctorMacaron_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/DoctorMacaron/AM_DoctorMacaron_Damaged.AM_DoctorMacaron_Damaged</t>
@@ -333,7 +339,7 @@
     <t>Famine</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Famine.DA_EnemyFX_Common_Famine",BasicAttackTag=(TagName="FX.Enemy.Common.Famine"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Famine.Hit"),DeathTag=(TagName="FX.Enemy.Common.Famine.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Famine.DA_EnemyFX_Common_Famine",BasicAttackTag=(TagName="FX.Enemy.Common.Famine"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Famine.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Famine.Hit"),DeathTag=(TagName="FX.Enemy.Common.Famine.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Famine/AM_Famine_BasicAttack.AM_Famine_BasicAttack</t>
@@ -345,6 +351,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Famine.Icon_Famine</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Famine/ABP_Famine.ABP_Famine_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/Famine/AM_Famine_Damaged.AM_Famine_Damaged</t>
   </si>
   <si>
@@ -354,7 +363,7 @@
     <t>FelicisMachine</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_FelicisMachine.DA_EnemyFX_Common_FelicisMachine",BasicAttackTag=(TagName="FX.Enemy.Common.FelicisMachine"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.FelicisMachine.Hit"),DeathTag=(TagName="FX.Enemy.Common.FelicisMachine.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_FelicisMachine.DA_EnemyFX_Common_FelicisMachine",BasicAttackTag=(TagName="FX.Enemy.Common.FelicisMachine"),BasicAttackHitTag=(TagName="FX.Enemy.Common.FelicisMachine.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.FelicisMachine.Hit"),DeathTag=(TagName="FX.Enemy.Common.FelicisMachine.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/FelicisMachine/AM_FelicisMachine_BasicAttack.AM_FelicisMachine_BasicAttack</t>
@@ -366,6 +375,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_FelicisMachine.Icon_FelicisMachine</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/FelicisMachine/ABP_FelicisMachine.ABP_FelicisMachine_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/FelicisMachine/AM_FelicisMachine_Damaged.AM_FelicisMachine_Damaged</t>
   </si>
   <si>
@@ -375,7 +387,7 @@
     <t>FelicisShinobi</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_FelicisShinobi.DA_EnemyFX_Common_FelicisShinobi",BasicAttackTag=(TagName="FX.Enemy.Common.FelicisShinobi"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.FelicisShinobi.Hit"),DeathTag=(TagName="FX.Enemy.Common.FelicisShinobi.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_FelicisShinobi.DA_EnemyFX_Common_FelicisShinobi",BasicAttackTag=(TagName="FX.Enemy.Common.FelicisShinobi"),BasicAttackHitTag=(TagName="FX.Enemy.Common.FelicisShinobi.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.FelicisShinobi.Hit"),DeathTag=(TagName="FX.Enemy.Common.FelicisShinobi.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/FelicisShinobi/AM_FelicisShinobi_BasicAttack.AM_FelicisShinobi_BasicAttack</t>
@@ -387,6 +399,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_FelicisShinobi.Icon_FelicisShinobi</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/FelicisShinobi/ABP_FelicisShinobi.ABP_FelicisShinobi_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/FelicisShinobi/AM_FelicisShinobi_Damaged.AM_FelicisShinobi_Damaged</t>
   </si>
   <si>
@@ -396,7 +411,7 @@
     <t>Fiti</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Fiti.DA_EnemyFX_Common_Fiti",BasicAttackTag=(TagName="FX.Enemy.Common.Fiti"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Fiti.Hit"),DeathTag=(TagName="FX.Enemy.Common.Fiti.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Fiti.DA_EnemyFX_Common_Fiti",BasicAttackTag=(TagName="FX.Enemy.Common.Fiti"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Fiti.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Fiti.Hit"),DeathTag=(TagName="FX.Enemy.Common.Fiti.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Fiti/AM_Fiti_BasicAttack.AM_Fiti_BasicAttack</t>
@@ -405,7 +420,10 @@
     <t>/Game/External_Assets/Monster/Fiti/SKM_Fiti.SKM_Fiti</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Fiti.Icon_Fiti</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_GrafFiti.Icon_GrafFiti</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Fiti/ABP_Fiti.ABP_Fiti_C'</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Fiti/AM_Fiti_Damaged.AM_Fiti_Damaged</t>
@@ -414,10 +432,10 @@
     <t>/Game/Blueprints/Characters/Enemy/Fiti/AM_Fiti_Dead.AM_Fiti_Dead</t>
   </si>
   <si>
-    <t>Gemini_Scythe</t>
-  </si>
-  <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Gemini_Scythe.DA_EnemyFX_Common_Gemini_Scythe",BasicAttackTag=(TagName="FX.Enemy.Common.GeminiScythe"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.GeminiScythe.Hit"),DeathTag=(TagName="FX.Enemy.Common.GeminiScythe.Death"))</t>
+    <t>GeminiScythe</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_GeminiScythe.DA_EnemyFX_Common_GeminiScythe",BasicAttackTag=(TagName="FX.Enemy.Common.GeminiScythe.BasicAttack"),BasicAttackHitTag=(TagName="FX.Enemy.Common.GeminiScythe.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.GeminiScythe.Hit"),DeathTag=(TagName="FX.Enemy.Common.GeminiScythe.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Gemini_Scythe/AM_Gemini_Scythe_BasicAttack.AM_Gemini_Scythe_BasicAttack</t>
@@ -429,6 +447,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Gemini_Scythe.Icon_Gemini_Scythe</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Gemini_Scythe/ABP_Gemini_Scythe.ABP_Gemini_Scythe_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/Gemini_Scythe/AM_Gemini_Scythe_Damaged.AM_Gemini_Scythe_Damaged</t>
   </si>
   <si>
@@ -438,7 +459,7 @@
     <t>GhostMacaron</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_GhostMacaron.DA_EnemyFX_Common_GhostMacaron",BasicAttackTag=(TagName="FX.Enemy.Common.GhostMacaron"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.GhostMacaron.Hit"),DeathTag=(TagName="FX.Enemy.Common.GhostMacaron.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_GhostMacaron.DA_EnemyFX_Common_GhostMacaron",BasicAttackTag=(TagName="FX.Enemy.Common.GhostMacaron"),BasicAttackHitTag=(TagName="FX.Enemy.Common.GhostMacaron.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.GhostMacaron.Hit"),DeathTag=(TagName="FX.Enemy.Common.GhostMacaron.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/GhostMacaron/AM_GhostMacaron_BasicAttack.AM_GhostMacaron_BasicAttack</t>
@@ -450,6 +471,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_GhostMacaron.Icon_GhostMacaron</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/GhostMacaron/ABP_GhostMacaron.ABP_GhostMacaron_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/GhostMacaron/AM_GhostMacaron_Damaged.AM_GhostMacaron_Damaged</t>
   </si>
   <si>
@@ -459,7 +483,7 @@
     <t>Graf</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Graf.DA_EnemyFX_Common_Graf",BasicAttackTag=(TagName="FX.Enemy.Common.Graf"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Graf.Hit"),DeathTag=(TagName="FX.Enemy.Common.Graf.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Graf.DA_EnemyFX_Common_Graf",BasicAttackTag=(TagName="FX.Enemy.Common.Graf"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Graf.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Graf.Hit"),DeathTag=(TagName="FX.Enemy.Common.Graf.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Graf/AM_Graf_BasicAttack.AM_Graf_BasicAttack</t>
@@ -471,6 +495,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Graf.Icon_Graf</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Graf/ABP_Graf.ABP_Graf_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/Graf/AM_Graf_Damaged.AM_Graf_Damaged</t>
   </si>
   <si>
@@ -480,7 +507,13 @@
     <t>GuardianTreant</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Boss/DA_EnemyFX_Boss_GuardianTreant.DA_EnemyFX_Boss_GuardianTreant",BasicAttackTag=(TagName="FX.Enemy.Boss.GuardianTreant"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Boss.GuardianTreant.Hit"),DeathTag=(TagName="FX.Enemy.Boss.GuardianTreant.Death"))</t>
+    <t>((TagName="FX.Enemy.Boss.GuardianTreant.Pattern1"),(TagName="FX.Enemy.Boss.GuardianTreant.Pattern2"))</t>
+  </si>
+  <si>
+    <t>((TagName="FX.Enemy.Boss.GuardianTreant.Pattern1Hit"),(TagName="FX.Enemy.Boss.GuardianTreant.Pattern2Hit"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Boss/DA_EnemyFX_Boss_GuardianTreant.DA_EnemyFX_Boss_GuardianTreant",BasicAttackTag=(TagName="FX.Enemy.Boss.GuardianTreant"),BasicAttackHitTag=(TagName="FX.Enemy.Boss.GuardianTreant.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Boss.GuardianTreant.Hit"),DeathTag=(TagName="FX.Enemy.Boss.GuardianTreant.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/GuardianTreant/AM_GuardianTreant_BasicAttack.AM_GuardianTreant_BasicAttack</t>
@@ -498,6 +531,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_GuardianTreant.Icon_GuardianTreant</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/GuardianTreant/ABP_GuardianTreant.ABP_GuardianTreant_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/GuardianTreant/AM_GuardianTreant_Damaged.AM_GuardianTreant_Damaged</t>
   </si>
   <si>
@@ -507,7 +543,7 @@
     <t>HackingTool</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_HackingTool.DA_EnemyFX_Common_HackingTool",BasicAttackTag=(TagName="FX.Enemy.Common.HackingTool"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.HackingTool.Hit"),DeathTag=(TagName="FX.Enemy.Common.HackingTool.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_HackingTool.DA_EnemyFX_Common_HackingTool",BasicAttackTag=(TagName="FX.Enemy.Common.HackingTool"),BasicAttackHitTag=(TagName="FX.Enemy.Common.HackingTool.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.HackingTool.Hit"),DeathTag=(TagName="FX.Enemy.Common.HackingTool.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/HackingTool/AM_HackingTool_BasicAttack.AM_HackingTool_BasicAttack</t>
@@ -519,6 +555,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_HackingTool.Icon_HackingTool</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/HackingTool/ABP_HackingTool.ABP_HackingTool_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/HackingTool/AM_HackingTool_Damaged.AM_HackingTool_Damaged</t>
   </si>
   <si>
@@ -528,7 +567,7 @@
     <t>HoneyMos</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_HoneyMos.DA_EnemyFX_Common_HoneyMos",BasicAttackTag=(TagName="FX.Enemy.Common.HoneyMos"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.HoneyMos.Hit"),DeathTag=(TagName="FX.Enemy.Common.HoneyMos.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_HoneyMos.DA_EnemyFX_Common_HoneyMos",BasicAttackTag=(TagName="FX.Enemy.Common.HoneyMos"),BasicAttackHitTag=(TagName="FX.Enemy.Common.HoneyMos.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.HoneyMos.Hit"),DeathTag=(TagName="FX.Enemy.Common.HoneyMos.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/HoneyMos/AM_HoneyMos_BasicAttack.AM_HoneyMos_BasicAttack</t>
@@ -540,6 +579,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_HoneyMos.Icon_HoneyMos</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/HoneyMos/ABP_HoneyMos.ABP_HoneyMos_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/HoneyMos/AM_HoneyMos_Damaged.AM_HoneyMos_Damaged</t>
   </si>
   <si>
@@ -549,7 +591,7 @@
     <t>Jellyfish</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Jellyfish.DA_EnemyFX_Common_Jellyfish",BasicAttackTag=(TagName="FX.Enemy.Common.Jellyfish"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Jellyfish.Hit"),DeathTag=(TagName="FX.Enemy.Common.Jellyfish.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Jellyfish.DA_EnemyFX_Common_Jellyfish",BasicAttackTag=(TagName="FX.Enemy.Common.Jellyfish"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Jellyfish.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Jellyfish.Hit"),DeathTag=(TagName="FX.Enemy.Common.Jellyfish.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Jellyfish/AM_JellyFish_BasicAttack.AM_JellyFish_BasicAttack</t>
@@ -561,6 +603,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Jellyfish.Icon_Jellyfish</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Jellyfish/ABP_Jellyfish.ABP_Jellyfish_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/Jellyfish/AM_JellyFish_Damaged.AM_JellyFish_Damaged</t>
   </si>
   <si>
@@ -570,7 +615,7 @@
     <t>Karakasa</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Karakasa.DA_EnemyFX_Common_Karakasa",BasicAttackTag=(TagName="FX.Enemy.Common.Karakasa"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Karakasa.Hit"),DeathTag=(TagName="FX.Enemy.Common.Karakasa.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Karakasa.DA_EnemyFX_Common_Karakasa",BasicAttackTag=(TagName="FX.Enemy.Common.Karakasa"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Karakasa.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Karakasa.Hit"),DeathTag=(TagName="FX.Enemy.Common.Karakasa.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Karakasa/AM_Karakasa_BasicAttack.AM_Karakasa_BasicAttack</t>
@@ -582,6 +627,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Karakasa.Icon_Karakasa</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Karakasa/ABP_Karakasa.ABP_Karakasa_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/Karakasa/AM_Karakasa_Damaged.AM_Karakasa_Damaged</t>
   </si>
   <si>
@@ -591,7 +639,7 @@
     <t>Kraken</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Kraken.DA_EnemyFX_Common_Kraken",BasicAttackTag=(TagName="FX.Enemy.Common.Kraken"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Kraken.Hit"),DeathTag=(TagName="FX.Enemy.Common.Kraken.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Kraken.DA_EnemyFX_Common_Kraken",BasicAttackTag=(TagName="FX.Enemy.Common.Kraken"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Kraken.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Kraken.Hit"),DeathTag=(TagName="FX.Enemy.Common.Kraken.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Kraken/AM_Kraken_BasicAttack.AM_Kraken_BasicAttack</t>
@@ -603,6 +651,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Kraken.Icon_Kraken</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Kraken/ABP_Kraken.ABP_Kraken_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/Kraken/AM_Kraken_Damaged.AM_Kraken_Damaged</t>
   </si>
   <si>
@@ -612,7 +663,7 @@
     <t>LikeStatue</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_LikeStatue.DA_EnemyFX_Common_LikeStatue",BasicAttackTag=(TagName="FX.Enemy.Common.LikeStatue"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.LikeStatue.Hit"),DeathTag=(TagName="FX.Enemy.Common.LikeStatue.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_LikeStatue.DA_EnemyFX_Common_LikeStatue",BasicAttackTag=(TagName="FX.Enemy.Common.LikeStatue"),BasicAttackHitTag=(TagName="FX.Enemy.Common.LikeStatue.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.LikeStatue.Hit"),DeathTag=(TagName="FX.Enemy.Common.LikeStatue.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/LikeStatue/AM_LikeStatue2_BasicAttack.AM_LikeStatue2_BasicAttack</t>
@@ -624,6 +675,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_LikeStatue.Icon_LikeStatue</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/LikeStatue/ABP_LikeStatue.ABP_LikeStatue_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/LikeStatue/AM_LikeStatue2_Damaged.AM_LikeStatue2_Damaged</t>
   </si>
   <si>
@@ -633,7 +687,7 @@
     <t>LordFelice</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_LordFelice.DA_EnemyFX_Common_LordFelice",BasicAttackTag=(TagName="FX.Enemy.Common.LordFelice"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.LordFelice.Hit"),DeathTag=(TagName="FX.Enemy.Common.LordFelice.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_LordFelice.DA_EnemyFX_Common_LordFelice",BasicAttackTag=(TagName="FX.Enemy.Common.LordFelice"),BasicAttackHitTag=(TagName="FX.Enemy.Common.LordFelice.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.LordFelice.Hit"),DeathTag=(TagName="FX.Enemy.Common.LordFelice.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/LordFelice/AM_LordFelice_BasicAttack.AM_LordFelice_BasicAttack</t>
@@ -645,6 +699,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_LordFelice.Icon_LordFelice</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/LordFelice/ABP_LordFelice.ABP_LordFelice_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/LordFelice/AM_LordFelice_Damaged.AM_LordFelice_Damaged</t>
   </si>
   <si>
@@ -654,7 +711,7 @@
     <t>Mandragora</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Mandragora.DA_EnemyFX_Common_Mandragora",BasicAttackTag=(TagName="FX.Enemy.Common.Mandragora"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Mandragora.Hit"),DeathTag=(TagName="FX.Enemy.Common.Mandragora.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Mandragora.DA_EnemyFX_Common_Mandragora",BasicAttackTag=(TagName="FX.Enemy.Common.Mandragora"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Mandragora.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Mandragora.Hit"),DeathTag=(TagName="FX.Enemy.Common.Mandragora.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Mandragora/AM_Mandragora_BasicAttack.AM_Mandragora_BasicAttack</t>
@@ -666,6 +723,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Mandragora.Icon_Mandragora</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Mandragora/ABP_Mandragora.ABP_Mandragora_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/Mandragora/AM_Mandragora_Damaged.AM_Mandragora_Damaged</t>
   </si>
   <si>
@@ -675,7 +735,7 @@
     <t>Mask</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Mask.DA_EnemyFX_Common_Mask",BasicAttackTag=(TagName="FX.Enemy.Common.Mask"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Mask.Hit"),DeathTag=(TagName="FX.Enemy.Common.Mask.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Mask.DA_EnemyFX_Common_Mask",BasicAttackTag=(TagName="FX.Enemy.Common.Mask"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Mask.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Mask.Hit"),DeathTag=(TagName="FX.Enemy.Common.Mask.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Mask/AM_Mask_BasicAttack.AM_Mask_BasicAttack</t>
@@ -687,6 +747,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_MaskScarecrow.Icon_MaskScarecrow</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Mask/ABP_Mask.ABP_Mask_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/Mask/AM_Mask_Damaged.AM_Mask_Damaged</t>
   </si>
   <si>
@@ -696,7 +759,10 @@
     <t>Mechanicus</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Mechanicus.DA_EnemyFX_Common_Mechanicus",BasicAttackTag=(TagName="FX.Enemy.Common.Mechanicus"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Mechanicus.Hit"),DeathTag=(TagName="FX.Enemy.Common.Mechanicus.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Mechanicus.DA_EnemyFX_Common_Mechanicus",BasicAttackTag=(TagName="FX.Enemy.Common.Mechanicus"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Mechanicus.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Mechanicus.Hit"),DeathTag=(TagName="FX.Enemy.Common.Mechanicus.Death"))</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Mechanicus/AM_Mechanicus_BasicAttack.AM_Mechanicus_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Mechanicus/SKM_Mechanicus.SKM_Mechanicus</t>
@@ -705,10 +771,25 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Mechanicus.Icon_Mechanicus</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Mechanicus/ABP_Mechanicus.ABP_Mechanicus_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Mechanicus/AM_Mechanicus_Damaged.AM_Mechanicus_Damaged</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Mechanicus/AM_Mechanicus_Dead.AM_Mechanicus_Dead</t>
+  </si>
+  <si>
     <t>Megaron</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Boss/DA_EnemyFX_Boss_Megaron.DA_EnemyFX_Boss_Megaron",BasicAttackTag=(TagName="FX.Enemy.Boss.Megaron"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Boss.Megaron.Hit"),DeathTag=(TagName="FX.Enemy.Boss.Megaron.Death"))</t>
+    <t>((TagName="FX.Enemy.Boss.Megaron.Pattern1"),(TagName="FX.Enemy.Boss.Megaron.Pattern2"))</t>
+  </si>
+  <si>
+    <t>((TagName="FX.Enemy.Boss.Megaron.Pattern1Hit"),(TagName="FX.Enemy.Boss.Megaron.Pattern2Hit"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Boss/DA_EnemyFX_Boss_Megaron.DA_EnemyFX_Boss_Megaron",BasicAttackTag=(TagName="FX.Enemy.Boss.Megaron"),BasicAttackHitTag=(TagName="FX.Enemy.Boss.Megaron.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Boss.Megaron.Hit"),DeathTag=(TagName="FX.Enemy.Boss.Megaron.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Megaron/AM_Megaron_BasicAttack.AM_Megaron_BasicAttack</t>
@@ -726,6 +807,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Megaron.Icon_Megaron</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Megaron/ABP_Megaron.ABP_Megaron_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/Megaron/AM_Megaron_Damaged.AM_Megaron_Damaged</t>
   </si>
   <si>
@@ -735,7 +819,7 @@
     <t>Mimic</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Mimic.DA_EnemyFX_Common_Mimic",BasicAttackTag=(TagName="FX.Enemy.Common.Mimic"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Mimic.Hit"),DeathTag=(TagName="FX.Enemy.Common.Mimic.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Mimic.DA_EnemyFX_Common_Mimic",BasicAttackTag=(TagName="FX.Enemy.Common.Mimic"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Mimic.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Mimic.Hit"),DeathTag=(TagName="FX.Enemy.Common.Mimic.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Mimic/AM_Mimic_BasicAttack.AM_Mimic_BasicAttack</t>
@@ -747,6 +831,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Mimic.Icon_Mimic</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Mimic/ABP_Mimic.ABP_Mimic_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/Mimic/AM_Mimic_Damaged.AM_Mimic_Damaged</t>
   </si>
   <si>
@@ -756,7 +843,7 @@
     <t>Octopus</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Octopus.DA_EnemyFX_Common_Octopus",BasicAttackTag=(TagName="FX.Enemy.Common.Octopus"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Octopus.Hit"),DeathTag=(TagName="FX.Enemy.Common.Octopus.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Octopus.DA_EnemyFX_Common_Octopus",BasicAttackTag=(TagName="FX.Enemy.Common.Octopus"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Octopus.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Octopus.Hit"),DeathTag=(TagName="FX.Enemy.Common.Octopus.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Octopus/AM_Octopus_BasicAttack.AM_Octopus_BasicAttack</t>
@@ -768,6 +855,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Octopus.Icon_Octopus</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Octopus/ABP_Octopus.ABP_Octopus_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/Octopus/AM_Octopus_Damaged.AM_Octopus_Damaged</t>
   </si>
   <si>
@@ -777,7 +867,7 @@
     <t>PistolShrimp</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_PistolShrimp.DA_EnemyFX_Common_PistolShrimp",BasicAttackTag=(TagName="FX.Enemy.Common.PistolShrimp"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.PistolShrimp.Hit"),DeathTag=(TagName="FX.Enemy.Common.PistolShrimp.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_PistolShrimp.DA_EnemyFX_Common_PistolShrimp",BasicAttackTag=(TagName="FX.Enemy.Common.PistolShrimp"),BasicAttackHitTag=(TagName="FX.Enemy.Common.PistolShrimp.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.PistolShrimp.Hit"),DeathTag=(TagName="FX.Enemy.Common.PistolShrimp.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/PistolShrimp/AM_PistolShrimp_BasicAttack.AM_PistolShrimp_BasicAttack</t>
@@ -789,6 +879,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_PistolShrimp.Icon_PistolShrimp</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/PistolShrimp/ABP_PistolShrimp.ABP_PistolShrimp_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/PistolShrimp/AM_PistolShrimp_Damaged.AM_PistolShrimp_Damaged</t>
   </si>
   <si>
@@ -798,7 +891,7 @@
     <t>Pufferfish</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Pufferfish.DA_EnemyFX_Common_Pufferfish",BasicAttackTag=(TagName="FX.Enemy.Common.Pufferfish"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Pufferfish.Hit"),DeathTag=(TagName="FX.Enemy.Common.Pufferfish.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Pufferfish.DA_EnemyFX_Common_Pufferfish",BasicAttackTag=(TagName="FX.Enemy.Common.Pufferfish"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Pufferfish.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Pufferfish.Hit"),DeathTag=(TagName="FX.Enemy.Common.Pufferfish.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Pufferfish/AM_Pufferfish_BasicAttack.AM_Pufferfish_BasicAttack</t>
@@ -810,6 +903,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Pufferfish.Icon_Pufferfish</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Pufferfish/ABP_Pufferfish.ABP_Pufferfish_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/Pufferfish/AM_Pufferfish_Damaged.AM_Pufferfish_Damaged</t>
   </si>
   <si>
@@ -819,7 +915,7 @@
     <t>Seasoner</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Seasoner.DA_EnemyFX_Common_Seasoner",BasicAttackTag=(TagName="FX.Enemy.Common.Seasoner"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Seasoner.Hit"),DeathTag=(TagName="FX.Enemy.Common.Seasoner.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Seasoner.DA_EnemyFX_Common_Seasoner",BasicAttackTag=(TagName="FX.Enemy.Common.Seasoner"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Seasoner.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Seasoner.Hit"),DeathTag=(TagName="FX.Enemy.Common.Seasoner.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Seasoner/AM_Seasoner_BasicAttack.AM_Seasoner_BasicAttack</t>
@@ -831,6 +927,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Seasoner.Icon_Seasoner</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Seasoner/ABP_Seasoner.ABP_Seasoner_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/Seasoner/AM_Seasoner_Damaged.AM_Seasoner_Damaged</t>
   </si>
   <si>
@@ -840,7 +939,7 @@
     <t>SharkRider</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_SharkRider.DA_EnemyFX_Common_SharkRider",BasicAttackTag=(TagName="FX.Enemy.Common.SharkRider"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.SharkRider.Hit"),DeathTag=(TagName="FX.Enemy.Common.SharkRider.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_SharkRider.DA_EnemyFX_Common_SharkRider",BasicAttackTag=(TagName="FX.Enemy.Common.SharkRider"),BasicAttackHitTag=(TagName="FX.Enemy.Common.SharkRider.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.SharkRider.Hit"),DeathTag=(TagName="FX.Enemy.Common.SharkRider.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/SharkRider/AM_SharkRider_BasicAttack.AM_SharkRider_BasicAttack</t>
@@ -852,6 +951,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_SharkRider.Icon_SharkRider</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/SharkRider/ABP_SharkRider.ABP_SharkRider_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/SharkRider/AM_SharkRider_Damaged.AM_SharkRider_Damaged</t>
   </si>
   <si>
@@ -861,7 +963,10 @@
     <t>Starspawn</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Starspawn.DA_EnemyFX_Common_Starspawn",BasicAttackTag=(TagName="FX.Enemy.Common.Starspawn"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Starspawn.Hit"),DeathTag=(TagName="FX.Enemy.Common.Starspawn.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Starspawn.DA_EnemyFX_Common_Starspawn",BasicAttackTag=(TagName="FX.Enemy.Common.Starspawn"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Starspawn.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Starspawn.Hit"),DeathTag=(TagName="FX.Enemy.Common.Starspawn.Death"))</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Starspawn/AM_Starspawn_BasicAttack.AM_Starspawn_BasicAttack</t>
   </si>
   <si>
     <t>/Game/External_Assets/Monster/Starspawn/SKM_Starspawn.SKM_Starspawn</t>
@@ -870,10 +975,19 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Starspawn.Icon_Starspawn</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Starspawn/ABP_Starspawn.ABP_Starspawn_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Starspawn/AM_Starspawn_Damaged.AM_Starspawn_Damaged</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Enemy/Starspawn/AM_Starspawn_Dead.AM_Starspawn_Dead</t>
+  </si>
+  <si>
     <t>Ushabti</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Ushabti.DA_EnemyFX_Common_Ushabti",BasicAttackTag=(TagName="FX.Enemy.Common.Ushabti"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Ushabti.Hit"),DeathTag=(TagName="FX.Enemy.Common.Ushabti.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Ushabti.DA_EnemyFX_Common_Ushabti",BasicAttackTag=(TagName="FX.Enemy.Common.Ushabti"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Ushabti.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Ushabti.Hit"),DeathTag=(TagName="FX.Enemy.Common.Ushabti.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Ushabti/AM_Ushabti_BasicAttack.AM_Ushabti_BasicAttack</t>
@@ -885,6 +999,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Ushabti.Icon_Ushabti</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Ushabti/ABP_Ushabti.ABP_Ushabti_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/Ushabti/AM_Ushabti_Damaged.AM_Ushabti_Damaged</t>
   </si>
   <si>
@@ -894,7 +1011,7 @@
     <t>Wagon</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Wagon.DA_EnemyFX_Common_Wagon",BasicAttackTag=(TagName="FX.Enemy.Common.Wagon"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Wagon.Hit"),DeathTag=(TagName="FX.Enemy.Common.Wagon.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Wagon.DA_EnemyFX_Common_Wagon",BasicAttackTag=(TagName="FX.Enemy.Common.Wagon"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Wagon.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Wagon.Hit"),DeathTag=(TagName="FX.Enemy.Common.Wagon.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Wagon/AM_Wagon_BasicAttack.AM_Wagon_BasicAttack</t>
@@ -906,6 +1023,9 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Wagon.Icon_Wagon</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Wagon/ABP_Wagon.ABP_Wagon_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/Wagon/AM_Wagon_Damaged.AM_Wagon_Damaged</t>
   </si>
   <si>
@@ -915,7 +1035,7 @@
     <t>Watcher</t>
   </si>
   <si>
-    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Watcher.DA_EnemyFX_Common_Watcher",BasicAttackTag=(TagName="FX.Enemy.Common.Watcher"),BasicAttackHitTag=(TagName=""),HitTag=(TagName="FX.Enemy.Common.Watcher.Hit"),DeathTag=(TagName="FX.Enemy.Common.Watcher.Death"))</t>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Common/DA_EnemyFX_Common_Watcher.DA_EnemyFX_Common_Watcher",BasicAttackTag=(TagName="FX.Enemy.Common.Watcher"),BasicAttackHitTag=(TagName="FX.Enemy.Common.Watcher.BasicAttackHit"),HitTag=(TagName="FX.Enemy.Common.Watcher.Hit"),DeathTag=(TagName="FX.Enemy.Common.Watcher.Death"))</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Watcher/AM_Watcher_BasicAttack.AM_Watcher_BasicAttack</t>
@@ -927,104 +1047,13 @@
     <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Watcher.Icon_Watcher</t>
   </si>
   <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Watcher/ABP_Watcher.ABP_Watcher_C'</t>
+  </si>
+  <si>
     <t>/Game/Blueprints/Characters/Enemy/Watcher/AM_Watcher_Damaged.AM_Watcher_Damaged</t>
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Watcher/AM_Watcher_Dead.AM_Watcher_Dead</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Dies/ABP_Dies.ABP_Dies_C'</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/DoctorMacaron/ABP_DoctorMacaron.ABP_DoctorMacaron_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Famine/ABP_Famine.ABP_Famine_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/FelicisMachine/ABP_FelicisMachine.ABP_FelicisMachine_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/FelicisShinobi/ABP_FelicisShinobi.ABP_FelicisShinobi_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Fiti/ABP_Fiti.ABP_Fiti_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Gemini_Scythe/ABP_Gemini_Scythe.ABP_Gemini_Scythe_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/GhostMacaron/ABP_GhostMacaron.ABP_GhostMacaron_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Graf/ABP_Graf.ABP_Graf_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/GuardianTreant/ABP_GuardianTreant.ABP_GuardianTreant_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/HackingTool/ABP_HackingTool.ABP_HackingTool_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/HoneyMos/ABP_HoneyMos.ABP_HoneyMos_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Jellyfish/ABP_Jellyfish.ABP_Jellyfish_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Karakasa/ABP_Karakasa.ABP_Karakasa_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Kraken/ABP_Kraken.ABP_Kraken_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/LikeStatue/ABP_LikeStatue.ABP_LikeStatue_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/LordFelice/ABP_LordFelice.ABP_LordFelice_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Mandragora/ABP_Mandragora.ABP_Mandragora_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Mask/ABP_Mask.ABP_Mask_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Mechanicus/ABP_Mechanicus.ABP_Mechanicus_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Megaron/ABP_Megaron.ABP_Megaron_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Mimic/ABP_Mimic.ABP_Mimic_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Octopus/ABP_Octopus.ABP_Octopus_C'</t>
-  </si>
-  <si>
-    <t>/Script/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/PistolShrimp/ABP_PistolShrimp.ABP_PistolShrimp_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Pufferfish/ABP_Pufferfish.ABP_Pufferfish_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Seasoner/ABP_Seasoner.ABP_Seasoner_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/SharkRider/ABP_SharkRider.ABP_SharkRider_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Starspawn/ABP_Starspawn.ABP_Starspawn_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Ushabti/ABP_Ushabti.ABP_Ushabti_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Wagon/ABP_Wagon.ABP_Wagon_C'</t>
-  </si>
-  <si>
-    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Watcher/ABP_Watcher.ABP_Watcher_C'</t>
   </si>
 </sst>
 </file>
@@ -2005,1699 +2034,1720 @@
       <c r="A2" t="s">
         <v>18</v>
       </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <v>1.3</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
       </c>
       <c r="D3">
         <v>0.8</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4">
         <v>0.8</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D6">
         <v>1.5</v>
       </c>
       <c r="E6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Q6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7">
         <v>1.8</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="R8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D9">
         <v>0.8</v>
       </c>
       <c r="E9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P9" t="s">
-        <v>304</v>
+        <v>94</v>
       </c>
       <c r="Q9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="R9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D10">
         <v>0.3</v>
       </c>
       <c r="E10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="P10" t="s">
-        <v>305</v>
+        <v>102</v>
       </c>
       <c r="Q10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D11">
         <v>1.2</v>
       </c>
       <c r="E11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="P11" t="s">
-        <v>306</v>
+        <v>110</v>
       </c>
       <c r="Q11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="R11" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F12" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N12" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="O12" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="P12" t="s">
-        <v>307</v>
+        <v>118</v>
       </c>
       <c r="Q12" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="R12" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D13">
         <v>0.5</v>
       </c>
       <c r="E13" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F13" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N13" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="O13" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="P13" t="s">
-        <v>308</v>
+        <v>126</v>
       </c>
       <c r="Q13" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="R13" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D14">
         <v>0.4</v>
       </c>
       <c r="E14" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F14" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N14" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="O14" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="P14" t="s">
-        <v>309</v>
+        <v>134</v>
       </c>
       <c r="Q14" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="R14" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D15">
         <v>1.3</v>
       </c>
       <c r="E15" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F15" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="H15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N15" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="O15" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="P15" t="s">
-        <v>310</v>
+        <v>142</v>
       </c>
       <c r="Q15" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="R15" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D16">
         <v>1.2</v>
       </c>
       <c r="E16" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="F16" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="H16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N16" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="O16" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="P16" t="s">
-        <v>311</v>
+        <v>150</v>
       </c>
       <c r="Q16" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="R16" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D17">
         <v>0.4</v>
       </c>
       <c r="E17" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F17" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="H17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N17" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="O17" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="P17" t="s">
-        <v>312</v>
+        <v>158</v>
       </c>
       <c r="Q17" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="R17" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>152</v>
+        <v>161</v>
+      </c>
+      <c r="B18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" t="s">
+        <v>163</v>
       </c>
       <c r="D18">
         <v>0.8</v>
       </c>
       <c r="E18" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="F18" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="G18" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="H18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L18" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="M18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N18" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="O18" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="P18" t="s">
-        <v>313</v>
+        <v>170</v>
       </c>
       <c r="Q18" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="R18" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D19">
         <v>0.3</v>
       </c>
       <c r="E19" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="F19" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="H19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N19" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="O19" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="P19" t="s">
-        <v>314</v>
+        <v>178</v>
       </c>
       <c r="Q19" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="R19" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="F20" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="H20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N20" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="O20" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="P20" t="s">
-        <v>315</v>
+        <v>186</v>
       </c>
       <c r="Q20" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="R20" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D21">
         <v>0.9</v>
       </c>
       <c r="E21" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="F21" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="H21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N21" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="O21" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="P21" t="s">
-        <v>316</v>
+        <v>194</v>
       </c>
       <c r="Q21" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="R21" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="D22">
         <v>0.6</v>
       </c>
       <c r="E22" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="F22" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="H22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N22" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="O22" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="P22" t="s">
-        <v>317</v>
+        <v>202</v>
       </c>
       <c r="Q22" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="R22" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="D23">
         <v>0.3</v>
       </c>
       <c r="E23" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="F23" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="H23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N23" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="O23" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="P23" t="s">
-        <v>318</v>
+        <v>210</v>
       </c>
       <c r="Q23" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="R23" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="D24">
         <v>0.7</v>
       </c>
       <c r="E24" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="F24" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="H24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N24" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="O24" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="P24" t="s">
-        <v>319</v>
+        <v>218</v>
       </c>
       <c r="Q24" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="R24" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="D25">
         <v>0.3</v>
       </c>
       <c r="E25" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="F25" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="H25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M25" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N25" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="O25" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="P25" t="s">
-        <v>320</v>
+        <v>226</v>
       </c>
       <c r="Q25" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="R25" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="D26">
         <v>1.5</v>
       </c>
       <c r="E26" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="F26" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="H26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N26" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="O26" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="P26" t="s">
-        <v>321</v>
+        <v>234</v>
       </c>
       <c r="Q26" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="R26" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="D27">
         <v>1.2</v>
       </c>
       <c r="E27" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="F27" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="H27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N27" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="O27" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="P27" t="s">
-        <v>322</v>
+        <v>242</v>
       </c>
       <c r="Q27" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="R27" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="D28">
         <v>1.5</v>
       </c>
       <c r="E28" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="F28" t="s">
-        <v>100</v>
+        <v>247</v>
       </c>
       <c r="H28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N28" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="O28" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="P28" t="s">
-        <v>323</v>
+        <v>250</v>
       </c>
       <c r="Q28" t="s">
-        <v>100</v>
+        <v>251</v>
       </c>
       <c r="R28" t="s">
-        <v>100</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>228</v>
+        <v>253</v>
+      </c>
+      <c r="B29" t="s">
+        <v>254</v>
+      </c>
+      <c r="C29" t="s">
+        <v>255</v>
       </c>
       <c r="D29">
         <v>2.5</v>
       </c>
       <c r="E29" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="F29" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="G29" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="H29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L29" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="M29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N29" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="O29" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="P29" t="s">
-        <v>324</v>
+        <v>262</v>
       </c>
       <c r="Q29" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="R29" t="s">
-        <v>236</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="D30">
         <v>0.5</v>
       </c>
       <c r="E30" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="F30" t="s">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="H30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N30" t="s">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="O30" t="s">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="P30" t="s">
-        <v>325</v>
+        <v>270</v>
       </c>
       <c r="Q30" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="R30" t="s">
-        <v>243</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="D31">
         <v>1.2</v>
       </c>
       <c r="E31" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="F31" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="H31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N31" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="O31" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="P31" t="s">
-        <v>326</v>
+        <v>278</v>
       </c>
       <c r="Q31" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="R31" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="D32">
         <v>0.6</v>
       </c>
       <c r="E32" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="F32" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="H32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N32" t="s">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="O32" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="P32" t="s">
-        <v>327</v>
+        <v>286</v>
       </c>
       <c r="Q32" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="R32" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>258</v>
+        <v>289</v>
       </c>
       <c r="D33">
         <v>0.6</v>
       </c>
       <c r="E33" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
       <c r="F33" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="H33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N33" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="O33" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="P33" t="s">
-        <v>328</v>
+        <v>294</v>
       </c>
       <c r="Q33" t="s">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="R33" t="s">
-        <v>264</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>265</v>
+        <v>297</v>
       </c>
       <c r="D34">
         <v>1.4</v>
       </c>
       <c r="E34" t="s">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="F34" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="H34" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M34" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N34" t="s">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="O34" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="P34" t="s">
-        <v>329</v>
+        <v>302</v>
       </c>
       <c r="Q34" t="s">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c r="R34" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="D35">
         <v>0.4</v>
       </c>
       <c r="E35" t="s">
-        <v>273</v>
+        <v>306</v>
       </c>
       <c r="F35" t="s">
-        <v>274</v>
+        <v>307</v>
       </c>
       <c r="H35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M35" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N35" t="s">
-        <v>275</v>
+        <v>308</v>
       </c>
       <c r="O35" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="P35" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="Q35" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="R35" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>279</v>
+        <v>313</v>
       </c>
       <c r="D36">
         <v>2</v>
       </c>
       <c r="E36" t="s">
-        <v>280</v>
+        <v>314</v>
       </c>
       <c r="F36" t="s">
-        <v>100</v>
+        <v>315</v>
       </c>
       <c r="H36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J36" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N36" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="O36" t="s">
-        <v>282</v>
+        <v>317</v>
       </c>
       <c r="P36" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="Q36" t="s">
-        <v>100</v>
+        <v>319</v>
       </c>
       <c r="R36" t="s">
-        <v>100</v>
+        <v>320</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="F37" t="s">
-        <v>285</v>
+        <v>323</v>
       </c>
       <c r="H37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M37" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N37" t="s">
-        <v>286</v>
+        <v>324</v>
       </c>
       <c r="O37" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="P37" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="Q37" t="s">
-        <v>288</v>
+        <v>327</v>
       </c>
       <c r="R37" t="s">
-        <v>289</v>
+        <v>328</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>290</v>
+        <v>329</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>291</v>
+        <v>330</v>
       </c>
       <c r="F38" t="s">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="H38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N38" t="s">
-        <v>293</v>
+        <v>332</v>
       </c>
       <c r="O38" t="s">
-        <v>294</v>
+        <v>333</v>
       </c>
       <c r="P38" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q38" t="s">
-        <v>295</v>
+        <v>335</v>
       </c>
       <c r="R38" t="s">
-        <v>296</v>
+        <v>336</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>297</v>
+        <v>337</v>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>298</v>
+        <v>338</v>
       </c>
       <c r="F39" t="s">
-        <v>299</v>
+        <v>339</v>
       </c>
       <c r="H39" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M39" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N39" t="s">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="O39" t="s">
-        <v>301</v>
+        <v>341</v>
       </c>
       <c r="P39" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="Q39" t="s">
-        <v>302</v>
+        <v>343</v>
       </c>
       <c r="R39" t="s">
-        <v>303</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/EnemyAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/EnemyAssets_Master.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="357">
   <si>
     <t>---</t>
   </si>
@@ -225,7 +225,7 @@
     <t>/Game/External_Assets/Monster/Cursedmass/SKM_Cursedmass.SKM_Cursedmass</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Monster/Cursedmass/Material/T_Cursedmas_A_Ball.T_Cursedmas_A_Ball</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Cursedmass.Cursedmass</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Cursedmass/ABP_Cursedmass.ABP_Cursedmass_C'</t>
@@ -249,7 +249,7 @@
     <t>/Game/External_Assets/Monster/DanceMakane/SKM_DanceMakane.SKM_DanceMakane</t>
   </si>
   <si>
-    <t>/Game/External_Assets/Monster/DanceMakane/Material/T_DanceMakane_Type_A.T_DanceMakane_Type_A</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/DanceMakane.DanceMakane</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/DanceMakane/ABP_DanceMakane.ABP_DanceMakane_C'</t>
@@ -300,7 +300,7 @@
     <t>/Game/External_Assets/Monster/DieS/SKM_DieS.SKM_DieS</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_DieS.Icon_DieS</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/DieS.DieS</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Dies/ABP_Dies.ABP_Dies_C'</t>
@@ -324,7 +324,7 @@
     <t>/Game/External_Assets/Monster/DoctorMacaron/SKM_DoctorMacaron.SKM_DoctorMacaron</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_DoctorMacaron.Icon_DoctorMacaron</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/DoctorMacaron.DoctorMacaron</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/DoctorMacaron/ABP_DoctorMacaron.ABP_DoctorMacaron_C'</t>
@@ -372,7 +372,7 @@
     <t>/Game/External_Assets/Monster/FelicisMachine/SKM_FelicisMachine.SKM_FelicisMachine</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_FelicisMachine.Icon_FelicisMachine</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/FelicisMachine.FelicisMachine</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/FelicisMachine/ABP_FelicisMachine.ABP_FelicisMachine_C'</t>
@@ -444,7 +444,7 @@
     <t>/Game/External_Assets/Monster/Gemini_Scythe/SKM_Gemini_Scythe.SKM_Gemini_Scythe</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Gemini_Scythe.Icon_Gemini_Scythe</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_GeminiScythe.Icon_GeminiScythe</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Gemini_Scythe/ABP_Gemini_Scythe.ABP_Gemini_Scythe_C'</t>
@@ -468,7 +468,7 @@
     <t>/Game/External_Assets/Monster/GhostMacaron/SKM_Ghostmacaron.SKM_Ghostmacaron</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_GhostMacaron.Icon_GhostMacaron</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/GhostMacaron.GhostMacaron</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/GhostMacaron/ABP_GhostMacaron.ABP_GhostMacaron_C'</t>
@@ -492,7 +492,7 @@
     <t>/Game/External_Assets/Monster/Graf/SKM_Graf.SKM_Graf</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Graf.Icon_Graf</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_GrafFiti_B.Icon_GrafFiti_B</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Graf/ABP_Graf.ABP_Graf_C'</t>
@@ -576,7 +576,7 @@
     <t>/Game/External_Assets/Monster/HoneyMos/SKM_HoneyMos.SKM_HoneyMos</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_HoneyMos.Icon_HoneyMos</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/HoneyMos.HoneyMos</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/HoneyMos/ABP_HoneyMos.ABP_HoneyMos_C'</t>
@@ -600,7 +600,7 @@
     <t>/Game/External_Assets/Monster/Jellyfish/SKM_JellyFish.SKM_JellyFish</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Jellyfish.Icon_Jellyfish</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Jellyfish.Jellyfish</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Jellyfish/ABP_Jellyfish.ABP_Jellyfish_C'</t>
@@ -624,7 +624,7 @@
     <t>/Game/External_Assets/Monster/Karakasa/SKM_Karakasa.SKM_Karakasa</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Karakasa.Icon_Karakasa</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Karakasa.Karakasa</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Karakasa/ABP_Karakasa.ABP_Karakasa_C'</t>
@@ -672,7 +672,7 @@
     <t>/Game/External_Assets/Monster/LikeStatue/SKM_LikeStatue2.SKM_LikeStatue2</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_LikeStatue.Icon_LikeStatue</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Boss_LikeStatue_D.Icon_Boss_LikeStatue_D</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/LikeStatue/ABP_LikeStatue.ABP_LikeStatue_C'</t>
@@ -720,7 +720,7 @@
     <t>/Game/External_Assets/Monster/Mandragora/SKM_Mandragora.SKM_Mandragora</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Mandragora.Icon_Mandragora</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Mandragora.Mandragora</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Mandragora/ABP_Mandragora.ABP_Mandragora_C'</t>
@@ -744,7 +744,7 @@
     <t>/Game/External_Assets/Monster/Mask/SKM_Mask.SKM_Mask</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_MaskScarecrow.Icon_MaskScarecrow</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Mask.Mask</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Mask/ABP_Mask.ABP_Mask_C'</t>
@@ -768,7 +768,7 @@
     <t>/Game/External_Assets/Monster/Mechanicus/SKM_Mechanicus.SKM_Mechanicus</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Mechanicus.Icon_Mechanicus</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Mechanicus.Mechanicus</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Mechanicus/ABP_Mechanicus.ABP_Mechanicus_C'</t>
@@ -804,7 +804,7 @@
     <t>/Game/External_Assets/Monster/Megaron/SKM_Megaron_A.SKM_Megaron_A</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Megaron.Icon_Megaron</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Megaron.Megaron</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Megaron/ABP_Megaron.ABP_Megaron_C'</t>
@@ -828,7 +828,7 @@
     <t>/Game/External_Assets/Monster/Mimic/SKM_Mimic_Box.SKM_Mimic_Box</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Mimic.Icon_Mimic</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Mimic.Mimic</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Mimic/ABP_Mimic.ABP_Mimic_C'</t>
@@ -852,7 +852,7 @@
     <t>/Game/External_Assets/Monster/Octopus/SKM_octopus.SKM_octopus</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Octopus.Icon_Octopus</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Boss_Octopus.Icon_Boss_Octopus</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Octopus/ABP_Octopus.ABP_Octopus_C'</t>
@@ -876,7 +876,7 @@
     <t>/Game/External_Assets/Monster/PistolShrimp/SKM_PistolShrimp.SKM_PistolShrimp</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_PistolShrimp.Icon_PistolShrimp</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/PistolShrimp.PistolShrimp</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/PistolShrimp/ABP_PistolShrimp.ABP_PistolShrimp_C'</t>
@@ -900,7 +900,7 @@
     <t>/Game/External_Assets/Monster/Pufferfish/SKM_PufferFish_A.SKM_PufferFish_A</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Pufferfish.Icon_Pufferfish</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Pufferfish.Pufferfish</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Pufferfish/ABP_Pufferfish.ABP_Pufferfish_C'</t>
@@ -924,7 +924,7 @@
     <t>/Game/External_Assets/Monster/Seasoner/SKM_Seasoner.SKM_Seasoner</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Seasoner.Icon_Seasoner</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Boss_Seasoner.Icon_Boss_Seasoner</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Seasoner/ABP_Seasoner.ABP_Seasoner_C'</t>
@@ -972,7 +972,7 @@
     <t>/Game/External_Assets/Monster/Starspawn/SKM_Starspawn.SKM_Starspawn</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Starspawn.Icon_Starspawn</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Starspawn.Starspawn</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Starspawn/ABP_Starspawn.ABP_Starspawn_C'</t>
@@ -996,7 +996,7 @@
     <t>/Game/External_Assets/Monster/Ushabti/SKM_Ushabti.SKM_Ushabti</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Ushabti.Icon_Ushabti</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Ushabti.Ushabti</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Ushabti/ABP_Ushabti.ABP_Ushabti_C'</t>
@@ -1044,7 +1044,7 @@
     <t>/Game/External_Assets/Monster/Watcher/SKM_Watcher_A.SKM_Watcher_A</t>
   </si>
   <si>
-    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_Watcher.Icon_Watcher</t>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Watcher.Watcher</t>
   </si>
   <si>
     <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Enemy/Watcher/ABP_Watcher.ABP_Watcher_C'</t>
@@ -1054,6 +1054,42 @@
   </si>
   <si>
     <t>/Game/Blueprints/Characters/Enemy/Watcher/AM_Watcher_Dead.AM_Watcher_Dead</t>
+  </si>
+  <si>
+    <t>Foxhound</t>
+  </si>
+  <si>
+    <t>((TagName="FX.Enemy.Boss.Foxhound.Pattern1"),(TagName="FX.Enemy.Boss.Foxhound.Pattern2"))</t>
+  </si>
+  <si>
+    <t>((TagName="FX.Enemy.Boss.Foxhound.Pattern1Hit"),(TagName="FX.Enemy.Boss.Foxhound.Pattern2Hit"))</t>
+  </si>
+  <si>
+    <t>(FXData="/Game/Data/Assets/EnemyFXAssets/Boss/DA_EnemyFX_Boss_Foxhound.DA_EnemyFX_Boss_Foxhound",BasicAttackTag=(TagName="FX.Enemy.Boss.Foxhound.BasicAttack"),BasicAttackHitTag=(TagName="FX.Enemy.Boss.Foxhound.Hit"),HitTag=(TagName="FX.Enemy.Boss.Foxhound.Hit"),DeathTag=(TagName="FX.Enemy.Boss.Foxhound.Death"))</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Familiar/Foxhound/AM_Foxhound_Attack.AM_Foxhound_Attack</t>
+  </si>
+  <si>
+    <t>("/Game/Blueprints/Characters/Familiar/Foxhound/AM_Foxhound_Pattern1.AM_Foxhound_Pattern1","/Game/Blueprints/Characters/Familiar/Foxhound/AM_Foxhound_Pattern2.AM_Foxhound_Pattern2")</t>
+  </si>
+  <si>
+    <t>((AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_BossAreaPattern1.GA_BossAreaPattern1_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Heal_Skill.GE_Heal_Skill_C'",ProjectileClass=None),(AbilityClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Abilities/GA_BossProjectilePattern2.GA_BossProjectilePattern2_C'",EffectClass="/Script/Engine.BlueprintGeneratedClass'/Game/GAS/Effects/GE_Damage_Skill.GE_Damage_Skill_C'",ProjectileClass="/Script/Engine.BlueprintGeneratedClass'/Game/Blueprints/Object/Projectile/BP_Bullet.BP_Bullet_C'"))</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/Monster/Foxhound/SKM_Foxhound.SKM_Foxhound</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Character/Icon_Monster/Icon_FoxHound.Icon_FoxHound</t>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimBlueprintGeneratedClass'/Game/Blueprints/Characters/Familiar/Foxhound/ABP_Foxhound.ABP_Foxhound_C'</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Familiar/Foxhound/AM_Foxhound_Damage.AM_Foxhound_Damage</t>
+  </si>
+  <si>
+    <t>/Game/Blueprints/Characters/Familiar/Foxhound/AM_Foxhound_Dead.AM_Foxhound_Dead</t>
   </si>
 </sst>
 </file>
@@ -1971,7 +2007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R39"/>
+  <dimension ref="A1:R40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -2628,60 +2664,72 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>137</v>
+        <v>345</v>
+      </c>
+      <c r="B15" t="s">
+        <v>346</v>
+      </c>
+      <c r="C15" t="s">
+        <v>347</v>
       </c>
       <c r="D15">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>138</v>
+        <v>348</v>
       </c>
       <c r="F15" t="s">
-        <v>139</v>
+        <v>349</v>
+      </c>
+      <c r="G15" t="s">
+        <v>350</v>
       </c>
       <c r="H15" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="I15" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="J15" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="K15" t="s">
         <v>27</v>
       </c>
+      <c r="L15" t="s">
+        <v>351</v>
+      </c>
       <c r="M15" t="s">
         <v>29</v>
       </c>
       <c r="N15" t="s">
-        <v>140</v>
+        <v>352</v>
       </c>
       <c r="O15" t="s">
-        <v>141</v>
+        <v>353</v>
       </c>
       <c r="P15" t="s">
-        <v>142</v>
+        <v>354</v>
       </c>
       <c r="Q15" t="s">
-        <v>143</v>
+        <v>355</v>
       </c>
       <c r="R15" t="s">
-        <v>144</v>
+        <v>356</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D16">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="E16" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="F16" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="H16" t="s">
         <v>48</v>
@@ -2699,33 +2747,33 @@
         <v>29</v>
       </c>
       <c r="N16" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="O16" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="P16" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="Q16" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="R16" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D17">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="E17" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F17" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="H17" t="s">
         <v>48</v>
@@ -2743,133 +2791,133 @@
         <v>29</v>
       </c>
       <c r="N17" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="O17" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="P17" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="Q17" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="R17" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B18" t="s">
-        <v>162</v>
-      </c>
-      <c r="C18" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="D18">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="E18" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="F18" t="s">
-        <v>165</v>
-      </c>
-      <c r="G18" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="H18" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="I18" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="J18" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="K18" t="s">
         <v>27</v>
       </c>
-      <c r="L18" t="s">
-        <v>167</v>
-      </c>
       <c r="M18" t="s">
         <v>29</v>
       </c>
       <c r="N18" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="O18" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="P18" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="Q18" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="R18" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>173</v>
+        <v>161</v>
+      </c>
+      <c r="B19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19" t="s">
+        <v>163</v>
       </c>
       <c r="D19">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E19" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="F19" t="s">
-        <v>175</v>
+        <v>165</v>
+      </c>
+      <c r="G19" t="s">
+        <v>166</v>
       </c>
       <c r="H19" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="I19" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="J19" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="K19" t="s">
         <v>27</v>
       </c>
+      <c r="L19" t="s">
+        <v>167</v>
+      </c>
       <c r="M19" t="s">
         <v>29</v>
       </c>
       <c r="N19" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="O19" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="P19" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="Q19" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="R19" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="E20" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="F20" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="H20" t="s">
         <v>48</v>
@@ -2887,33 +2935,33 @@
         <v>29</v>
       </c>
       <c r="N20" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="O20" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="P20" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="Q20" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="R20" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F21" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="H21" t="s">
         <v>48</v>
@@ -2931,33 +2979,33 @@
         <v>29</v>
       </c>
       <c r="N21" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="O21" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="P21" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="Q21" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="R21" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D22">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E22" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="F22" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="H22" t="s">
         <v>48</v>
@@ -2975,33 +3023,33 @@
         <v>29</v>
       </c>
       <c r="N22" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="O22" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="P22" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="Q22" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="R22" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D23">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="E23" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F23" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H23" t="s">
         <v>48</v>
@@ -3019,33 +3067,33 @@
         <v>29</v>
       </c>
       <c r="N23" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="O23" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="P23" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="Q23" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="R23" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D24">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="E24" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="F24" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="H24" t="s">
         <v>48</v>
@@ -3063,33 +3111,33 @@
         <v>29</v>
       </c>
       <c r="N24" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="O24" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="P24" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="Q24" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="R24" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="D25">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="E25" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="F25" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="H25" t="s">
         <v>48</v>
@@ -3107,33 +3155,33 @@
         <v>29</v>
       </c>
       <c r="N25" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="O25" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="P25" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="Q25" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="R25" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D26">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="E26" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F26" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="H26" t="s">
         <v>48</v>
@@ -3145,39 +3193,39 @@
         <v>50</v>
       </c>
       <c r="K26" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="M26" t="s">
         <v>29</v>
       </c>
       <c r="N26" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="O26" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="P26" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="Q26" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="R26" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D27">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="E27" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="F27" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="H27" t="s">
         <v>48</v>
@@ -3189,39 +3237,39 @@
         <v>50</v>
       </c>
       <c r="K27" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="M27" t="s">
         <v>29</v>
       </c>
       <c r="N27" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="O27" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="P27" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="Q27" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="R27" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="D28">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="E28" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="F28" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="H28" t="s">
         <v>48</v>
@@ -3233,48 +3281,39 @@
         <v>50</v>
       </c>
       <c r="K28" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="M28" t="s">
         <v>29</v>
       </c>
       <c r="N28" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="O28" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="P28" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="Q28" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="R28" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>253</v>
-      </c>
-      <c r="B29" t="s">
-        <v>254</v>
-      </c>
-      <c r="C29" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="D29">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="E29" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="F29" t="s">
-        <v>257</v>
-      </c>
-      <c r="G29" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="H29" t="s">
         <v>48</v>
@@ -3286,42 +3325,48 @@
         <v>50</v>
       </c>
       <c r="K29" t="s">
-        <v>27</v>
-      </c>
-      <c r="L29" t="s">
-        <v>259</v>
+        <v>83</v>
       </c>
       <c r="M29" t="s">
         <v>29</v>
       </c>
       <c r="N29" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="O29" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="P29" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="Q29" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="R29" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>265</v>
+        <v>253</v>
+      </c>
+      <c r="B30" t="s">
+        <v>254</v>
+      </c>
+      <c r="C30" t="s">
+        <v>255</v>
       </c>
       <c r="D30">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="E30" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="F30" t="s">
-        <v>267</v>
+        <v>257</v>
+      </c>
+      <c r="G30" t="s">
+        <v>258</v>
       </c>
       <c r="H30" t="s">
         <v>48</v>
@@ -3335,37 +3380,40 @@
       <c r="K30" t="s">
         <v>27</v>
       </c>
+      <c r="L30" t="s">
+        <v>259</v>
+      </c>
       <c r="M30" t="s">
         <v>29</v>
       </c>
       <c r="N30" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="O30" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="P30" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="Q30" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="R30" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="D31">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="E31" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F31" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="H31" t="s">
         <v>48</v>
@@ -3383,33 +3431,33 @@
         <v>29</v>
       </c>
       <c r="N31" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="O31" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="P31" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="Q31" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="R31" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="D32">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="E32" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F32" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="H32" t="s">
         <v>48</v>
@@ -3427,33 +3475,33 @@
         <v>29</v>
       </c>
       <c r="N32" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="O32" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="P32" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="Q32" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="R32" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="D33">
         <v>0.6</v>
       </c>
       <c r="E33" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F33" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="H33" t="s">
         <v>48</v>
@@ -3471,33 +3519,33 @@
         <v>29</v>
       </c>
       <c r="N33" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="O33" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="P33" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="Q33" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="R33" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="D34">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="E34" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F34" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="H34" t="s">
         <v>48</v>
@@ -3515,33 +3563,33 @@
         <v>29</v>
       </c>
       <c r="N34" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="O34" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="P34" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="Q34" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="R34" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="D35">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="E35" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="F35" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="H35" t="s">
         <v>48</v>
@@ -3559,33 +3607,33 @@
         <v>29</v>
       </c>
       <c r="N35" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="O35" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="P35" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="Q35" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="R35" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="E36" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="F36" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="H36" t="s">
         <v>48</v>
@@ -3603,33 +3651,33 @@
         <v>29</v>
       </c>
       <c r="N36" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="O36" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="P36" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="Q36" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="R36" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="F37" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="H37" t="s">
         <v>48</v>
@@ -3647,33 +3695,33 @@
         <v>29</v>
       </c>
       <c r="N37" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="O37" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="P37" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="Q37" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="R37" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="F38" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="H38" t="s">
         <v>48</v>
@@ -3685,39 +3733,39 @@
         <v>50</v>
       </c>
       <c r="K38" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="M38" t="s">
         <v>29</v>
       </c>
       <c r="N38" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="O38" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="P38" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="Q38" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="R38" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F39" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="H39" t="s">
         <v>48</v>
@@ -3729,28 +3777,75 @@
         <v>50</v>
       </c>
       <c r="K39" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="M39" t="s">
         <v>29</v>
       </c>
       <c r="N39" t="s">
+        <v>332</v>
+      </c>
+      <c r="O39" t="s">
+        <v>333</v>
+      </c>
+      <c r="P39" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>335</v>
+      </c>
+      <c r="R39" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>337</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>338</v>
+      </c>
+      <c r="F40" t="s">
+        <v>339</v>
+      </c>
+      <c r="H40" t="s">
+        <v>48</v>
+      </c>
+      <c r="I40" t="s">
+        <v>49</v>
+      </c>
+      <c r="J40" t="s">
+        <v>50</v>
+      </c>
+      <c r="K40" t="s">
+        <v>27</v>
+      </c>
+      <c r="M40" t="s">
+        <v>29</v>
+      </c>
+      <c r="N40" t="s">
         <v>340</v>
       </c>
-      <c r="O39" t="s">
+      <c r="O40" t="s">
         <v>341</v>
       </c>
-      <c r="P39" t="s">
+      <c r="P40" t="s">
         <v>342</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="Q40" t="s">
         <v>343</v>
       </c>
-      <c r="R39" t="s">
+      <c r="R40" t="s">
         <v>344</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="A2:R40">
+    <sortCondition ref="A2"/>
+  </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
